--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD42B534-2A0E-4681-8691-0CD9F64A716D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1D15DA-D296-432E-A617-0F653630A77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -655,6 +655,9 @@
                 <c:pt idx="103">
                   <c:v>46276</c:v>
                 </c:pt>
+                <c:pt idx="104">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -977,7 +980,7 @@
                   <c:v>41.642173913043479</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0</c:v>
+                  <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>0</c:v>
@@ -2293,6 +2296,9 @@
                 <c:pt idx="103">
                   <c:v>46276</c:v>
                 </c:pt>
+                <c:pt idx="104">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2615,7 +2621,7 @@
                   <c:v>3.6068421052631581</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0</c:v>
+                  <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>0</c:v>
@@ -3931,6 +3937,9 @@
                 <c:pt idx="103">
                   <c:v>46276</c:v>
                 </c:pt>
+                <c:pt idx="104">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4253,7 +4262,7 @@
                   <c:v>3.0133333333333336</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>0</c:v>
@@ -5569,6 +5578,9 @@
                 <c:pt idx="103">
                   <c:v>46276</c:v>
                 </c:pt>
+                <c:pt idx="104">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5891,7 +5903,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>0</c:v>
@@ -15522,33 +15534,81 @@
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-      <c r="O109" s="3"/>
-      <c r="P109" s="3"/>
-      <c r="Q109" s="3"/>
-      <c r="R109" s="3"/>
-      <c r="S109" s="3"/>
-      <c r="T109" s="3"/>
-      <c r="U109" s="3"/>
-      <c r="V109" s="3"/>
-      <c r="W109" s="3"/>
-      <c r="X109" s="3"/>
-      <c r="Y109" s="4" t="str">
+      <c r="A109" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B109" s="3">
+        <v>39</v>
+      </c>
+      <c r="C109" s="3">
+        <v>44</v>
+      </c>
+      <c r="D109" s="3">
+        <v>44</v>
+      </c>
+      <c r="E109" s="3">
+        <v>42</v>
+      </c>
+      <c r="F109" s="3">
+        <v>43</v>
+      </c>
+      <c r="G109" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H109" s="3">
+        <v>44</v>
+      </c>
+      <c r="I109" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J109" s="3">
+        <v>42</v>
+      </c>
+      <c r="K109" s="3">
+        <v>38</v>
+      </c>
+      <c r="L109" s="3">
+        <v>36</v>
+      </c>
+      <c r="M109" s="3">
+        <v>41</v>
+      </c>
+      <c r="N109" s="3">
+        <v>44</v>
+      </c>
+      <c r="O109" s="3">
+        <v>41.17</v>
+      </c>
+      <c r="P109" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q109" s="3">
+        <v>43</v>
+      </c>
+      <c r="R109" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S109" s="3">
+        <v>42</v>
+      </c>
+      <c r="T109" s="3">
+        <v>41</v>
+      </c>
+      <c r="U109" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="V109" s="3">
+        <v>38</v>
+      </c>
+      <c r="W109" s="3">
+        <v>45</v>
+      </c>
+      <c r="X109" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y109" s="4">
         <f t="shared" si="26"/>
-        <v/>
+        <v>41.322608695652171</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.25">
@@ -30986,29 +31046,69 @@
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-      <c r="O109" s="3"/>
-      <c r="P109" s="3"/>
-      <c r="Q109" s="3"/>
-      <c r="R109" s="3"/>
-      <c r="S109" s="3"/>
-      <c r="T109" s="3"/>
-      <c r="U109" s="4" t="str">
+      <c r="A109" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B109" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C109" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D109" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E109" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F109" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G109" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H109" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I109" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J109" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K109" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="L109" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M109" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N109" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O109" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P109" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q109" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R109" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S109" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T109" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U109" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.4747368421052629</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -42152,19 +42252,39 @@
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="4" t="str">
+      <c r="A109" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B109" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C109" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D109" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E109" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F109" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G109" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H109" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I109" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J109" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K109" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -50815,20 +50935,42 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="4" t="str">
+      <c r="A109" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B109" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C109" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D109" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E109" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F109" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G109" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H109" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I109" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J109" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K109" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L109" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1D15DA-D296-432E-A617-0F653630A77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C95DBEF-DBE7-4EF4-AFB7-19AAA3A62F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -658,6 +658,9 @@
                 <c:pt idx="104">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="105">
+                  <c:v>46280</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -983,7 +986,7 @@
                   <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0</c:v>
+                  <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>0</c:v>
@@ -2299,6 +2302,9 @@
                 <c:pt idx="104">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="105">
+                  <c:v>46280</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2624,7 +2630,7 @@
                   <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0</c:v>
+                  <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>0</c:v>
@@ -3940,6 +3946,9 @@
                 <c:pt idx="104">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="105">
+                  <c:v>46280</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4265,7 +4274,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>0</c:v>
@@ -5581,6 +5590,9 @@
                 <c:pt idx="104">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="105">
+                  <c:v>46280</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5906,7 +5918,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>0</c:v>
@@ -15612,33 +15624,81 @@
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
-      <c r="O110" s="3"/>
-      <c r="P110" s="3"/>
-      <c r="Q110" s="3"/>
-      <c r="R110" s="3"/>
-      <c r="S110" s="3"/>
-      <c r="T110" s="3"/>
-      <c r="U110" s="3"/>
-      <c r="V110" s="3"/>
-      <c r="W110" s="3"/>
-      <c r="X110" s="3"/>
-      <c r="Y110" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A110" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B110" s="3">
+        <v>39</v>
+      </c>
+      <c r="C110" s="3">
+        <v>44</v>
+      </c>
+      <c r="D110" s="3">
+        <v>44</v>
+      </c>
+      <c r="E110" s="3">
+        <v>42</v>
+      </c>
+      <c r="F110" s="3">
+        <v>43</v>
+      </c>
+      <c r="G110" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H110" s="3">
+        <v>44</v>
+      </c>
+      <c r="I110" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J110" s="3">
+        <v>42</v>
+      </c>
+      <c r="K110" s="3">
+        <v>38</v>
+      </c>
+      <c r="L110" s="3">
+        <v>36</v>
+      </c>
+      <c r="M110" s="3">
+        <v>41</v>
+      </c>
+      <c r="N110" s="3">
+        <v>44</v>
+      </c>
+      <c r="O110" s="3">
+        <v>41.17</v>
+      </c>
+      <c r="P110" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q110" s="3">
+        <v>43</v>
+      </c>
+      <c r="R110" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S110" s="3">
+        <v>42</v>
+      </c>
+      <c r="T110" s="3">
+        <v>41</v>
+      </c>
+      <c r="U110" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="V110" s="3">
+        <v>38</v>
+      </c>
+      <c r="W110" s="3">
+        <v>45</v>
+      </c>
+      <c r="X110" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y110" s="4">
+        <f t="shared" ref="Y110" si="57">IF(COUNTA(B110:X110)=0,"",AVERAGE(B110:X110))</f>
+        <v>41.322608695652171</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.25">
@@ -16327,7 +16387,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="57">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="58">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16357,7 +16417,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16387,7 +16447,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16417,7 +16477,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16447,7 +16507,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16477,7 +16537,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16507,7 +16567,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16537,7 +16597,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16567,7 +16627,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16597,7 +16657,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16627,7 +16687,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="58">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="59">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="59">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="60">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="60">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="61">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="61">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="62">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -31112,29 +31172,69 @@
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
-      <c r="O110" s="3"/>
-      <c r="P110" s="3"/>
-      <c r="Q110" s="3"/>
-      <c r="R110" s="3"/>
-      <c r="S110" s="3"/>
-      <c r="T110" s="3"/>
-      <c r="U110" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A110" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B110" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C110" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D110" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E110" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F110" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G110" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H110" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I110" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J110" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K110" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="L110" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M110" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N110" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O110" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P110" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q110" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R110" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S110" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T110" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U110" s="4">
+        <f t="shared" ref="U110" si="65">IF(COUNTA(B110:T110)=0,"",AVERAGE(B110:T110))</f>
+        <v>3.4747368421052629</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -31731,7 +31831,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="65">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="66">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -31757,7 +31857,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31783,7 +31883,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31809,7 +31909,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31835,7 +31935,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31861,7 +31961,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31887,7 +31987,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31913,7 +32013,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31939,7 +32039,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31965,7 +32065,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31991,7 +32091,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32017,7 +32117,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32043,7 +32143,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32069,7 +32169,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32095,7 +32195,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32121,7 +32221,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32147,7 +32247,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32173,7 +32273,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32199,7 +32299,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32225,7 +32325,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32251,7 +32351,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32277,7 +32377,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32303,7 +32403,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32329,7 +32429,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32355,7 +32455,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32381,7 +32481,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32407,7 +32507,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32433,7 +32533,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32459,7 +32559,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32485,7 +32585,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32511,7 +32611,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32537,7 +32637,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32563,7 +32663,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32589,7 +32689,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32615,7 +32715,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32641,7 +32741,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32667,7 +32767,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32693,7 +32793,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32719,7 +32819,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32745,7 +32845,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32771,7 +32871,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32797,7 +32897,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32823,7 +32923,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32849,7 +32949,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32875,7 +32975,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32901,7 +33001,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32927,7 +33027,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32953,7 +33053,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -32979,7 +33079,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33005,7 +33105,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33031,7 +33131,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33057,7 +33157,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33083,7 +33183,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33109,7 +33209,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33135,7 +33235,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33161,7 +33261,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33187,7 +33287,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33213,7 +33313,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33239,7 +33339,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33265,7 +33365,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33291,7 +33391,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33317,7 +33417,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33343,7 +33443,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33369,7 +33469,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -33395,7 +33495,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="66">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="67">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -33421,7 +33521,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33447,7 +33547,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33473,7 +33573,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33499,7 +33599,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33525,7 +33625,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33551,7 +33651,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33577,7 +33677,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33603,7 +33703,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33629,7 +33729,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33655,7 +33755,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33681,7 +33781,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33707,7 +33807,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33733,7 +33833,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33759,7 +33859,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33785,7 +33885,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33811,7 +33911,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33837,7 +33937,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33863,7 +33963,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33889,7 +33989,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33915,7 +34015,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33941,7 +34041,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33967,7 +34067,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33993,7 +34093,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34019,7 +34119,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34045,7 +34145,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34071,7 +34171,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34097,7 +34197,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34123,7 +34223,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34149,7 +34249,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34175,7 +34275,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34201,7 +34301,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34227,7 +34327,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34253,7 +34353,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34279,7 +34379,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34305,7 +34405,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34331,7 +34431,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34357,7 +34457,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34383,7 +34483,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34409,7 +34509,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34435,7 +34535,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34461,7 +34561,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34487,7 +34587,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34513,7 +34613,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34539,7 +34639,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34565,7 +34665,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34591,7 +34691,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34617,7 +34717,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34643,7 +34743,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34669,7 +34769,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34695,7 +34795,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34721,7 +34821,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34747,7 +34847,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34773,7 +34873,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34799,7 +34899,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34825,7 +34925,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34851,7 +34951,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34877,7 +34977,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34903,7 +35003,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34929,7 +35029,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34955,7 +35055,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -34981,7 +35081,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -35007,7 +35107,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -35033,7 +35133,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -35059,7 +35159,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="67">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="68">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35085,7 +35185,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35111,7 +35211,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35137,7 +35237,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35163,7 +35263,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35189,7 +35289,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35215,7 +35315,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35241,7 +35341,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35267,7 +35367,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35293,7 +35393,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35319,7 +35419,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35345,7 +35445,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35371,7 +35471,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35397,7 +35497,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35423,7 +35523,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35449,7 +35549,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35475,7 +35575,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35501,7 +35601,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35527,7 +35627,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35553,7 +35653,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35579,7 +35679,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35605,7 +35705,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35631,7 +35731,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35657,7 +35757,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35683,7 +35783,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35709,7 +35809,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35735,7 +35835,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35761,7 +35861,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35787,7 +35887,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35813,7 +35913,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35839,7 +35939,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35865,7 +35965,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35891,7 +35991,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35917,7 +36017,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35943,7 +36043,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35969,7 +36069,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35995,7 +36095,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36021,7 +36121,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36047,7 +36147,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36073,7 +36173,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36099,7 +36199,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36125,7 +36225,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36151,7 +36251,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36177,7 +36277,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36203,7 +36303,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36229,7 +36329,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36255,7 +36355,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36281,7 +36381,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36307,7 +36407,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36333,7 +36433,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36359,7 +36459,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36385,7 +36485,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36411,7 +36511,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36437,7 +36537,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36463,7 +36563,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36489,7 +36589,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36515,7 +36615,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36541,7 +36641,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36567,7 +36667,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36593,7 +36693,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36619,7 +36719,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36645,7 +36745,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36671,7 +36771,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36697,7 +36797,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -36723,7 +36823,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="68">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="69">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -36749,7 +36849,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36775,7 +36875,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36801,7 +36901,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36827,7 +36927,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36853,7 +36953,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36879,7 +36979,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36905,7 +37005,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36931,7 +37031,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36957,7 +37057,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36983,7 +37083,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37009,7 +37109,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37035,7 +37135,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37061,7 +37161,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37087,7 +37187,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37113,7 +37213,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37139,7 +37239,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37165,7 +37265,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37191,7 +37291,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37217,7 +37317,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37243,7 +37343,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37269,7 +37369,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37295,7 +37395,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37321,7 +37421,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37347,7 +37447,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37373,7 +37473,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37399,7 +37499,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37425,7 +37525,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37451,7 +37551,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37477,7 +37577,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37503,7 +37603,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37529,7 +37629,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37555,7 +37655,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37581,7 +37681,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37607,7 +37707,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37633,7 +37733,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37659,7 +37759,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37685,7 +37785,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37711,7 +37811,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37737,7 +37837,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37763,7 +37863,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37789,7 +37889,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37815,7 +37915,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37841,7 +37941,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37867,7 +37967,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37893,7 +37993,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37919,7 +38019,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37945,7 +38045,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37971,7 +38071,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -37997,7 +38097,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38023,7 +38123,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38049,7 +38149,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38075,7 +38175,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38101,7 +38201,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38127,7 +38227,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38153,7 +38253,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38179,7 +38279,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38205,7 +38305,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38231,7 +38331,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38257,7 +38357,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38283,7 +38383,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38309,7 +38409,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38335,7 +38435,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38361,7 +38461,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -38387,7 +38487,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="69">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="70">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -38413,7 +38513,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -42288,19 +42388,39 @@
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A110" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B110" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C110" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D110" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E110" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F110" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G110" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H110" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I110" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J110" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K110" s="4">
+        <f t="shared" ref="K110" si="65">IF(COUNTA(B110:J110)=0,"",AVERAGE(B110:J110))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -42667,7 +42787,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="65">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="66">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -42683,7 +42803,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42699,7 +42819,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42715,7 +42835,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42731,7 +42851,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42747,7 +42867,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42763,7 +42883,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42779,7 +42899,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42795,7 +42915,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42811,7 +42931,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42827,7 +42947,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42843,7 +42963,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42859,7 +42979,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42875,7 +42995,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42891,7 +43011,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42907,7 +43027,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42923,7 +43043,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42939,7 +43059,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42955,7 +43075,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42971,7 +43091,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -42987,7 +43107,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43003,7 +43123,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43019,7 +43139,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43035,7 +43155,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43051,7 +43171,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43067,7 +43187,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43083,7 +43203,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43099,7 +43219,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43115,7 +43235,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43131,7 +43251,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43147,7 +43267,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43163,7 +43283,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43179,7 +43299,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43195,7 +43315,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43211,7 +43331,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43227,7 +43347,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43243,7 +43363,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43259,7 +43379,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43275,7 +43395,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43291,7 +43411,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43307,7 +43427,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43323,7 +43443,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43339,7 +43459,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43355,7 +43475,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43371,7 +43491,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43387,7 +43507,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43403,7 +43523,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43419,7 +43539,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43435,7 +43555,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43451,7 +43571,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43467,7 +43587,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43483,7 +43603,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43499,7 +43619,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43515,7 +43635,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43531,7 +43651,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43547,7 +43667,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43563,7 +43683,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43579,7 +43699,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43595,7 +43715,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43611,7 +43731,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43627,7 +43747,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43643,7 +43763,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43659,7 +43779,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43675,7 +43795,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -43691,7 +43811,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="66">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="67">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -43707,7 +43827,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43723,7 +43843,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43739,7 +43859,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43755,7 +43875,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43771,7 +43891,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43787,7 +43907,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43803,7 +43923,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43819,7 +43939,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43835,7 +43955,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43851,7 +43971,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43867,7 +43987,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43883,7 +44003,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43899,7 +44019,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43915,7 +44035,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43931,7 +44051,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43947,7 +44067,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43963,7 +44083,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43979,7 +44099,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43995,7 +44115,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44011,7 +44131,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44027,7 +44147,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44043,7 +44163,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44059,7 +44179,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44075,7 +44195,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44091,7 +44211,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44107,7 +44227,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44123,7 +44243,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44139,7 +44259,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44155,7 +44275,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44171,7 +44291,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44187,7 +44307,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44203,7 +44323,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44219,7 +44339,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44235,7 +44355,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44251,7 +44371,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44267,7 +44387,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44283,7 +44403,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44299,7 +44419,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44315,7 +44435,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44331,7 +44451,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44347,7 +44467,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44363,7 +44483,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44379,7 +44499,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44395,7 +44515,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44411,7 +44531,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44427,7 +44547,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44443,7 +44563,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44459,7 +44579,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44475,7 +44595,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44491,7 +44611,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44507,7 +44627,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44523,7 +44643,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44539,7 +44659,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44555,7 +44675,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44571,7 +44691,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44587,7 +44707,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44603,7 +44723,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44619,7 +44739,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44635,7 +44755,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44651,7 +44771,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44667,7 +44787,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44683,7 +44803,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44699,7 +44819,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -44715,7 +44835,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="67">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="68">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -44731,7 +44851,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44747,7 +44867,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44763,7 +44883,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44779,7 +44899,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44795,7 +44915,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44811,7 +44931,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44827,7 +44947,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44843,7 +44963,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44859,7 +44979,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44875,7 +44995,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44891,7 +45011,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44907,7 +45027,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44923,7 +45043,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44939,7 +45059,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44955,7 +45075,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44971,7 +45091,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44987,7 +45107,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45003,7 +45123,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45019,7 +45139,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45035,7 +45155,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45051,7 +45171,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45067,7 +45187,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45083,7 +45203,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45099,7 +45219,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45115,7 +45235,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45131,7 +45251,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45147,7 +45267,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45163,7 +45283,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45179,7 +45299,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45195,7 +45315,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45211,7 +45331,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45227,7 +45347,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45243,7 +45363,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45259,7 +45379,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45275,7 +45395,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45291,7 +45411,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45307,7 +45427,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45323,7 +45443,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45339,7 +45459,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45355,7 +45475,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45371,7 +45491,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45387,7 +45507,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45403,7 +45523,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45419,7 +45539,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45435,7 +45555,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45451,7 +45571,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45467,7 +45587,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45483,7 +45603,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45499,7 +45619,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45515,7 +45635,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45531,7 +45651,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45547,7 +45667,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45563,7 +45683,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45579,7 +45699,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45595,7 +45715,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45611,7 +45731,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45627,7 +45747,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45643,7 +45763,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45659,7 +45779,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45675,7 +45795,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45691,7 +45811,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45707,7 +45827,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45723,7 +45843,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -45739,7 +45859,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="68">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="69">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -45755,7 +45875,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45771,7 +45891,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45787,7 +45907,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45803,7 +45923,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45819,7 +45939,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45835,7 +45955,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45851,7 +45971,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45867,7 +45987,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45883,7 +46003,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45899,7 +46019,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45915,7 +46035,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45931,7 +46051,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45947,7 +46067,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45963,7 +46083,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45979,7 +46099,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45995,7 +46115,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46011,7 +46131,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46027,7 +46147,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46043,7 +46163,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46059,7 +46179,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46075,7 +46195,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46091,7 +46211,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46107,7 +46227,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46123,7 +46243,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46139,7 +46259,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46155,7 +46275,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46171,7 +46291,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46187,7 +46307,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46203,7 +46323,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46219,7 +46339,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46235,7 +46355,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46251,7 +46371,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46267,7 +46387,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46283,7 +46403,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46299,7 +46419,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46315,7 +46435,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46331,7 +46451,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46347,7 +46467,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46363,7 +46483,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46379,7 +46499,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46395,7 +46515,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46411,7 +46531,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46427,7 +46547,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46443,7 +46563,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46459,7 +46579,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46475,7 +46595,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46491,7 +46611,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46507,7 +46627,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46523,7 +46643,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46539,7 +46659,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46555,7 +46675,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46571,7 +46691,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46587,7 +46707,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46603,7 +46723,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46619,7 +46739,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46635,7 +46755,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46651,7 +46771,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46667,7 +46787,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46683,7 +46803,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46699,7 +46819,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46715,7 +46835,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46731,7 +46851,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46747,7 +46867,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -46763,7 +46883,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="69">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="70">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -46779,7 +46899,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -50974,20 +51094,42 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A110" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B110" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C110" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D110" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E110" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F110" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G110" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H110" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I110" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J110" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K110" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L110" s="4">
+        <f t="shared" ref="L110" si="65">IF(COUNTA(B110:K110)=0,"",AVERAGE(B110:K110))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -51377,7 +51519,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="65">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="66">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -51394,7 +51536,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51411,7 +51553,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51428,7 +51570,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51445,7 +51587,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51462,7 +51604,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51479,7 +51621,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51496,7 +51638,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51513,7 +51655,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51530,7 +51672,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51547,7 +51689,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51564,7 +51706,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51581,7 +51723,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51598,7 +51740,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51615,7 +51757,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51632,7 +51774,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51649,7 +51791,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51666,7 +51808,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51683,7 +51825,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51700,7 +51842,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51717,7 +51859,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51734,7 +51876,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51751,7 +51893,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51768,7 +51910,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51785,7 +51927,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51802,7 +51944,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51819,7 +51961,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51836,7 +51978,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51853,7 +51995,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51870,7 +52012,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51887,7 +52029,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51904,7 +52046,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51921,7 +52063,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51938,7 +52080,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51955,7 +52097,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51972,7 +52114,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -51989,7 +52131,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52006,7 +52148,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52023,7 +52165,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52040,7 +52182,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52057,7 +52199,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52074,7 +52216,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52091,7 +52233,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52108,7 +52250,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52125,7 +52267,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52142,7 +52284,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52159,7 +52301,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52176,7 +52318,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52193,7 +52335,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52210,7 +52352,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52227,7 +52369,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52244,7 +52386,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52261,7 +52403,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52278,7 +52420,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52295,7 +52437,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52312,7 +52454,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52329,7 +52471,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52346,7 +52488,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52363,7 +52505,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52380,7 +52522,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52397,7 +52539,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52414,7 +52556,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52431,7 +52573,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52448,7 +52590,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -52465,7 +52607,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="66">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="67">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -52482,7 +52624,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52499,7 +52641,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52516,7 +52658,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52533,7 +52675,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52550,7 +52692,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52567,7 +52709,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52584,7 +52726,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52601,7 +52743,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52618,7 +52760,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52635,7 +52777,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52652,7 +52794,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52669,7 +52811,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52686,7 +52828,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52703,7 +52845,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52720,7 +52862,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52737,7 +52879,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52754,7 +52896,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52771,7 +52913,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52788,7 +52930,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52805,7 +52947,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52822,7 +52964,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52839,7 +52981,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52856,7 +52998,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52873,7 +53015,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52890,7 +53032,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52907,7 +53049,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52924,7 +53066,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52941,7 +53083,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52958,7 +53100,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52975,7 +53117,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52992,7 +53134,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53009,7 +53151,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53026,7 +53168,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53043,7 +53185,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53060,7 +53202,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53077,7 +53219,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53094,7 +53236,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53111,7 +53253,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53128,7 +53270,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53145,7 +53287,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53162,7 +53304,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53179,7 +53321,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53196,7 +53338,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53213,7 +53355,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53230,7 +53372,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53247,7 +53389,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53264,7 +53406,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53281,7 +53423,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53298,7 +53440,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53315,7 +53457,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53332,7 +53474,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53349,7 +53491,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53366,7 +53508,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53383,7 +53525,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53400,7 +53542,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53417,7 +53559,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53434,7 +53576,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53451,7 +53593,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53468,7 +53610,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53485,7 +53627,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53502,7 +53644,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53519,7 +53661,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53536,7 +53678,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -53553,7 +53695,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="67">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="68">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -53570,7 +53712,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53587,7 +53729,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53604,7 +53746,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53621,7 +53763,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53638,7 +53780,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53655,7 +53797,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53672,7 +53814,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53689,7 +53831,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53706,7 +53848,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53723,7 +53865,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53740,7 +53882,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53757,7 +53899,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53774,7 +53916,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53791,7 +53933,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53808,7 +53950,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53825,7 +53967,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53842,7 +53984,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53859,7 +54001,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53876,7 +54018,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53893,7 +54035,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53910,7 +54052,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53927,7 +54069,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53944,7 +54086,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53961,7 +54103,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53978,7 +54120,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53995,7 +54137,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54012,7 +54154,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54029,7 +54171,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54046,7 +54188,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54063,7 +54205,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54080,7 +54222,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54097,7 +54239,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54114,7 +54256,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54131,7 +54273,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54148,7 +54290,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54165,7 +54307,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54182,7 +54324,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54199,7 +54341,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54216,7 +54358,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54233,7 +54375,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54250,7 +54392,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54267,7 +54409,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54284,7 +54426,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54301,7 +54443,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54318,7 +54460,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54335,7 +54477,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54352,7 +54494,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54369,7 +54511,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54386,7 +54528,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54403,7 +54545,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54420,7 +54562,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54437,7 +54579,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54454,7 +54596,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54471,7 +54613,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54488,7 +54630,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54505,7 +54647,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54522,7 +54664,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54539,7 +54681,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54556,7 +54698,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54573,7 +54715,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54590,7 +54732,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54607,7 +54749,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54624,7 +54766,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -54641,7 +54783,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="68">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="69">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -54658,7 +54800,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54675,7 +54817,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54692,7 +54834,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54709,7 +54851,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54726,7 +54868,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54743,7 +54885,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54760,7 +54902,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54777,7 +54919,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54794,7 +54936,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54811,7 +54953,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54828,7 +54970,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54845,7 +54987,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54862,7 +55004,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54879,7 +55021,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54896,7 +55038,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54913,7 +55055,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54930,7 +55072,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54947,7 +55089,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54964,7 +55106,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54981,7 +55123,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54998,7 +55140,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55015,7 +55157,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55032,7 +55174,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55049,7 +55191,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55066,7 +55208,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55083,7 +55225,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55100,7 +55242,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55117,7 +55259,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55134,7 +55276,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55151,7 +55293,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55168,7 +55310,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55185,7 +55327,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55202,7 +55344,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55219,7 +55361,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55236,7 +55378,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55253,7 +55395,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55270,7 +55412,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55287,7 +55429,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55304,7 +55446,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55321,7 +55463,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55338,7 +55480,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55355,7 +55497,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55372,7 +55514,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55389,7 +55531,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55406,7 +55548,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55423,7 +55565,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55440,7 +55582,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55457,7 +55599,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55474,7 +55616,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55491,7 +55633,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55508,7 +55650,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55525,7 +55667,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55542,7 +55684,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55559,7 +55701,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55576,7 +55718,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55593,7 +55735,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55610,7 +55752,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55627,7 +55769,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55644,7 +55786,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55661,7 +55803,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55678,7 +55820,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55695,7 +55837,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55712,7 +55854,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -55729,7 +55871,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="69">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="70">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -55746,7 +55888,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C95DBEF-DBE7-4EF4-AFB7-19AAA3A62F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173C487A-0A4C-4A1E-A6F0-A13DE070208E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,6 +661,9 @@
                 <c:pt idx="105">
                   <c:v>46280</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -989,7 +992,7 @@
                   <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0</c:v>
+                  <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>0</c:v>
@@ -2305,6 +2308,9 @@
                 <c:pt idx="105">
                   <c:v>46280</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2633,7 +2639,7 @@
                   <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0</c:v>
+                  <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>0</c:v>
@@ -3949,6 +3955,9 @@
                 <c:pt idx="105">
                   <c:v>46280</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4277,7 +4286,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>0</c:v>
@@ -5593,6 +5602,9 @@
                 <c:pt idx="105">
                   <c:v>46280</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5921,7 +5933,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>0</c:v>
@@ -15702,33 +15714,81 @@
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3"/>
-      <c r="O111" s="3"/>
-      <c r="P111" s="3"/>
-      <c r="Q111" s="3"/>
-      <c r="R111" s="3"/>
-      <c r="S111" s="3"/>
-      <c r="T111" s="3"/>
-      <c r="U111" s="3"/>
-      <c r="V111" s="3"/>
-      <c r="W111" s="3"/>
-      <c r="X111" s="3"/>
-      <c r="Y111" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A111" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B111" s="3">
+        <v>39</v>
+      </c>
+      <c r="C111" s="3">
+        <v>44</v>
+      </c>
+      <c r="D111" s="3">
+        <v>44</v>
+      </c>
+      <c r="E111" s="3">
+        <v>42</v>
+      </c>
+      <c r="F111" s="3">
+        <v>43</v>
+      </c>
+      <c r="G111" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H111" s="3">
+        <v>44</v>
+      </c>
+      <c r="I111" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J111" s="3">
+        <v>42</v>
+      </c>
+      <c r="K111" s="3">
+        <v>38</v>
+      </c>
+      <c r="L111" s="3">
+        <v>36</v>
+      </c>
+      <c r="M111" s="3">
+        <v>41</v>
+      </c>
+      <c r="N111" s="3">
+        <v>44</v>
+      </c>
+      <c r="O111" s="3">
+        <v>41.17</v>
+      </c>
+      <c r="P111" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q111" s="3">
+        <v>43</v>
+      </c>
+      <c r="R111" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S111" s="3">
+        <v>42</v>
+      </c>
+      <c r="T111" s="3">
+        <v>41</v>
+      </c>
+      <c r="U111" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="V111" s="3">
+        <v>38</v>
+      </c>
+      <c r="W111" s="3">
+        <v>45</v>
+      </c>
+      <c r="X111" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y111" s="4">
+        <f t="shared" ref="Y111" si="58">IF(COUNTA(B111:X111)=0,"",AVERAGE(B111:X111))</f>
+        <v>41.322608695652171</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
@@ -16387,7 +16447,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="58">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="59">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16417,7 +16477,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16447,7 +16507,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16477,7 +16537,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16507,7 +16567,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16537,7 +16597,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16567,7 +16627,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16597,7 +16657,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16627,7 +16687,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="59">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="60">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="60">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="61">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="61">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="62">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="62">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="63">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -31238,29 +31298,69 @@
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3"/>
-      <c r="O111" s="3"/>
-      <c r="P111" s="3"/>
-      <c r="Q111" s="3"/>
-      <c r="R111" s="3"/>
-      <c r="S111" s="3"/>
-      <c r="T111" s="3"/>
-      <c r="U111" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A111" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B111" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C111" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D111" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E111" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F111" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G111" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H111" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I111" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J111" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K111" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="L111" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M111" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N111" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O111" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P111" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q111" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R111" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S111" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T111" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U111" s="4">
+        <f t="shared" ref="U111" si="66">IF(COUNTA(B111:T111)=0,"",AVERAGE(B111:T111))</f>
+        <v>3.4747368421052629</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -31831,7 +31931,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="66">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="67">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -31857,7 +31957,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -31883,7 +31983,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -31909,7 +32009,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -31935,7 +32035,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -31961,7 +32061,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -31987,7 +32087,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32013,7 +32113,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32039,7 +32139,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32065,7 +32165,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32091,7 +32191,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32117,7 +32217,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32143,7 +32243,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32169,7 +32269,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32195,7 +32295,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32221,7 +32321,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32247,7 +32347,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32273,7 +32373,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32299,7 +32399,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32325,7 +32425,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32351,7 +32451,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32377,7 +32477,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32403,7 +32503,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32429,7 +32529,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32455,7 +32555,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32481,7 +32581,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32507,7 +32607,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32533,7 +32633,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32559,7 +32659,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32585,7 +32685,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32611,7 +32711,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32637,7 +32737,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32663,7 +32763,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32689,7 +32789,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32715,7 +32815,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32741,7 +32841,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32767,7 +32867,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32793,7 +32893,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32819,7 +32919,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32845,7 +32945,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32871,7 +32971,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32897,7 +32997,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32923,7 +33023,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32949,7 +33049,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -32975,7 +33075,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33001,7 +33101,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33027,7 +33127,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33053,7 +33153,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33079,7 +33179,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33105,7 +33205,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33131,7 +33231,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33157,7 +33257,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33183,7 +33283,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33209,7 +33309,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33235,7 +33335,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33261,7 +33361,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33287,7 +33387,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33313,7 +33413,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33339,7 +33439,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33365,7 +33465,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33391,7 +33491,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33417,7 +33517,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33443,7 +33543,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33469,7 +33569,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -33495,7 +33595,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="67">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="68">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -33521,7 +33621,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33547,7 +33647,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33573,7 +33673,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33599,7 +33699,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33625,7 +33725,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33651,7 +33751,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33677,7 +33777,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33703,7 +33803,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33729,7 +33829,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33755,7 +33855,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33781,7 +33881,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33807,7 +33907,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33833,7 +33933,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33859,7 +33959,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33885,7 +33985,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33911,7 +34011,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33937,7 +34037,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33963,7 +34063,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33989,7 +34089,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34015,7 +34115,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34041,7 +34141,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34067,7 +34167,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34093,7 +34193,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34119,7 +34219,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34145,7 +34245,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34171,7 +34271,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34197,7 +34297,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34223,7 +34323,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34249,7 +34349,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34275,7 +34375,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34301,7 +34401,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34327,7 +34427,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34353,7 +34453,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34379,7 +34479,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34405,7 +34505,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34431,7 +34531,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34457,7 +34557,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34483,7 +34583,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34509,7 +34609,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34535,7 +34635,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34561,7 +34661,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34587,7 +34687,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34613,7 +34713,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34639,7 +34739,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34665,7 +34765,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34691,7 +34791,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34717,7 +34817,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34743,7 +34843,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34769,7 +34869,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34795,7 +34895,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34821,7 +34921,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34847,7 +34947,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34873,7 +34973,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34899,7 +34999,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34925,7 +35025,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34951,7 +35051,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -34977,7 +35077,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35003,7 +35103,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35029,7 +35129,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35055,7 +35155,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35081,7 +35181,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35107,7 +35207,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35133,7 +35233,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -35159,7 +35259,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="68">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="69">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35185,7 +35285,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35211,7 +35311,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35237,7 +35337,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35263,7 +35363,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35289,7 +35389,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35315,7 +35415,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35341,7 +35441,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35367,7 +35467,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35393,7 +35493,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35419,7 +35519,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35445,7 +35545,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35471,7 +35571,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35497,7 +35597,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35523,7 +35623,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35549,7 +35649,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35575,7 +35675,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35601,7 +35701,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35627,7 +35727,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35653,7 +35753,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35679,7 +35779,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35705,7 +35805,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35731,7 +35831,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35757,7 +35857,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35783,7 +35883,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35809,7 +35909,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35835,7 +35935,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35861,7 +35961,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35887,7 +35987,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35913,7 +36013,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35939,7 +36039,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35965,7 +36065,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35991,7 +36091,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36017,7 +36117,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36043,7 +36143,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36069,7 +36169,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36095,7 +36195,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36121,7 +36221,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36147,7 +36247,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36173,7 +36273,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36199,7 +36299,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36225,7 +36325,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36251,7 +36351,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36277,7 +36377,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36303,7 +36403,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36329,7 +36429,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36355,7 +36455,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36381,7 +36481,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36407,7 +36507,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36433,7 +36533,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36459,7 +36559,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36485,7 +36585,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36511,7 +36611,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36537,7 +36637,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36563,7 +36663,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36589,7 +36689,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36615,7 +36715,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36641,7 +36741,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36667,7 +36767,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36693,7 +36793,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36719,7 +36819,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36745,7 +36845,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36771,7 +36871,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36797,7 +36897,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -36823,7 +36923,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="69">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="70">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -36849,7 +36949,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36875,7 +36975,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36901,7 +37001,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36927,7 +37027,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36953,7 +37053,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36979,7 +37079,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37005,7 +37105,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37031,7 +37131,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37057,7 +37157,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37083,7 +37183,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37109,7 +37209,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37135,7 +37235,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37161,7 +37261,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37187,7 +37287,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37213,7 +37313,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37239,7 +37339,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37265,7 +37365,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37291,7 +37391,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37317,7 +37417,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37343,7 +37443,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37369,7 +37469,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37395,7 +37495,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37421,7 +37521,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37447,7 +37547,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37473,7 +37573,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37499,7 +37599,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37525,7 +37625,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37551,7 +37651,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37577,7 +37677,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37603,7 +37703,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37629,7 +37729,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37655,7 +37755,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37681,7 +37781,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37707,7 +37807,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37733,7 +37833,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37759,7 +37859,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37785,7 +37885,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37811,7 +37911,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37837,7 +37937,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37863,7 +37963,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37889,7 +37989,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37915,7 +38015,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37941,7 +38041,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37967,7 +38067,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -37993,7 +38093,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38019,7 +38119,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38045,7 +38145,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38071,7 +38171,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38097,7 +38197,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38123,7 +38223,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38149,7 +38249,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38175,7 +38275,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38201,7 +38301,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38227,7 +38327,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38253,7 +38353,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38279,7 +38379,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38305,7 +38405,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38331,7 +38431,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38357,7 +38457,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38383,7 +38483,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38409,7 +38509,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38435,7 +38535,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38461,7 +38561,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -38487,7 +38587,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="70">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="71">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -38513,7 +38613,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -42424,19 +42524,39 @@
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A111" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B111" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C111" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D111" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E111" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F111" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G111" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H111" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I111" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J111" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K111" s="4">
+        <f t="shared" ref="K111" si="66">IF(COUNTA(B111:J111)=0,"",AVERAGE(B111:J111))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -42787,7 +42907,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="66">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="67">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -42803,7 +42923,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42819,7 +42939,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42835,7 +42955,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42851,7 +42971,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42867,7 +42987,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42883,7 +43003,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42899,7 +43019,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42915,7 +43035,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42931,7 +43051,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42947,7 +43067,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42963,7 +43083,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42979,7 +43099,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -42995,7 +43115,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43011,7 +43131,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43027,7 +43147,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43043,7 +43163,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43059,7 +43179,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43075,7 +43195,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43091,7 +43211,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43107,7 +43227,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43123,7 +43243,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43139,7 +43259,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43155,7 +43275,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43171,7 +43291,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43187,7 +43307,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43203,7 +43323,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43219,7 +43339,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43235,7 +43355,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43251,7 +43371,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43267,7 +43387,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43283,7 +43403,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43299,7 +43419,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43315,7 +43435,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43331,7 +43451,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43347,7 +43467,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43363,7 +43483,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43379,7 +43499,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43395,7 +43515,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43411,7 +43531,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43427,7 +43547,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43443,7 +43563,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43459,7 +43579,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43475,7 +43595,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43491,7 +43611,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43507,7 +43627,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43523,7 +43643,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43539,7 +43659,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43555,7 +43675,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43571,7 +43691,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43587,7 +43707,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43603,7 +43723,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43619,7 +43739,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43635,7 +43755,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43651,7 +43771,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43667,7 +43787,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43683,7 +43803,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43699,7 +43819,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43715,7 +43835,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43731,7 +43851,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43747,7 +43867,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43763,7 +43883,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43779,7 +43899,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43795,7 +43915,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -43811,7 +43931,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="67">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="68">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -43827,7 +43947,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43843,7 +43963,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43859,7 +43979,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43875,7 +43995,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43891,7 +44011,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43907,7 +44027,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43923,7 +44043,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43939,7 +44059,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43955,7 +44075,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43971,7 +44091,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43987,7 +44107,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44003,7 +44123,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44019,7 +44139,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44035,7 +44155,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44051,7 +44171,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44067,7 +44187,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44083,7 +44203,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44099,7 +44219,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44115,7 +44235,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44131,7 +44251,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44147,7 +44267,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44163,7 +44283,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44179,7 +44299,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44195,7 +44315,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44211,7 +44331,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44227,7 +44347,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44243,7 +44363,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44259,7 +44379,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44275,7 +44395,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44291,7 +44411,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44307,7 +44427,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44323,7 +44443,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44339,7 +44459,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44355,7 +44475,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44371,7 +44491,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44387,7 +44507,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44403,7 +44523,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44419,7 +44539,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44435,7 +44555,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44451,7 +44571,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44467,7 +44587,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44483,7 +44603,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44499,7 +44619,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44515,7 +44635,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44531,7 +44651,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44547,7 +44667,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44563,7 +44683,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44579,7 +44699,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44595,7 +44715,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44611,7 +44731,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44627,7 +44747,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44643,7 +44763,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44659,7 +44779,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44675,7 +44795,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44691,7 +44811,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44707,7 +44827,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44723,7 +44843,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44739,7 +44859,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44755,7 +44875,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44771,7 +44891,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44787,7 +44907,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44803,7 +44923,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44819,7 +44939,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -44835,7 +44955,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="68">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="69">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -44851,7 +44971,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44867,7 +44987,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44883,7 +45003,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44899,7 +45019,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44915,7 +45035,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44931,7 +45051,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44947,7 +45067,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44963,7 +45083,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44979,7 +45099,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44995,7 +45115,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45011,7 +45131,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45027,7 +45147,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45043,7 +45163,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45059,7 +45179,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45075,7 +45195,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45091,7 +45211,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45107,7 +45227,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45123,7 +45243,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45139,7 +45259,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45155,7 +45275,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45171,7 +45291,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45187,7 +45307,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45203,7 +45323,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45219,7 +45339,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45235,7 +45355,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45251,7 +45371,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45267,7 +45387,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45283,7 +45403,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45299,7 +45419,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45315,7 +45435,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45331,7 +45451,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45347,7 +45467,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45363,7 +45483,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45379,7 +45499,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45395,7 +45515,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45411,7 +45531,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45427,7 +45547,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45443,7 +45563,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45459,7 +45579,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45475,7 +45595,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45491,7 +45611,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45507,7 +45627,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45523,7 +45643,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45539,7 +45659,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45555,7 +45675,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45571,7 +45691,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45587,7 +45707,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45603,7 +45723,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45619,7 +45739,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45635,7 +45755,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45651,7 +45771,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45667,7 +45787,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45683,7 +45803,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45699,7 +45819,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45715,7 +45835,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45731,7 +45851,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45747,7 +45867,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45763,7 +45883,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45779,7 +45899,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45795,7 +45915,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45811,7 +45931,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45827,7 +45947,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45843,7 +45963,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -45859,7 +45979,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="69">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="70">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -45875,7 +45995,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45891,7 +46011,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45907,7 +46027,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45923,7 +46043,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45939,7 +46059,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45955,7 +46075,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45971,7 +46091,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45987,7 +46107,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46003,7 +46123,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46019,7 +46139,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46035,7 +46155,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46051,7 +46171,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46067,7 +46187,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46083,7 +46203,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46099,7 +46219,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46115,7 +46235,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46131,7 +46251,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46147,7 +46267,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46163,7 +46283,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46179,7 +46299,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46195,7 +46315,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46211,7 +46331,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46227,7 +46347,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46243,7 +46363,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46259,7 +46379,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46275,7 +46395,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46291,7 +46411,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46307,7 +46427,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46323,7 +46443,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46339,7 +46459,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46355,7 +46475,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46371,7 +46491,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46387,7 +46507,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46403,7 +46523,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46419,7 +46539,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46435,7 +46555,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46451,7 +46571,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46467,7 +46587,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46483,7 +46603,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46499,7 +46619,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46515,7 +46635,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46531,7 +46651,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46547,7 +46667,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46563,7 +46683,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46579,7 +46699,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46595,7 +46715,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46611,7 +46731,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46627,7 +46747,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46643,7 +46763,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46659,7 +46779,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46675,7 +46795,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46691,7 +46811,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46707,7 +46827,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46723,7 +46843,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46739,7 +46859,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46755,7 +46875,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46771,7 +46891,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46787,7 +46907,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46803,7 +46923,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46819,7 +46939,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46835,7 +46955,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46851,7 +46971,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46867,7 +46987,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -46883,7 +47003,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="70">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="71">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -46899,7 +47019,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -51133,20 +51253,42 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A111" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B111" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C111" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D111" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E111" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F111" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G111" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H111" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I111" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J111" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K111" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L111" s="4">
+        <f t="shared" ref="L111" si="66">IF(COUNTA(B111:K111)=0,"",AVERAGE(B111:K111))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -51519,7 +51661,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="66">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="67">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -51536,7 +51678,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51553,7 +51695,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51570,7 +51712,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51587,7 +51729,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51604,7 +51746,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51621,7 +51763,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51638,7 +51780,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51655,7 +51797,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51672,7 +51814,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51689,7 +51831,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51706,7 +51848,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51723,7 +51865,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51740,7 +51882,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51757,7 +51899,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51774,7 +51916,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51791,7 +51933,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51808,7 +51950,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51825,7 +51967,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51842,7 +51984,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51859,7 +52001,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51876,7 +52018,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51893,7 +52035,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51910,7 +52052,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51927,7 +52069,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51944,7 +52086,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51961,7 +52103,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51978,7 +52120,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -51995,7 +52137,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52012,7 +52154,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52029,7 +52171,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52046,7 +52188,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52063,7 +52205,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52080,7 +52222,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52097,7 +52239,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52114,7 +52256,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52131,7 +52273,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52148,7 +52290,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52165,7 +52307,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52182,7 +52324,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52199,7 +52341,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52216,7 +52358,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52233,7 +52375,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52250,7 +52392,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52267,7 +52409,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52284,7 +52426,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52301,7 +52443,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52318,7 +52460,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52335,7 +52477,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52352,7 +52494,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52369,7 +52511,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52386,7 +52528,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52403,7 +52545,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52420,7 +52562,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52437,7 +52579,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52454,7 +52596,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52471,7 +52613,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52488,7 +52630,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52505,7 +52647,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52522,7 +52664,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52539,7 +52681,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52556,7 +52698,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52573,7 +52715,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52590,7 +52732,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -52607,7 +52749,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="67">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="68">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -52624,7 +52766,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52641,7 +52783,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52658,7 +52800,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52675,7 +52817,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52692,7 +52834,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52709,7 +52851,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52726,7 +52868,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52743,7 +52885,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52760,7 +52902,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52777,7 +52919,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52794,7 +52936,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52811,7 +52953,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52828,7 +52970,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52845,7 +52987,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52862,7 +53004,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52879,7 +53021,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52896,7 +53038,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52913,7 +53055,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52930,7 +53072,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52947,7 +53089,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52964,7 +53106,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52981,7 +53123,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52998,7 +53140,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53015,7 +53157,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53032,7 +53174,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53049,7 +53191,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53066,7 +53208,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53083,7 +53225,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53100,7 +53242,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53117,7 +53259,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53134,7 +53276,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53151,7 +53293,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53168,7 +53310,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53185,7 +53327,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53202,7 +53344,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53219,7 +53361,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53236,7 +53378,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53253,7 +53395,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53270,7 +53412,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53287,7 +53429,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53304,7 +53446,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53321,7 +53463,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53338,7 +53480,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53355,7 +53497,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53372,7 +53514,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53389,7 +53531,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53406,7 +53548,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53423,7 +53565,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53440,7 +53582,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53457,7 +53599,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53474,7 +53616,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53491,7 +53633,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53508,7 +53650,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53525,7 +53667,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53542,7 +53684,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53559,7 +53701,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53576,7 +53718,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53593,7 +53735,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53610,7 +53752,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53627,7 +53769,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53644,7 +53786,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53661,7 +53803,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53678,7 +53820,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -53695,7 +53837,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="68">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="69">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -53712,7 +53854,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53729,7 +53871,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53746,7 +53888,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53763,7 +53905,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53780,7 +53922,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53797,7 +53939,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53814,7 +53956,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53831,7 +53973,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53848,7 +53990,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53865,7 +54007,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53882,7 +54024,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53899,7 +54041,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53916,7 +54058,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53933,7 +54075,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53950,7 +54092,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53967,7 +54109,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53984,7 +54126,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54001,7 +54143,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54018,7 +54160,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54035,7 +54177,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54052,7 +54194,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54069,7 +54211,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54086,7 +54228,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54103,7 +54245,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54120,7 +54262,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54137,7 +54279,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54154,7 +54296,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54171,7 +54313,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54188,7 +54330,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54205,7 +54347,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54222,7 +54364,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54239,7 +54381,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54256,7 +54398,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54273,7 +54415,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54290,7 +54432,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54307,7 +54449,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54324,7 +54466,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54341,7 +54483,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54358,7 +54500,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54375,7 +54517,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54392,7 +54534,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54409,7 +54551,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54426,7 +54568,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54443,7 +54585,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54460,7 +54602,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54477,7 +54619,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54494,7 +54636,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54511,7 +54653,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54528,7 +54670,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54545,7 +54687,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54562,7 +54704,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54579,7 +54721,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54596,7 +54738,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54613,7 +54755,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54630,7 +54772,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54647,7 +54789,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54664,7 +54806,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54681,7 +54823,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54698,7 +54840,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54715,7 +54857,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54732,7 +54874,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54749,7 +54891,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54766,7 +54908,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -54783,7 +54925,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="69">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="70">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -54800,7 +54942,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54817,7 +54959,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54834,7 +54976,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54851,7 +54993,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54868,7 +55010,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54885,7 +55027,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54902,7 +55044,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54919,7 +55061,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54936,7 +55078,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54953,7 +55095,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54970,7 +55112,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54987,7 +55129,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55004,7 +55146,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55021,7 +55163,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55038,7 +55180,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55055,7 +55197,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55072,7 +55214,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55089,7 +55231,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55106,7 +55248,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55123,7 +55265,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55140,7 +55282,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55157,7 +55299,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55174,7 +55316,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55191,7 +55333,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55208,7 +55350,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55225,7 +55367,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55242,7 +55384,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55259,7 +55401,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55276,7 +55418,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55293,7 +55435,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55310,7 +55452,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55327,7 +55469,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55344,7 +55486,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55361,7 +55503,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55378,7 +55520,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55395,7 +55537,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55412,7 +55554,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55429,7 +55571,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55446,7 +55588,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55463,7 +55605,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55480,7 +55622,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55497,7 +55639,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55514,7 +55656,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55531,7 +55673,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55548,7 +55690,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55565,7 +55707,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55582,7 +55724,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55599,7 +55741,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55616,7 +55758,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55633,7 +55775,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55650,7 +55792,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55667,7 +55809,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55684,7 +55826,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55701,7 +55843,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55718,7 +55860,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55735,7 +55877,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55752,7 +55894,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55769,7 +55911,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55786,7 +55928,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55803,7 +55945,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55820,7 +55962,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55837,7 +55979,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55854,7 +55996,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -55871,7 +56013,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="70">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="71">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -55888,7 +56030,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173C487A-0A4C-4A1E-A6F0-A13DE070208E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B8AF76-BB9A-4937-948A-6D6BF12B6B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -664,6 +664,9 @@
                 <c:pt idx="106">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="107">
+                  <c:v>46282</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -995,7 +998,7 @@
                   <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0</c:v>
+                  <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>0</c:v>
@@ -2311,6 +2314,9 @@
                 <c:pt idx="106">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="107">
+                  <c:v>46282</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2642,7 +2648,7 @@
                   <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0</c:v>
+                  <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>0</c:v>
@@ -3958,6 +3964,9 @@
                 <c:pt idx="106">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="107">
+                  <c:v>46282</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4289,7 +4298,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>0</c:v>
@@ -5605,6 +5614,9 @@
                 <c:pt idx="106">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="107">
+                  <c:v>46282</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5936,7 +5948,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>0</c:v>
@@ -15792,33 +15804,81 @@
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="3"/>
-      <c r="O112" s="3"/>
-      <c r="P112" s="3"/>
-      <c r="Q112" s="3"/>
-      <c r="R112" s="3"/>
-      <c r="S112" s="3"/>
-      <c r="T112" s="3"/>
-      <c r="U112" s="3"/>
-      <c r="V112" s="3"/>
-      <c r="W112" s="3"/>
-      <c r="X112" s="3"/>
-      <c r="Y112" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A112" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B112" s="3">
+        <v>39</v>
+      </c>
+      <c r="C112" s="3">
+        <v>44</v>
+      </c>
+      <c r="D112" s="3">
+        <v>44</v>
+      </c>
+      <c r="E112" s="3">
+        <v>42</v>
+      </c>
+      <c r="F112" s="3">
+        <v>43</v>
+      </c>
+      <c r="G112" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H112" s="3">
+        <v>44</v>
+      </c>
+      <c r="I112" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J112" s="3">
+        <v>42</v>
+      </c>
+      <c r="K112" s="3">
+        <v>38</v>
+      </c>
+      <c r="L112" s="3">
+        <v>36</v>
+      </c>
+      <c r="M112" s="3">
+        <v>41</v>
+      </c>
+      <c r="N112" s="3">
+        <v>44</v>
+      </c>
+      <c r="O112" s="3">
+        <v>41.17</v>
+      </c>
+      <c r="P112" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q112" s="3">
+        <v>43</v>
+      </c>
+      <c r="R112" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S112" s="3">
+        <v>42</v>
+      </c>
+      <c r="T112" s="3">
+        <v>41</v>
+      </c>
+      <c r="U112" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="V112" s="3">
+        <v>38</v>
+      </c>
+      <c r="W112" s="3">
+        <v>45</v>
+      </c>
+      <c r="X112" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y112" s="4">
+        <f t="shared" ref="Y112" si="59">IF(COUNTA(B112:X112)=0,"",AVERAGE(B112:X112))</f>
+        <v>41.322608695652171</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.25">
@@ -16447,7 +16507,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="59">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="60">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16477,7 +16537,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16507,7 +16567,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16537,7 +16597,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16567,7 +16627,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16597,7 +16657,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16627,7 +16687,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="60">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="61">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="61">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="62">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="62">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="63">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="63">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="64">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -31364,29 +31424,69 @@
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="3"/>
-      <c r="O112" s="3"/>
-      <c r="P112" s="3"/>
-      <c r="Q112" s="3"/>
-      <c r="R112" s="3"/>
-      <c r="S112" s="3"/>
-      <c r="T112" s="3"/>
-      <c r="U112" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A112" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B112" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C112" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D112" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E112" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F112" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G112" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H112" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I112" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J112" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K112" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="L112" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M112" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N112" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O112" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P112" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q112" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R112" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S112" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T112" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U112" s="4">
+        <f t="shared" ref="U112" si="67">IF(COUNTA(B112:T112)=0,"",AVERAGE(B112:T112))</f>
+        <v>3.4747368421052629</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -31931,7 +32031,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="67">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="68">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -31957,7 +32057,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -31983,7 +32083,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32009,7 +32109,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32035,7 +32135,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32061,7 +32161,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32087,7 +32187,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32113,7 +32213,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32139,7 +32239,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32165,7 +32265,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32191,7 +32291,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32217,7 +32317,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32243,7 +32343,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32269,7 +32369,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32295,7 +32395,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32321,7 +32421,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32347,7 +32447,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32373,7 +32473,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32399,7 +32499,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32425,7 +32525,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32451,7 +32551,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32477,7 +32577,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32503,7 +32603,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32529,7 +32629,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32555,7 +32655,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32581,7 +32681,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32607,7 +32707,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32633,7 +32733,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32659,7 +32759,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32685,7 +32785,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32711,7 +32811,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32737,7 +32837,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32763,7 +32863,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32789,7 +32889,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32815,7 +32915,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32841,7 +32941,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32867,7 +32967,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32893,7 +32993,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32919,7 +33019,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32945,7 +33045,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32971,7 +33071,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -32997,7 +33097,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33023,7 +33123,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33049,7 +33149,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33075,7 +33175,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33101,7 +33201,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33127,7 +33227,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33153,7 +33253,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33179,7 +33279,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33205,7 +33305,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33231,7 +33331,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33257,7 +33357,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33283,7 +33383,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33309,7 +33409,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33335,7 +33435,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33361,7 +33461,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33387,7 +33487,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33413,7 +33513,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33439,7 +33539,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33465,7 +33565,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33491,7 +33591,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33517,7 +33617,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33543,7 +33643,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33569,7 +33669,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -33595,7 +33695,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="68">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="69">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -33621,7 +33721,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33647,7 +33747,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33673,7 +33773,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33699,7 +33799,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33725,7 +33825,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33751,7 +33851,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33777,7 +33877,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33803,7 +33903,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33829,7 +33929,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33855,7 +33955,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33881,7 +33981,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33907,7 +34007,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33933,7 +34033,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33959,7 +34059,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33985,7 +34085,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34011,7 +34111,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34037,7 +34137,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34063,7 +34163,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34089,7 +34189,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34115,7 +34215,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34141,7 +34241,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34167,7 +34267,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34193,7 +34293,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34219,7 +34319,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34245,7 +34345,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34271,7 +34371,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34297,7 +34397,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34323,7 +34423,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34349,7 +34449,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34375,7 +34475,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34401,7 +34501,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34427,7 +34527,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34453,7 +34553,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34479,7 +34579,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34505,7 +34605,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34531,7 +34631,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34557,7 +34657,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34583,7 +34683,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34609,7 +34709,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34635,7 +34735,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34661,7 +34761,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34687,7 +34787,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34713,7 +34813,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34739,7 +34839,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34765,7 +34865,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34791,7 +34891,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34817,7 +34917,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34843,7 +34943,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34869,7 +34969,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34895,7 +34995,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34921,7 +35021,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34947,7 +35047,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34973,7 +35073,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -34999,7 +35099,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35025,7 +35125,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35051,7 +35151,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35077,7 +35177,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35103,7 +35203,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35129,7 +35229,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35155,7 +35255,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35181,7 +35281,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35207,7 +35307,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35233,7 +35333,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -35259,7 +35359,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="69">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="70">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35285,7 +35385,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35311,7 +35411,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35337,7 +35437,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35363,7 +35463,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35389,7 +35489,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35415,7 +35515,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35441,7 +35541,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35467,7 +35567,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35493,7 +35593,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35519,7 +35619,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35545,7 +35645,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35571,7 +35671,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35597,7 +35697,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35623,7 +35723,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35649,7 +35749,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35675,7 +35775,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35701,7 +35801,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35727,7 +35827,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35753,7 +35853,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35779,7 +35879,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35805,7 +35905,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35831,7 +35931,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35857,7 +35957,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35883,7 +35983,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35909,7 +36009,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35935,7 +36035,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35961,7 +36061,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35987,7 +36087,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36013,7 +36113,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36039,7 +36139,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36065,7 +36165,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36091,7 +36191,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36117,7 +36217,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36143,7 +36243,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36169,7 +36269,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36195,7 +36295,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36221,7 +36321,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36247,7 +36347,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36273,7 +36373,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36299,7 +36399,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36325,7 +36425,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36351,7 +36451,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36377,7 +36477,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36403,7 +36503,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36429,7 +36529,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36455,7 +36555,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36481,7 +36581,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36507,7 +36607,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36533,7 +36633,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36559,7 +36659,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36585,7 +36685,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36611,7 +36711,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36637,7 +36737,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36663,7 +36763,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36689,7 +36789,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36715,7 +36815,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36741,7 +36841,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36767,7 +36867,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36793,7 +36893,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36819,7 +36919,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36845,7 +36945,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36871,7 +36971,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36897,7 +36997,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -36923,7 +37023,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="70">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="71">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -36949,7 +37049,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36975,7 +37075,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37001,7 +37101,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37027,7 +37127,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37053,7 +37153,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37079,7 +37179,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37105,7 +37205,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37131,7 +37231,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37157,7 +37257,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37183,7 +37283,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37209,7 +37309,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37235,7 +37335,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37261,7 +37361,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37287,7 +37387,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37313,7 +37413,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37339,7 +37439,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37365,7 +37465,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37391,7 +37491,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37417,7 +37517,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37443,7 +37543,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37469,7 +37569,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37495,7 +37595,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37521,7 +37621,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37547,7 +37647,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37573,7 +37673,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37599,7 +37699,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37625,7 +37725,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37651,7 +37751,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37677,7 +37777,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37703,7 +37803,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37729,7 +37829,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37755,7 +37855,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37781,7 +37881,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37807,7 +37907,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37833,7 +37933,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37859,7 +37959,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37885,7 +37985,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37911,7 +38011,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37937,7 +38037,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37963,7 +38063,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37989,7 +38089,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38015,7 +38115,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38041,7 +38141,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38067,7 +38167,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38093,7 +38193,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38119,7 +38219,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38145,7 +38245,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38171,7 +38271,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38197,7 +38297,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38223,7 +38323,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38249,7 +38349,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38275,7 +38375,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38301,7 +38401,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38327,7 +38427,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38353,7 +38453,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38379,7 +38479,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38405,7 +38505,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38431,7 +38531,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38457,7 +38557,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38483,7 +38583,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38509,7 +38609,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38535,7 +38635,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38561,7 +38661,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -38587,7 +38687,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="71">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="72">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -38613,7 +38713,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -42560,19 +42660,39 @@
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A112" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B112" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C112" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D112" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E112" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F112" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G112" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H112" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I112" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J112" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K112" s="4">
+        <f t="shared" ref="K112" si="67">IF(COUNTA(B112:J112)=0,"",AVERAGE(B112:J112))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -42907,7 +43027,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="67">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="68">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -42923,7 +43043,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -42939,7 +43059,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -42955,7 +43075,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -42971,7 +43091,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -42987,7 +43107,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43003,7 +43123,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43019,7 +43139,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43035,7 +43155,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43051,7 +43171,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43067,7 +43187,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43083,7 +43203,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43099,7 +43219,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43115,7 +43235,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43131,7 +43251,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43147,7 +43267,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43163,7 +43283,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43179,7 +43299,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43195,7 +43315,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43211,7 +43331,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43227,7 +43347,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43243,7 +43363,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43259,7 +43379,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43275,7 +43395,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43291,7 +43411,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43307,7 +43427,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43323,7 +43443,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43339,7 +43459,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43355,7 +43475,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43371,7 +43491,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43387,7 +43507,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43403,7 +43523,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43419,7 +43539,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43435,7 +43555,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43451,7 +43571,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43467,7 +43587,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43483,7 +43603,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43499,7 +43619,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43515,7 +43635,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43531,7 +43651,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43547,7 +43667,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43563,7 +43683,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43579,7 +43699,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43595,7 +43715,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43611,7 +43731,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43627,7 +43747,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43643,7 +43763,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43659,7 +43779,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43675,7 +43795,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43691,7 +43811,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43707,7 +43827,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43723,7 +43843,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43739,7 +43859,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43755,7 +43875,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43771,7 +43891,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43787,7 +43907,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43803,7 +43923,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43819,7 +43939,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43835,7 +43955,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43851,7 +43971,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43867,7 +43987,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43883,7 +44003,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43899,7 +44019,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43915,7 +44035,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -43931,7 +44051,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="68">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="69">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -43947,7 +44067,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43963,7 +44083,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43979,7 +44099,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43995,7 +44115,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44011,7 +44131,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44027,7 +44147,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44043,7 +44163,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44059,7 +44179,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44075,7 +44195,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44091,7 +44211,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44107,7 +44227,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44123,7 +44243,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44139,7 +44259,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44155,7 +44275,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44171,7 +44291,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44187,7 +44307,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44203,7 +44323,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44219,7 +44339,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44235,7 +44355,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44251,7 +44371,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44267,7 +44387,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44283,7 +44403,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44299,7 +44419,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44315,7 +44435,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44331,7 +44451,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44347,7 +44467,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44363,7 +44483,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44379,7 +44499,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44395,7 +44515,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44411,7 +44531,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44427,7 +44547,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44443,7 +44563,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44459,7 +44579,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44475,7 +44595,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44491,7 +44611,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44507,7 +44627,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44523,7 +44643,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44539,7 +44659,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44555,7 +44675,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44571,7 +44691,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44587,7 +44707,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44603,7 +44723,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44619,7 +44739,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44635,7 +44755,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44651,7 +44771,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44667,7 +44787,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44683,7 +44803,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44699,7 +44819,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44715,7 +44835,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44731,7 +44851,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44747,7 +44867,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44763,7 +44883,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44779,7 +44899,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44795,7 +44915,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44811,7 +44931,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44827,7 +44947,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44843,7 +44963,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44859,7 +44979,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44875,7 +44995,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44891,7 +45011,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44907,7 +45027,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44923,7 +45043,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44939,7 +45059,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44955,7 +45075,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="69">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="70">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -44971,7 +45091,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44987,7 +45107,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45003,7 +45123,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45019,7 +45139,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45035,7 +45155,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45051,7 +45171,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45067,7 +45187,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45083,7 +45203,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45099,7 +45219,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45115,7 +45235,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45131,7 +45251,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45147,7 +45267,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45163,7 +45283,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45179,7 +45299,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45195,7 +45315,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45211,7 +45331,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45227,7 +45347,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45243,7 +45363,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45259,7 +45379,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45275,7 +45395,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45291,7 +45411,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45307,7 +45427,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45323,7 +45443,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45339,7 +45459,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45355,7 +45475,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45371,7 +45491,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45387,7 +45507,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45403,7 +45523,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45419,7 +45539,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45435,7 +45555,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45451,7 +45571,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45467,7 +45587,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45483,7 +45603,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45499,7 +45619,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45515,7 +45635,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45531,7 +45651,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45547,7 +45667,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45563,7 +45683,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45579,7 +45699,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45595,7 +45715,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45611,7 +45731,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45627,7 +45747,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45643,7 +45763,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45659,7 +45779,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45675,7 +45795,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45691,7 +45811,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45707,7 +45827,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45723,7 +45843,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45739,7 +45859,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45755,7 +45875,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45771,7 +45891,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45787,7 +45907,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45803,7 +45923,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45819,7 +45939,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45835,7 +45955,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45851,7 +45971,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45867,7 +45987,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45883,7 +46003,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45899,7 +46019,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45915,7 +46035,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45931,7 +46051,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45947,7 +46067,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45963,7 +46083,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45979,7 +46099,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="70">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="71">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -45995,7 +46115,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46011,7 +46131,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46027,7 +46147,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46043,7 +46163,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46059,7 +46179,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46075,7 +46195,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46091,7 +46211,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46107,7 +46227,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46123,7 +46243,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46139,7 +46259,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46155,7 +46275,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46171,7 +46291,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46187,7 +46307,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46203,7 +46323,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46219,7 +46339,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46235,7 +46355,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46251,7 +46371,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46267,7 +46387,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46283,7 +46403,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46299,7 +46419,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46315,7 +46435,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46331,7 +46451,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46347,7 +46467,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46363,7 +46483,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46379,7 +46499,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46395,7 +46515,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46411,7 +46531,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46427,7 +46547,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46443,7 +46563,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46459,7 +46579,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46475,7 +46595,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46491,7 +46611,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46507,7 +46627,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46523,7 +46643,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46539,7 +46659,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46555,7 +46675,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46571,7 +46691,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46587,7 +46707,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46603,7 +46723,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46619,7 +46739,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46635,7 +46755,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46651,7 +46771,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46667,7 +46787,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46683,7 +46803,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46699,7 +46819,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46715,7 +46835,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46731,7 +46851,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46747,7 +46867,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46763,7 +46883,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46779,7 +46899,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46795,7 +46915,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46811,7 +46931,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46827,7 +46947,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46843,7 +46963,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46859,7 +46979,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46875,7 +46995,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46891,7 +47011,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46907,7 +47027,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46923,7 +47043,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46939,7 +47059,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46955,7 +47075,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46971,7 +47091,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46987,7 +47107,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -47003,7 +47123,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="71">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="72">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -47019,7 +47139,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -51292,20 +51412,42 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A112" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B112" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C112" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D112" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E112" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F112" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G112" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H112" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I112" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J112" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K112" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L112" s="4">
+        <f t="shared" ref="L112" si="67">IF(COUNTA(B112:K112)=0,"",AVERAGE(B112:K112))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -51661,7 +51803,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="67">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="68">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -51678,7 +51820,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51695,7 +51837,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51712,7 +51854,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51729,7 +51871,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51746,7 +51888,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51763,7 +51905,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51780,7 +51922,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51797,7 +51939,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51814,7 +51956,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51831,7 +51973,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51848,7 +51990,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51865,7 +52007,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51882,7 +52024,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51899,7 +52041,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51916,7 +52058,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51933,7 +52075,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51950,7 +52092,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51967,7 +52109,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -51984,7 +52126,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52001,7 +52143,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52018,7 +52160,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52035,7 +52177,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52052,7 +52194,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52069,7 +52211,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52086,7 +52228,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52103,7 +52245,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52120,7 +52262,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52137,7 +52279,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52154,7 +52296,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52171,7 +52313,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52188,7 +52330,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52205,7 +52347,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52222,7 +52364,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52239,7 +52381,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52256,7 +52398,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52273,7 +52415,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52290,7 +52432,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52307,7 +52449,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52324,7 +52466,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52341,7 +52483,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52358,7 +52500,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52375,7 +52517,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52392,7 +52534,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52409,7 +52551,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52426,7 +52568,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52443,7 +52585,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52460,7 +52602,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52477,7 +52619,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52494,7 +52636,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52511,7 +52653,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52528,7 +52670,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52545,7 +52687,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52562,7 +52704,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52579,7 +52721,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52596,7 +52738,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52613,7 +52755,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52630,7 +52772,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52647,7 +52789,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52664,7 +52806,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52681,7 +52823,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52698,7 +52840,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52715,7 +52857,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52732,7 +52874,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -52749,7 +52891,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="68">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="69">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -52766,7 +52908,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52783,7 +52925,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52800,7 +52942,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52817,7 +52959,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52834,7 +52976,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52851,7 +52993,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52868,7 +53010,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52885,7 +53027,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52902,7 +53044,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52919,7 +53061,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52936,7 +53078,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52953,7 +53095,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52970,7 +53112,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52987,7 +53129,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53004,7 +53146,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53021,7 +53163,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53038,7 +53180,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53055,7 +53197,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53072,7 +53214,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53089,7 +53231,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53106,7 +53248,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53123,7 +53265,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53140,7 +53282,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53157,7 +53299,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53174,7 +53316,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53191,7 +53333,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53208,7 +53350,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53225,7 +53367,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53242,7 +53384,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53259,7 +53401,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53276,7 +53418,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53293,7 +53435,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53310,7 +53452,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53327,7 +53469,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53344,7 +53486,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53361,7 +53503,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53378,7 +53520,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53395,7 +53537,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53412,7 +53554,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53429,7 +53571,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53446,7 +53588,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53463,7 +53605,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53480,7 +53622,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53497,7 +53639,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53514,7 +53656,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53531,7 +53673,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53548,7 +53690,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53565,7 +53707,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53582,7 +53724,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53599,7 +53741,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53616,7 +53758,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53633,7 +53775,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53650,7 +53792,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53667,7 +53809,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53684,7 +53826,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53701,7 +53843,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53718,7 +53860,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53735,7 +53877,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53752,7 +53894,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53769,7 +53911,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53786,7 +53928,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53803,7 +53945,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53820,7 +53962,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -53837,7 +53979,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="69">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="70">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -53854,7 +53996,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53871,7 +54013,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53888,7 +54030,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53905,7 +54047,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53922,7 +54064,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53939,7 +54081,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53956,7 +54098,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53973,7 +54115,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53990,7 +54132,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54007,7 +54149,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54024,7 +54166,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54041,7 +54183,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54058,7 +54200,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54075,7 +54217,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54092,7 +54234,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54109,7 +54251,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54126,7 +54268,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54143,7 +54285,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54160,7 +54302,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54177,7 +54319,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54194,7 +54336,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54211,7 +54353,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54228,7 +54370,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54245,7 +54387,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54262,7 +54404,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54279,7 +54421,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54296,7 +54438,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54313,7 +54455,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54330,7 +54472,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54347,7 +54489,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54364,7 +54506,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54381,7 +54523,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54398,7 +54540,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54415,7 +54557,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54432,7 +54574,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54449,7 +54591,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54466,7 +54608,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54483,7 +54625,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54500,7 +54642,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54517,7 +54659,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54534,7 +54676,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54551,7 +54693,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54568,7 +54710,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54585,7 +54727,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54602,7 +54744,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54619,7 +54761,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54636,7 +54778,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54653,7 +54795,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54670,7 +54812,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54687,7 +54829,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54704,7 +54846,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54721,7 +54863,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54738,7 +54880,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54755,7 +54897,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54772,7 +54914,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54789,7 +54931,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54806,7 +54948,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54823,7 +54965,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54840,7 +54982,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54857,7 +54999,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54874,7 +55016,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54891,7 +55033,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54908,7 +55050,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -54925,7 +55067,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="70">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="71">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -54942,7 +55084,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54959,7 +55101,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54976,7 +55118,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54993,7 +55135,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55010,7 +55152,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55027,7 +55169,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55044,7 +55186,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55061,7 +55203,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55078,7 +55220,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55095,7 +55237,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55112,7 +55254,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55129,7 +55271,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55146,7 +55288,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55163,7 +55305,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55180,7 +55322,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55197,7 +55339,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55214,7 +55356,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55231,7 +55373,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55248,7 +55390,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55265,7 +55407,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55282,7 +55424,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55299,7 +55441,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55316,7 +55458,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55333,7 +55475,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55350,7 +55492,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55367,7 +55509,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55384,7 +55526,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55401,7 +55543,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55418,7 +55560,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55435,7 +55577,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55452,7 +55594,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55469,7 +55611,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55486,7 +55628,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55503,7 +55645,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55520,7 +55662,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55537,7 +55679,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55554,7 +55696,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55571,7 +55713,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55588,7 +55730,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55605,7 +55747,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55622,7 +55764,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55639,7 +55781,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55656,7 +55798,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55673,7 +55815,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55690,7 +55832,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55707,7 +55849,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55724,7 +55866,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55741,7 +55883,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55758,7 +55900,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55775,7 +55917,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55792,7 +55934,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55809,7 +55951,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55826,7 +55968,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55843,7 +55985,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55860,7 +56002,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55877,7 +56019,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55894,7 +56036,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55911,7 +56053,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55928,7 +56070,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55945,7 +56087,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55962,7 +56104,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55979,7 +56121,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55996,7 +56138,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -56013,7 +56155,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="71">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="72">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -56030,7 +56172,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B8AF76-BB9A-4937-948A-6D6BF12B6B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202BA8EA-F68C-4CB7-9B9F-80275C32E311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,6 +667,9 @@
                 <c:pt idx="107">
                   <c:v>46282</c:v>
                 </c:pt>
+                <c:pt idx="108">
+                  <c:v>46283</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1001,7 +1004,7 @@
                   <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0</c:v>
+                  <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>0</c:v>
@@ -2317,6 +2320,9 @@
                 <c:pt idx="107">
                   <c:v>46282</c:v>
                 </c:pt>
+                <c:pt idx="108">
+                  <c:v>46283</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2651,7 +2657,7 @@
                   <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0</c:v>
+                  <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>0</c:v>
@@ -3967,6 +3973,9 @@
                 <c:pt idx="107">
                   <c:v>46282</c:v>
                 </c:pt>
+                <c:pt idx="108">
+                  <c:v>46283</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4301,7 +4310,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>0</c:v>
@@ -5617,6 +5626,9 @@
                 <c:pt idx="107">
                   <c:v>46282</c:v>
                 </c:pt>
+                <c:pt idx="108">
+                  <c:v>46283</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5951,7 +5963,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>0</c:v>
@@ -15882,33 +15894,81 @@
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3"/>
-      <c r="O113" s="3"/>
-      <c r="P113" s="3"/>
-      <c r="Q113" s="3"/>
-      <c r="R113" s="3"/>
-      <c r="S113" s="3"/>
-      <c r="T113" s="3"/>
-      <c r="U113" s="3"/>
-      <c r="V113" s="3"/>
-      <c r="W113" s="3"/>
-      <c r="X113" s="3"/>
-      <c r="Y113" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A113" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B113" s="3">
+        <v>39</v>
+      </c>
+      <c r="C113" s="3">
+        <v>44</v>
+      </c>
+      <c r="D113" s="3">
+        <v>44</v>
+      </c>
+      <c r="E113" s="3">
+        <v>42</v>
+      </c>
+      <c r="F113" s="3">
+        <v>43</v>
+      </c>
+      <c r="G113" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H113" s="3">
+        <v>44</v>
+      </c>
+      <c r="I113" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J113" s="3">
+        <v>42</v>
+      </c>
+      <c r="K113" s="3">
+        <v>38</v>
+      </c>
+      <c r="L113" s="3">
+        <v>36</v>
+      </c>
+      <c r="M113" s="3">
+        <v>41</v>
+      </c>
+      <c r="N113" s="3">
+        <v>44</v>
+      </c>
+      <c r="O113" s="3">
+        <v>41.17</v>
+      </c>
+      <c r="P113" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q113" s="3">
+        <v>43</v>
+      </c>
+      <c r="R113" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S113" s="3">
+        <v>42</v>
+      </c>
+      <c r="T113" s="3">
+        <v>41</v>
+      </c>
+      <c r="U113" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="V113" s="3">
+        <v>38</v>
+      </c>
+      <c r="W113" s="3">
+        <v>45</v>
+      </c>
+      <c r="X113" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y113" s="4">
+        <f t="shared" ref="Y113" si="60">IF(COUNTA(B113:X113)=0,"",AVERAGE(B113:X113))</f>
+        <v>41.322608695652171</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.25">
@@ -16507,7 +16567,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="60">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="61">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16537,7 +16597,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16567,7 +16627,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16597,7 +16657,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16627,7 +16687,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="61">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="62">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="62">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="63">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="63">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="64">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -24187,7 +24247,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="64">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="65">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24217,7 +24277,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -31490,29 +31550,69 @@
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3"/>
-      <c r="O113" s="3"/>
-      <c r="P113" s="3"/>
-      <c r="Q113" s="3"/>
-      <c r="R113" s="3"/>
-      <c r="S113" s="3"/>
-      <c r="T113" s="3"/>
-      <c r="U113" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A113" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B113" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C113" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D113" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E113" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F113" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G113" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H113" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I113" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J113" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K113" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="L113" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M113" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N113" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O113" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P113" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q113" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R113" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S113" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T113" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U113" s="4">
+        <f t="shared" ref="U113" si="68">IF(COUNTA(B113:T113)=0,"",AVERAGE(B113:T113))</f>
+        <v>3.4747368421052629</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -32031,7 +32131,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="68">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="69">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -32057,7 +32157,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32083,7 +32183,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32109,7 +32209,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32135,7 +32235,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32161,7 +32261,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32187,7 +32287,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32213,7 +32313,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32239,7 +32339,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32265,7 +32365,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32291,7 +32391,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32317,7 +32417,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32343,7 +32443,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32369,7 +32469,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32395,7 +32495,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32421,7 +32521,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32447,7 +32547,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32473,7 +32573,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32499,7 +32599,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32525,7 +32625,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32551,7 +32651,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32577,7 +32677,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32603,7 +32703,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32629,7 +32729,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32655,7 +32755,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32681,7 +32781,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32707,7 +32807,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32733,7 +32833,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32759,7 +32859,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32785,7 +32885,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32811,7 +32911,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32837,7 +32937,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32863,7 +32963,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32889,7 +32989,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32915,7 +33015,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32941,7 +33041,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32967,7 +33067,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32993,7 +33093,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33019,7 +33119,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33045,7 +33145,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33071,7 +33171,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33097,7 +33197,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33123,7 +33223,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33149,7 +33249,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33175,7 +33275,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33201,7 +33301,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33227,7 +33327,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33253,7 +33353,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33279,7 +33379,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33305,7 +33405,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33331,7 +33431,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33357,7 +33457,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33383,7 +33483,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33409,7 +33509,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33435,7 +33535,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33461,7 +33561,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33487,7 +33587,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33513,7 +33613,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33539,7 +33639,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33565,7 +33665,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33591,7 +33691,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33617,7 +33717,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33643,7 +33743,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33669,7 +33769,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -33695,7 +33795,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="69">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="70">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -33721,7 +33821,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33747,7 +33847,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33773,7 +33873,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33799,7 +33899,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33825,7 +33925,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33851,7 +33951,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33877,7 +33977,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33903,7 +34003,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33929,7 +34029,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33955,7 +34055,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33981,7 +34081,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34007,7 +34107,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34033,7 +34133,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34059,7 +34159,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34085,7 +34185,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34111,7 +34211,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34137,7 +34237,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34163,7 +34263,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34189,7 +34289,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34215,7 +34315,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34241,7 +34341,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34267,7 +34367,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34293,7 +34393,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34319,7 +34419,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34345,7 +34445,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34371,7 +34471,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34397,7 +34497,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34423,7 +34523,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34449,7 +34549,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34475,7 +34575,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34501,7 +34601,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34527,7 +34627,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34553,7 +34653,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34579,7 +34679,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34605,7 +34705,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34631,7 +34731,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34657,7 +34757,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34683,7 +34783,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34709,7 +34809,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34735,7 +34835,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34761,7 +34861,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34787,7 +34887,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34813,7 +34913,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34839,7 +34939,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34865,7 +34965,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34891,7 +34991,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34917,7 +35017,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34943,7 +35043,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34969,7 +35069,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -34995,7 +35095,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35021,7 +35121,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35047,7 +35147,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35073,7 +35173,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35099,7 +35199,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35125,7 +35225,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35151,7 +35251,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35177,7 +35277,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35203,7 +35303,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35229,7 +35329,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35255,7 +35355,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35281,7 +35381,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35307,7 +35407,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35333,7 +35433,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -35359,7 +35459,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="70">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="71">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35385,7 +35485,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35411,7 +35511,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35437,7 +35537,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35463,7 +35563,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35489,7 +35589,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35515,7 +35615,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35541,7 +35641,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35567,7 +35667,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35593,7 +35693,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35619,7 +35719,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35645,7 +35745,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35671,7 +35771,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35697,7 +35797,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35723,7 +35823,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35749,7 +35849,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35775,7 +35875,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35801,7 +35901,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35827,7 +35927,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35853,7 +35953,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35879,7 +35979,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35905,7 +36005,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35931,7 +36031,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35957,7 +36057,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35983,7 +36083,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36009,7 +36109,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36035,7 +36135,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36061,7 +36161,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36087,7 +36187,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36113,7 +36213,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36139,7 +36239,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36165,7 +36265,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36191,7 +36291,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36217,7 +36317,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36243,7 +36343,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36269,7 +36369,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36295,7 +36395,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36321,7 +36421,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36347,7 +36447,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36373,7 +36473,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36399,7 +36499,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36425,7 +36525,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36451,7 +36551,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36477,7 +36577,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36503,7 +36603,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36529,7 +36629,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36555,7 +36655,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36581,7 +36681,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36607,7 +36707,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36633,7 +36733,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36659,7 +36759,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36685,7 +36785,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36711,7 +36811,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36737,7 +36837,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36763,7 +36863,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36789,7 +36889,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36815,7 +36915,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36841,7 +36941,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36867,7 +36967,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36893,7 +36993,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36919,7 +37019,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36945,7 +37045,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36971,7 +37071,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -36997,7 +37097,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -37023,7 +37123,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="71">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="72">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -37049,7 +37149,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37075,7 +37175,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37101,7 +37201,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37127,7 +37227,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37153,7 +37253,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37179,7 +37279,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37205,7 +37305,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37231,7 +37331,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37257,7 +37357,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37283,7 +37383,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37309,7 +37409,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37335,7 +37435,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37361,7 +37461,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37387,7 +37487,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37413,7 +37513,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37439,7 +37539,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37465,7 +37565,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37491,7 +37591,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37517,7 +37617,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37543,7 +37643,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37569,7 +37669,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37595,7 +37695,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37621,7 +37721,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37647,7 +37747,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37673,7 +37773,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37699,7 +37799,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37725,7 +37825,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37751,7 +37851,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37777,7 +37877,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37803,7 +37903,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37829,7 +37929,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37855,7 +37955,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37881,7 +37981,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37907,7 +38007,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37933,7 +38033,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37959,7 +38059,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37985,7 +38085,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38011,7 +38111,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38037,7 +38137,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38063,7 +38163,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38089,7 +38189,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38115,7 +38215,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38141,7 +38241,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38167,7 +38267,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38193,7 +38293,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38219,7 +38319,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38245,7 +38345,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38271,7 +38371,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38297,7 +38397,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38323,7 +38423,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38349,7 +38449,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38375,7 +38475,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38401,7 +38501,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38427,7 +38527,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38453,7 +38553,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38479,7 +38579,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38505,7 +38605,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38531,7 +38631,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38557,7 +38657,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38583,7 +38683,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38609,7 +38709,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38635,7 +38735,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38661,7 +38761,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -38687,7 +38787,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="72">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="73">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -38713,7 +38813,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -42696,19 +42796,39 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A113" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B113" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C113" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D113" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E113" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F113" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G113" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H113" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I113" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J113" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K113" s="4">
+        <f t="shared" ref="K113" si="68">IF(COUNTA(B113:J113)=0,"",AVERAGE(B113:J113))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -43027,7 +43147,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="68">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="69">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -43043,7 +43163,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43059,7 +43179,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43075,7 +43195,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43091,7 +43211,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43107,7 +43227,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43123,7 +43243,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43139,7 +43259,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43155,7 +43275,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43171,7 +43291,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43187,7 +43307,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43203,7 +43323,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43219,7 +43339,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43235,7 +43355,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43251,7 +43371,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43267,7 +43387,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43283,7 +43403,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43299,7 +43419,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43315,7 +43435,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43331,7 +43451,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43347,7 +43467,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43363,7 +43483,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43379,7 +43499,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43395,7 +43515,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43411,7 +43531,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43427,7 +43547,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43443,7 +43563,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43459,7 +43579,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43475,7 +43595,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43491,7 +43611,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43507,7 +43627,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43523,7 +43643,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43539,7 +43659,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43555,7 +43675,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43571,7 +43691,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43587,7 +43707,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43603,7 +43723,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43619,7 +43739,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43635,7 +43755,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43651,7 +43771,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43667,7 +43787,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43683,7 +43803,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43699,7 +43819,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43715,7 +43835,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43731,7 +43851,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43747,7 +43867,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43763,7 +43883,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43779,7 +43899,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43795,7 +43915,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43811,7 +43931,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43827,7 +43947,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43843,7 +43963,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43859,7 +43979,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43875,7 +43995,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43891,7 +44011,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43907,7 +44027,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43923,7 +44043,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43939,7 +44059,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43955,7 +44075,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43971,7 +44091,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -43987,7 +44107,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44003,7 +44123,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44019,7 +44139,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44035,7 +44155,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -44051,7 +44171,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="69">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="70">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -44067,7 +44187,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44083,7 +44203,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44099,7 +44219,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44115,7 +44235,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44131,7 +44251,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44147,7 +44267,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44163,7 +44283,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44179,7 +44299,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44195,7 +44315,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44211,7 +44331,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44227,7 +44347,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44243,7 +44363,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44259,7 +44379,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44275,7 +44395,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44291,7 +44411,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44307,7 +44427,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44323,7 +44443,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44339,7 +44459,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44355,7 +44475,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44371,7 +44491,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44387,7 +44507,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44403,7 +44523,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44419,7 +44539,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44435,7 +44555,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44451,7 +44571,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44467,7 +44587,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44483,7 +44603,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44499,7 +44619,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44515,7 +44635,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44531,7 +44651,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44547,7 +44667,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44563,7 +44683,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44579,7 +44699,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44595,7 +44715,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44611,7 +44731,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44627,7 +44747,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44643,7 +44763,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44659,7 +44779,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44675,7 +44795,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44691,7 +44811,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44707,7 +44827,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44723,7 +44843,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44739,7 +44859,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44755,7 +44875,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44771,7 +44891,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44787,7 +44907,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44803,7 +44923,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44819,7 +44939,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44835,7 +44955,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44851,7 +44971,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44867,7 +44987,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44883,7 +45003,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44899,7 +45019,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44915,7 +45035,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44931,7 +45051,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44947,7 +45067,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44963,7 +45083,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44979,7 +45099,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44995,7 +45115,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45011,7 +45131,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45027,7 +45147,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45043,7 +45163,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45059,7 +45179,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -45075,7 +45195,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="70">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="71">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -45091,7 +45211,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45107,7 +45227,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45123,7 +45243,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45139,7 +45259,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45155,7 +45275,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45171,7 +45291,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45187,7 +45307,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45203,7 +45323,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45219,7 +45339,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45235,7 +45355,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45251,7 +45371,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45267,7 +45387,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45283,7 +45403,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45299,7 +45419,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45315,7 +45435,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45331,7 +45451,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45347,7 +45467,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45363,7 +45483,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45379,7 +45499,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45395,7 +45515,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45411,7 +45531,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45427,7 +45547,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45443,7 +45563,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45459,7 +45579,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45475,7 +45595,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45491,7 +45611,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45507,7 +45627,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45523,7 +45643,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45539,7 +45659,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45555,7 +45675,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45571,7 +45691,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45587,7 +45707,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45603,7 +45723,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45619,7 +45739,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45635,7 +45755,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45651,7 +45771,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45667,7 +45787,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45683,7 +45803,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45699,7 +45819,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45715,7 +45835,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45731,7 +45851,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45747,7 +45867,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45763,7 +45883,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45779,7 +45899,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45795,7 +45915,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45811,7 +45931,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45827,7 +45947,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45843,7 +45963,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45859,7 +45979,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45875,7 +45995,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45891,7 +46011,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45907,7 +46027,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45923,7 +46043,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45939,7 +46059,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45955,7 +46075,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45971,7 +46091,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45987,7 +46107,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46003,7 +46123,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46019,7 +46139,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46035,7 +46155,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46051,7 +46171,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46067,7 +46187,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46083,7 +46203,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -46099,7 +46219,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="71">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="72">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -46115,7 +46235,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46131,7 +46251,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46147,7 +46267,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46163,7 +46283,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46179,7 +46299,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46195,7 +46315,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46211,7 +46331,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46227,7 +46347,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46243,7 +46363,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46259,7 +46379,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46275,7 +46395,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46291,7 +46411,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46307,7 +46427,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46323,7 +46443,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46339,7 +46459,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46355,7 +46475,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46371,7 +46491,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46387,7 +46507,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46403,7 +46523,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46419,7 +46539,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46435,7 +46555,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46451,7 +46571,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46467,7 +46587,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46483,7 +46603,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46499,7 +46619,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46515,7 +46635,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46531,7 +46651,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46547,7 +46667,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46563,7 +46683,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46579,7 +46699,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46595,7 +46715,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46611,7 +46731,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46627,7 +46747,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46643,7 +46763,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46659,7 +46779,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46675,7 +46795,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46691,7 +46811,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46707,7 +46827,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46723,7 +46843,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46739,7 +46859,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46755,7 +46875,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46771,7 +46891,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46787,7 +46907,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46803,7 +46923,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46819,7 +46939,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46835,7 +46955,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46851,7 +46971,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46867,7 +46987,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46883,7 +47003,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46899,7 +47019,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46915,7 +47035,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46931,7 +47051,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46947,7 +47067,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46963,7 +47083,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46979,7 +47099,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46995,7 +47115,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47011,7 +47131,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47027,7 +47147,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47043,7 +47163,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47059,7 +47179,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47075,7 +47195,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47091,7 +47211,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47107,7 +47227,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -47123,7 +47243,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="72">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="73">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -47139,7 +47259,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -51451,20 +51571,42 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A113" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B113" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C113" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D113" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E113" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F113" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G113" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H113" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I113" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J113" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K113" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L113" s="4">
+        <f t="shared" ref="L113" si="68">IF(COUNTA(B113:K113)=0,"",AVERAGE(B113:K113))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -51803,7 +51945,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="68">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="69">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -51820,7 +51962,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51837,7 +51979,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51854,7 +51996,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51871,7 +52013,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51888,7 +52030,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51905,7 +52047,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51922,7 +52064,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51939,7 +52081,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51956,7 +52098,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51973,7 +52115,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -51990,7 +52132,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52007,7 +52149,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52024,7 +52166,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52041,7 +52183,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52058,7 +52200,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52075,7 +52217,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52092,7 +52234,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52109,7 +52251,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52126,7 +52268,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52143,7 +52285,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52160,7 +52302,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52177,7 +52319,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52194,7 +52336,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52211,7 +52353,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52228,7 +52370,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52245,7 +52387,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52262,7 +52404,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52279,7 +52421,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52296,7 +52438,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52313,7 +52455,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52330,7 +52472,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52347,7 +52489,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52364,7 +52506,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52381,7 +52523,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52398,7 +52540,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52415,7 +52557,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52432,7 +52574,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52449,7 +52591,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52466,7 +52608,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52483,7 +52625,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52500,7 +52642,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52517,7 +52659,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52534,7 +52676,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52551,7 +52693,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52568,7 +52710,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52585,7 +52727,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52602,7 +52744,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52619,7 +52761,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52636,7 +52778,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52653,7 +52795,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52670,7 +52812,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52687,7 +52829,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52704,7 +52846,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52721,7 +52863,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52738,7 +52880,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52755,7 +52897,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52772,7 +52914,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52789,7 +52931,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52806,7 +52948,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52823,7 +52965,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52840,7 +52982,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52857,7 +52999,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52874,7 +53016,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -52891,7 +53033,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="69">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="70">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -52908,7 +53050,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52925,7 +53067,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52942,7 +53084,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52959,7 +53101,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52976,7 +53118,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52993,7 +53135,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53010,7 +53152,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53027,7 +53169,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53044,7 +53186,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53061,7 +53203,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53078,7 +53220,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53095,7 +53237,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53112,7 +53254,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53129,7 +53271,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53146,7 +53288,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53163,7 +53305,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53180,7 +53322,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53197,7 +53339,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53214,7 +53356,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53231,7 +53373,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53248,7 +53390,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53265,7 +53407,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53282,7 +53424,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53299,7 +53441,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53316,7 +53458,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53333,7 +53475,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53350,7 +53492,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53367,7 +53509,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53384,7 +53526,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53401,7 +53543,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53418,7 +53560,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53435,7 +53577,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53452,7 +53594,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53469,7 +53611,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53486,7 +53628,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53503,7 +53645,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53520,7 +53662,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53537,7 +53679,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53554,7 +53696,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53571,7 +53713,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53588,7 +53730,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53605,7 +53747,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53622,7 +53764,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53639,7 +53781,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53656,7 +53798,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53673,7 +53815,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53690,7 +53832,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53707,7 +53849,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53724,7 +53866,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53741,7 +53883,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53758,7 +53900,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53775,7 +53917,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53792,7 +53934,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53809,7 +53951,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53826,7 +53968,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53843,7 +53985,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53860,7 +54002,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53877,7 +54019,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53894,7 +54036,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53911,7 +54053,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53928,7 +54070,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53945,7 +54087,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53962,7 +54104,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53979,7 +54121,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="70">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="71">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -53996,7 +54138,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54013,7 +54155,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54030,7 +54172,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54047,7 +54189,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54064,7 +54206,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54081,7 +54223,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54098,7 +54240,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54115,7 +54257,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54132,7 +54274,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54149,7 +54291,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54166,7 +54308,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54183,7 +54325,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54200,7 +54342,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54217,7 +54359,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54234,7 +54376,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54251,7 +54393,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54268,7 +54410,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54285,7 +54427,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54302,7 +54444,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54319,7 +54461,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54336,7 +54478,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54353,7 +54495,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54370,7 +54512,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54387,7 +54529,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54404,7 +54546,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54421,7 +54563,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54438,7 +54580,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54455,7 +54597,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54472,7 +54614,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54489,7 +54631,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54506,7 +54648,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54523,7 +54665,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54540,7 +54682,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54557,7 +54699,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54574,7 +54716,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54591,7 +54733,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54608,7 +54750,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54625,7 +54767,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54642,7 +54784,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54659,7 +54801,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54676,7 +54818,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54693,7 +54835,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54710,7 +54852,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54727,7 +54869,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54744,7 +54886,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54761,7 +54903,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54778,7 +54920,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54795,7 +54937,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54812,7 +54954,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54829,7 +54971,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54846,7 +54988,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54863,7 +55005,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54880,7 +55022,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54897,7 +55039,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54914,7 +55056,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54931,7 +55073,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54948,7 +55090,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54965,7 +55107,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54982,7 +55124,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54999,7 +55141,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55016,7 +55158,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55033,7 +55175,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55050,7 +55192,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -55067,7 +55209,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="71">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="72">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -55084,7 +55226,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55101,7 +55243,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55118,7 +55260,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55135,7 +55277,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55152,7 +55294,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55169,7 +55311,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55186,7 +55328,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55203,7 +55345,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55220,7 +55362,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55237,7 +55379,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55254,7 +55396,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55271,7 +55413,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55288,7 +55430,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55305,7 +55447,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55322,7 +55464,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55339,7 +55481,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55356,7 +55498,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55373,7 +55515,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55390,7 +55532,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55407,7 +55549,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55424,7 +55566,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55441,7 +55583,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55458,7 +55600,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55475,7 +55617,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55492,7 +55634,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55509,7 +55651,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55526,7 +55668,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55543,7 +55685,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55560,7 +55702,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55577,7 +55719,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55594,7 +55736,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55611,7 +55753,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55628,7 +55770,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55645,7 +55787,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55662,7 +55804,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55679,7 +55821,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55696,7 +55838,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55713,7 +55855,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55730,7 +55872,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55747,7 +55889,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55764,7 +55906,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55781,7 +55923,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55798,7 +55940,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55815,7 +55957,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55832,7 +55974,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55849,7 +55991,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55866,7 +56008,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55883,7 +56025,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55900,7 +56042,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55917,7 +56059,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55934,7 +56076,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55951,7 +56093,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55968,7 +56110,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55985,7 +56127,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56002,7 +56144,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56019,7 +56161,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56036,7 +56178,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56053,7 +56195,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56070,7 +56212,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56087,7 +56229,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56104,7 +56246,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56121,7 +56263,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56138,7 +56280,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -56155,7 +56297,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="72">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="73">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -56172,7 +56314,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202BA8EA-F68C-4CB7-9B9F-80275C32E311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78034774-48DA-44DE-B8FD-E47742AF7566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,6 +670,9 @@
                 <c:pt idx="108">
                   <c:v>46283</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1007,7 +1010,7 @@
                   <c:v>41.322608695652171</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0</c:v>
+                  <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>0</c:v>
@@ -2323,6 +2326,9 @@
                 <c:pt idx="108">
                   <c:v>46283</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2660,7 +2666,7 @@
                   <c:v>3.4747368421052629</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0</c:v>
+                  <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>0</c:v>
@@ -3976,6 +3982,9 @@
                 <c:pt idx="108">
                   <c:v>46283</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4313,7 +4322,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>0</c:v>
@@ -5629,6 +5638,9 @@
                 <c:pt idx="108">
                   <c:v>46283</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5966,7 +5978,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>0</c:v>
@@ -15972,33 +15984,81 @@
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="3"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="3"/>
-      <c r="O114" s="3"/>
-      <c r="P114" s="3"/>
-      <c r="Q114" s="3"/>
-      <c r="R114" s="3"/>
-      <c r="S114" s="3"/>
-      <c r="T114" s="3"/>
-      <c r="U114" s="3"/>
-      <c r="V114" s="3"/>
-      <c r="W114" s="3"/>
-      <c r="X114" s="3"/>
-      <c r="Y114" s="4" t="str">
+      <c r="A114" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B114" s="3">
+        <v>39</v>
+      </c>
+      <c r="C114" s="3">
+        <v>44</v>
+      </c>
+      <c r="D114" s="3">
+        <v>44</v>
+      </c>
+      <c r="E114" s="3">
+        <v>42</v>
+      </c>
+      <c r="F114" s="3">
+        <v>42</v>
+      </c>
+      <c r="G114" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="H114" s="3">
+        <v>44</v>
+      </c>
+      <c r="I114" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J114" s="3">
+        <v>41</v>
+      </c>
+      <c r="K114" s="3">
+        <v>38</v>
+      </c>
+      <c r="L114" s="3">
+        <v>36</v>
+      </c>
+      <c r="M114" s="3">
+        <v>41</v>
+      </c>
+      <c r="N114" s="3">
+        <v>44</v>
+      </c>
+      <c r="O114" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="P114" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q114" s="3">
+        <v>42</v>
+      </c>
+      <c r="R114" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S114" s="3">
+        <v>42</v>
+      </c>
+      <c r="T114" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="U114" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="V114" s="3">
+        <v>38</v>
+      </c>
+      <c r="W114" s="3">
+        <v>44</v>
+      </c>
+      <c r="X114" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y114" s="4">
         <f t="shared" si="26"/>
-        <v/>
+        <v>39.678260869565221</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.25">
@@ -31616,29 +31676,69 @@
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="3"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="3"/>
-      <c r="O114" s="3"/>
-      <c r="P114" s="3"/>
-      <c r="Q114" s="3"/>
-      <c r="R114" s="3"/>
-      <c r="S114" s="3"/>
-      <c r="T114" s="3"/>
-      <c r="U114" s="4" t="str">
+      <c r="A114" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B114" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C114" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D114" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E114" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F114" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G114" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H114" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I114" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="J114" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K114" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L114" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M114" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N114" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O114" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P114" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q114" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R114" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S114" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T114" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U114" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.4610526315789478</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -42832,19 +42932,39 @@
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="4" t="str">
+      <c r="A114" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B114" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C114" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D114" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E114" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F114" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G114" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H114" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I114" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J114" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K114" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -51610,20 +51730,42 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="4" t="str">
+      <c r="A114" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B114" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C114" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D114" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E114" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F114" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G114" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H114" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I114" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J114" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K114" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L114" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78034774-48DA-44DE-B8FD-E47742AF7566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B835AF-3C33-4271-85F4-77BC51AF20CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -673,6 +673,9 @@
                 <c:pt idx="109">
                   <c:v>46286</c:v>
                 </c:pt>
+                <c:pt idx="110">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1013,7 +1016,7 @@
                   <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0</c:v>
+                  <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>0</c:v>
@@ -2329,6 +2332,9 @@
                 <c:pt idx="109">
                   <c:v>46286</c:v>
                 </c:pt>
+                <c:pt idx="110">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2669,7 +2675,7 @@
                   <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0</c:v>
+                  <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>0</c:v>
@@ -3985,6 +3991,9 @@
                 <c:pt idx="109">
                   <c:v>46286</c:v>
                 </c:pt>
+                <c:pt idx="110">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4325,7 +4334,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>0</c:v>
@@ -5641,6 +5650,9 @@
                 <c:pt idx="109">
                   <c:v>46286</c:v>
                 </c:pt>
+                <c:pt idx="110">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5981,7 +5993,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>0</c:v>
@@ -16062,33 +16074,81 @@
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3"/>
-      <c r="O115" s="3"/>
-      <c r="P115" s="3"/>
-      <c r="Q115" s="3"/>
-      <c r="R115" s="3"/>
-      <c r="S115" s="3"/>
-      <c r="T115" s="3"/>
-      <c r="U115" s="3"/>
-      <c r="V115" s="3"/>
-      <c r="W115" s="3"/>
-      <c r="X115" s="3"/>
-      <c r="Y115" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A115" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B115" s="3">
+        <v>39</v>
+      </c>
+      <c r="C115" s="3">
+        <v>44</v>
+      </c>
+      <c r="D115" s="3">
+        <v>44</v>
+      </c>
+      <c r="E115" s="3">
+        <v>42</v>
+      </c>
+      <c r="F115" s="3">
+        <v>42</v>
+      </c>
+      <c r="G115" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="H115" s="3">
+        <v>44</v>
+      </c>
+      <c r="I115" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J115" s="3">
+        <v>41</v>
+      </c>
+      <c r="K115" s="3">
+        <v>38</v>
+      </c>
+      <c r="L115" s="3">
+        <v>36</v>
+      </c>
+      <c r="M115" s="3">
+        <v>41</v>
+      </c>
+      <c r="N115" s="3">
+        <v>44</v>
+      </c>
+      <c r="O115" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="P115" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q115" s="3">
+        <v>42</v>
+      </c>
+      <c r="R115" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S115" s="3">
+        <v>42</v>
+      </c>
+      <c r="T115" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="U115" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="V115" s="3">
+        <v>38</v>
+      </c>
+      <c r="W115" s="3">
+        <v>44</v>
+      </c>
+      <c r="X115" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y115" s="4">
+        <f t="shared" ref="Y115" si="61">IF(COUNTA(B115:X115)=0,"",AVERAGE(B115:X115))</f>
+        <v>39.678260869565221</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.25">
@@ -16627,7 +16687,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="61">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="62">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="62">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="63">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="63">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="64">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="64">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="65">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24187,7 +24247,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24217,7 +24277,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24247,7 +24307,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24277,7 +24337,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -24307,7 +24367,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="65">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="66">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24337,7 +24397,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -31742,29 +31802,69 @@
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3"/>
-      <c r="O115" s="3"/>
-      <c r="P115" s="3"/>
-      <c r="Q115" s="3"/>
-      <c r="R115" s="3"/>
-      <c r="S115" s="3"/>
-      <c r="T115" s="3"/>
-      <c r="U115" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A115" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B115" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C115" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E115" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F115" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G115" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H115" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I115" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="J115" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K115" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L115" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M115" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N115" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O115" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P115" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q115" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R115" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S115" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T115" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U115" s="4">
+        <f t="shared" ref="U115" si="69">IF(COUNTA(B115:T115)=0,"",AVERAGE(B115:T115))</f>
+        <v>3.4610526315789478</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -32231,7 +32331,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="69">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="70">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -32257,7 +32357,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32283,7 +32383,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32309,7 +32409,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32335,7 +32435,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32361,7 +32461,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32387,7 +32487,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32413,7 +32513,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32439,7 +32539,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32465,7 +32565,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32491,7 +32591,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32517,7 +32617,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32543,7 +32643,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32569,7 +32669,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32595,7 +32695,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32621,7 +32721,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32647,7 +32747,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32673,7 +32773,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32699,7 +32799,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32725,7 +32825,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32751,7 +32851,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32777,7 +32877,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32803,7 +32903,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32829,7 +32929,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32855,7 +32955,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32881,7 +32981,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32907,7 +33007,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32933,7 +33033,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32959,7 +33059,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32985,7 +33085,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33011,7 +33111,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33037,7 +33137,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33063,7 +33163,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33089,7 +33189,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33115,7 +33215,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33141,7 +33241,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33167,7 +33267,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33193,7 +33293,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33219,7 +33319,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33245,7 +33345,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33271,7 +33371,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33297,7 +33397,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33323,7 +33423,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33349,7 +33449,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33375,7 +33475,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33401,7 +33501,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33427,7 +33527,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33453,7 +33553,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33479,7 +33579,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33505,7 +33605,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33531,7 +33631,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33557,7 +33657,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33583,7 +33683,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33609,7 +33709,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33635,7 +33735,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33661,7 +33761,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33687,7 +33787,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33713,7 +33813,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33739,7 +33839,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33765,7 +33865,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33791,7 +33891,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33817,7 +33917,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33843,7 +33943,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33869,7 +33969,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -33895,7 +33995,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="70">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="71">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -33921,7 +34021,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33947,7 +34047,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33973,7 +34073,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33999,7 +34099,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34025,7 +34125,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34051,7 +34151,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34077,7 +34177,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34103,7 +34203,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34129,7 +34229,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34155,7 +34255,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34181,7 +34281,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34207,7 +34307,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34233,7 +34333,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34259,7 +34359,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34285,7 +34385,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34311,7 +34411,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34337,7 +34437,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34363,7 +34463,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34389,7 +34489,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34415,7 +34515,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34441,7 +34541,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34467,7 +34567,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34493,7 +34593,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34519,7 +34619,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34545,7 +34645,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34571,7 +34671,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34597,7 +34697,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34623,7 +34723,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34649,7 +34749,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34675,7 +34775,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34701,7 +34801,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34727,7 +34827,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34753,7 +34853,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34779,7 +34879,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34805,7 +34905,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34831,7 +34931,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34857,7 +34957,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34883,7 +34983,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34909,7 +35009,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34935,7 +35035,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34961,7 +35061,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -34987,7 +35087,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35013,7 +35113,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35039,7 +35139,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35065,7 +35165,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35091,7 +35191,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35117,7 +35217,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35143,7 +35243,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35169,7 +35269,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35195,7 +35295,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35221,7 +35321,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35247,7 +35347,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35273,7 +35373,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35299,7 +35399,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35325,7 +35425,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35351,7 +35451,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35377,7 +35477,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35403,7 +35503,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35429,7 +35529,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35455,7 +35555,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35481,7 +35581,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35507,7 +35607,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35533,7 +35633,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -35559,7 +35659,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="71">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="72">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35585,7 +35685,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35611,7 +35711,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35637,7 +35737,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35663,7 +35763,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35689,7 +35789,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35715,7 +35815,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35741,7 +35841,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35767,7 +35867,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35793,7 +35893,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35819,7 +35919,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35845,7 +35945,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35871,7 +35971,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35897,7 +35997,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35923,7 +36023,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35949,7 +36049,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35975,7 +36075,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36001,7 +36101,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36027,7 +36127,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36053,7 +36153,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36079,7 +36179,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36105,7 +36205,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36131,7 +36231,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36157,7 +36257,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36183,7 +36283,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36209,7 +36309,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36235,7 +36335,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36261,7 +36361,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36287,7 +36387,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36313,7 +36413,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36339,7 +36439,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36365,7 +36465,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36391,7 +36491,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36417,7 +36517,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36443,7 +36543,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36469,7 +36569,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36495,7 +36595,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36521,7 +36621,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36547,7 +36647,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36573,7 +36673,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36599,7 +36699,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36625,7 +36725,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36651,7 +36751,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36677,7 +36777,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36703,7 +36803,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36729,7 +36829,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36755,7 +36855,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36781,7 +36881,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36807,7 +36907,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36833,7 +36933,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36859,7 +36959,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36885,7 +36985,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36911,7 +37011,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36937,7 +37037,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36963,7 +37063,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -36989,7 +37089,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37015,7 +37115,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37041,7 +37141,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37067,7 +37167,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37093,7 +37193,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37119,7 +37219,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37145,7 +37245,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37171,7 +37271,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37197,7 +37297,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -37223,7 +37323,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="72">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="73">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -37249,7 +37349,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37275,7 +37375,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37301,7 +37401,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37327,7 +37427,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37353,7 +37453,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37379,7 +37479,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37405,7 +37505,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37431,7 +37531,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37457,7 +37557,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37483,7 +37583,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37509,7 +37609,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37535,7 +37635,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37561,7 +37661,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37587,7 +37687,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37613,7 +37713,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37639,7 +37739,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37665,7 +37765,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37691,7 +37791,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37717,7 +37817,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37743,7 +37843,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37769,7 +37869,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37795,7 +37895,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37821,7 +37921,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37847,7 +37947,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37873,7 +37973,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37899,7 +37999,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37925,7 +38025,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37951,7 +38051,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37977,7 +38077,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38003,7 +38103,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38029,7 +38129,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38055,7 +38155,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38081,7 +38181,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38107,7 +38207,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38133,7 +38233,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38159,7 +38259,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38185,7 +38285,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38211,7 +38311,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38237,7 +38337,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38263,7 +38363,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38289,7 +38389,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38315,7 +38415,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38341,7 +38441,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38367,7 +38467,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38393,7 +38493,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38419,7 +38519,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38445,7 +38545,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38471,7 +38571,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38497,7 +38597,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38523,7 +38623,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38549,7 +38649,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38575,7 +38675,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38601,7 +38701,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38627,7 +38727,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38653,7 +38753,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38679,7 +38779,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38705,7 +38805,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38731,7 +38831,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38757,7 +38857,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38783,7 +38883,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38809,7 +38909,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38835,7 +38935,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38861,7 +38961,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -38887,7 +38987,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="73">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="74">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -38913,7 +39013,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -42968,19 +43068,39 @@
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A115" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B115" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C115" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D115" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E115" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F115" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G115" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H115" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I115" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J115" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K115" s="4">
+        <f t="shared" ref="K115" si="69">IF(COUNTA(B115:J115)=0,"",AVERAGE(B115:J115))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -43267,7 +43387,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="69">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="70">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -43283,7 +43403,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43299,7 +43419,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43315,7 +43435,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43331,7 +43451,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43347,7 +43467,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43363,7 +43483,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43379,7 +43499,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43395,7 +43515,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43411,7 +43531,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43427,7 +43547,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43443,7 +43563,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43459,7 +43579,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43475,7 +43595,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43491,7 +43611,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43507,7 +43627,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43523,7 +43643,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43539,7 +43659,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43555,7 +43675,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43571,7 +43691,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43587,7 +43707,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43603,7 +43723,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43619,7 +43739,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43635,7 +43755,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43651,7 +43771,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43667,7 +43787,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43683,7 +43803,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43699,7 +43819,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43715,7 +43835,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43731,7 +43851,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43747,7 +43867,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43763,7 +43883,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43779,7 +43899,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43795,7 +43915,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43811,7 +43931,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43827,7 +43947,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43843,7 +43963,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43859,7 +43979,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43875,7 +43995,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43891,7 +44011,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43907,7 +44027,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43923,7 +44043,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43939,7 +44059,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43955,7 +44075,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43971,7 +44091,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -43987,7 +44107,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44003,7 +44123,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44019,7 +44139,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44035,7 +44155,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44051,7 +44171,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44067,7 +44187,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44083,7 +44203,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44099,7 +44219,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44115,7 +44235,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44131,7 +44251,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44147,7 +44267,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44163,7 +44283,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44179,7 +44299,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44195,7 +44315,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44211,7 +44331,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44227,7 +44347,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44243,7 +44363,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44259,7 +44379,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44275,7 +44395,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -44291,7 +44411,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="70">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="71">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -44307,7 +44427,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44323,7 +44443,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44339,7 +44459,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44355,7 +44475,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44371,7 +44491,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44387,7 +44507,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44403,7 +44523,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44419,7 +44539,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44435,7 +44555,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44451,7 +44571,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44467,7 +44587,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44483,7 +44603,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44499,7 +44619,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44515,7 +44635,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44531,7 +44651,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44547,7 +44667,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44563,7 +44683,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44579,7 +44699,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44595,7 +44715,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44611,7 +44731,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44627,7 +44747,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44643,7 +44763,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44659,7 +44779,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44675,7 +44795,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44691,7 +44811,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44707,7 +44827,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44723,7 +44843,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44739,7 +44859,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44755,7 +44875,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44771,7 +44891,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44787,7 +44907,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44803,7 +44923,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44819,7 +44939,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44835,7 +44955,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44851,7 +44971,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44867,7 +44987,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44883,7 +45003,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44899,7 +45019,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44915,7 +45035,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44931,7 +45051,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44947,7 +45067,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44963,7 +45083,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44979,7 +45099,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44995,7 +45115,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45011,7 +45131,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45027,7 +45147,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45043,7 +45163,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45059,7 +45179,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45075,7 +45195,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45091,7 +45211,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45107,7 +45227,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45123,7 +45243,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45139,7 +45259,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45155,7 +45275,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45171,7 +45291,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45187,7 +45307,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45203,7 +45323,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45219,7 +45339,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45235,7 +45355,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45251,7 +45371,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45267,7 +45387,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45283,7 +45403,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45299,7 +45419,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -45315,7 +45435,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="71">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="72">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -45331,7 +45451,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45347,7 +45467,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45363,7 +45483,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45379,7 +45499,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45395,7 +45515,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45411,7 +45531,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45427,7 +45547,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45443,7 +45563,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45459,7 +45579,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45475,7 +45595,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45491,7 +45611,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45507,7 +45627,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45523,7 +45643,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45539,7 +45659,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45555,7 +45675,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45571,7 +45691,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45587,7 +45707,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45603,7 +45723,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45619,7 +45739,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45635,7 +45755,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45651,7 +45771,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45667,7 +45787,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45683,7 +45803,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45699,7 +45819,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45715,7 +45835,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45731,7 +45851,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45747,7 +45867,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45763,7 +45883,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45779,7 +45899,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45795,7 +45915,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45811,7 +45931,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45827,7 +45947,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45843,7 +45963,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45859,7 +45979,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45875,7 +45995,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45891,7 +46011,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45907,7 +46027,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45923,7 +46043,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45939,7 +46059,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45955,7 +46075,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45971,7 +46091,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45987,7 +46107,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46003,7 +46123,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46019,7 +46139,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46035,7 +46155,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46051,7 +46171,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46067,7 +46187,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46083,7 +46203,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46099,7 +46219,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46115,7 +46235,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46131,7 +46251,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46147,7 +46267,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46163,7 +46283,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46179,7 +46299,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46195,7 +46315,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46211,7 +46331,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46227,7 +46347,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46243,7 +46363,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46259,7 +46379,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46275,7 +46395,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46291,7 +46411,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46307,7 +46427,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46323,7 +46443,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -46339,7 +46459,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="72">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="73">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -46355,7 +46475,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46371,7 +46491,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46387,7 +46507,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46403,7 +46523,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46419,7 +46539,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46435,7 +46555,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46451,7 +46571,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46467,7 +46587,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46483,7 +46603,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46499,7 +46619,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46515,7 +46635,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46531,7 +46651,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46547,7 +46667,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46563,7 +46683,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46579,7 +46699,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46595,7 +46715,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46611,7 +46731,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46627,7 +46747,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46643,7 +46763,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46659,7 +46779,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46675,7 +46795,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46691,7 +46811,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46707,7 +46827,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46723,7 +46843,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46739,7 +46859,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46755,7 +46875,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46771,7 +46891,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46787,7 +46907,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46803,7 +46923,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46819,7 +46939,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46835,7 +46955,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46851,7 +46971,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46867,7 +46987,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46883,7 +47003,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46899,7 +47019,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46915,7 +47035,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46931,7 +47051,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46947,7 +47067,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46963,7 +47083,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46979,7 +47099,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46995,7 +47115,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47011,7 +47131,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47027,7 +47147,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47043,7 +47163,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47059,7 +47179,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47075,7 +47195,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47091,7 +47211,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47107,7 +47227,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47123,7 +47243,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47139,7 +47259,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47155,7 +47275,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47171,7 +47291,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47187,7 +47307,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47203,7 +47323,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47219,7 +47339,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47235,7 +47355,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47251,7 +47371,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47267,7 +47387,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47283,7 +47403,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47299,7 +47419,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47315,7 +47435,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47331,7 +47451,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47347,7 +47467,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -47363,7 +47483,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="73">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="74">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -47379,7 +47499,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -51769,20 +51889,42 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A115" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B115" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C115" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D115" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E115" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F115" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G115" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H115" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I115" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J115" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K115" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L115" s="4">
+        <f t="shared" ref="L115" si="69">IF(COUNTA(B115:K115)=0,"",AVERAGE(B115:K115))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -52087,7 +52229,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="69">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="70">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -52104,7 +52246,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52121,7 +52263,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52138,7 +52280,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52155,7 +52297,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52172,7 +52314,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52189,7 +52331,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52206,7 +52348,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52223,7 +52365,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52240,7 +52382,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52257,7 +52399,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52274,7 +52416,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52291,7 +52433,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52308,7 +52450,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52325,7 +52467,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52342,7 +52484,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52359,7 +52501,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52376,7 +52518,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52393,7 +52535,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52410,7 +52552,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52427,7 +52569,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52444,7 +52586,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52461,7 +52603,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52478,7 +52620,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52495,7 +52637,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52512,7 +52654,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52529,7 +52671,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52546,7 +52688,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52563,7 +52705,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52580,7 +52722,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52597,7 +52739,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52614,7 +52756,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52631,7 +52773,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52648,7 +52790,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52665,7 +52807,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52682,7 +52824,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52699,7 +52841,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52716,7 +52858,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52733,7 +52875,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52750,7 +52892,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52767,7 +52909,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52784,7 +52926,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52801,7 +52943,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52818,7 +52960,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52835,7 +52977,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52852,7 +52994,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52869,7 +53011,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52886,7 +53028,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52903,7 +53045,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52920,7 +53062,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52937,7 +53079,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52954,7 +53096,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52971,7 +53113,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -52988,7 +53130,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53005,7 +53147,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53022,7 +53164,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53039,7 +53181,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53056,7 +53198,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53073,7 +53215,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53090,7 +53232,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53107,7 +53249,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53124,7 +53266,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53141,7 +53283,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53158,7 +53300,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -53175,7 +53317,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="70">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="71">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -53192,7 +53334,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53209,7 +53351,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53226,7 +53368,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53243,7 +53385,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53260,7 +53402,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53277,7 +53419,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53294,7 +53436,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53311,7 +53453,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53328,7 +53470,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53345,7 +53487,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53362,7 +53504,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53379,7 +53521,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53396,7 +53538,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53413,7 +53555,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53430,7 +53572,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53447,7 +53589,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53464,7 +53606,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53481,7 +53623,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53498,7 +53640,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53515,7 +53657,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53532,7 +53674,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53549,7 +53691,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53566,7 +53708,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53583,7 +53725,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53600,7 +53742,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53617,7 +53759,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53634,7 +53776,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53651,7 +53793,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53668,7 +53810,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53685,7 +53827,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53702,7 +53844,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53719,7 +53861,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53736,7 +53878,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53753,7 +53895,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53770,7 +53912,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53787,7 +53929,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53804,7 +53946,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53821,7 +53963,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53838,7 +53980,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53855,7 +53997,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53872,7 +54014,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53889,7 +54031,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53906,7 +54048,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53923,7 +54065,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53940,7 +54082,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53957,7 +54099,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53974,7 +54116,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53991,7 +54133,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54008,7 +54150,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54025,7 +54167,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54042,7 +54184,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54059,7 +54201,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54076,7 +54218,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54093,7 +54235,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54110,7 +54252,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54127,7 +54269,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54144,7 +54286,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54161,7 +54303,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54178,7 +54320,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54195,7 +54337,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54212,7 +54354,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54229,7 +54371,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54246,7 +54388,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -54263,7 +54405,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="71">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="72">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -54280,7 +54422,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54297,7 +54439,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54314,7 +54456,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54331,7 +54473,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54348,7 +54490,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54365,7 +54507,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54382,7 +54524,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54399,7 +54541,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54416,7 +54558,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54433,7 +54575,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54450,7 +54592,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54467,7 +54609,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54484,7 +54626,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54501,7 +54643,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54518,7 +54660,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54535,7 +54677,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54552,7 +54694,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54569,7 +54711,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54586,7 +54728,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54603,7 +54745,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54620,7 +54762,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54637,7 +54779,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54654,7 +54796,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54671,7 +54813,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54688,7 +54830,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54705,7 +54847,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54722,7 +54864,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54739,7 +54881,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54756,7 +54898,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54773,7 +54915,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54790,7 +54932,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54807,7 +54949,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54824,7 +54966,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54841,7 +54983,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54858,7 +55000,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54875,7 +55017,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54892,7 +55034,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54909,7 +55051,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54926,7 +55068,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54943,7 +55085,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54960,7 +55102,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54977,7 +55119,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54994,7 +55136,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55011,7 +55153,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55028,7 +55170,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55045,7 +55187,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55062,7 +55204,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55079,7 +55221,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55096,7 +55238,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55113,7 +55255,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55130,7 +55272,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55147,7 +55289,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55164,7 +55306,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55181,7 +55323,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55198,7 +55340,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55215,7 +55357,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55232,7 +55374,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55249,7 +55391,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55266,7 +55408,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55283,7 +55425,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55300,7 +55442,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55317,7 +55459,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55334,7 +55476,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -55351,7 +55493,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="72">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="73">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -55368,7 +55510,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55385,7 +55527,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55402,7 +55544,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55419,7 +55561,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55436,7 +55578,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55453,7 +55595,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55470,7 +55612,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55487,7 +55629,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55504,7 +55646,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55521,7 +55663,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55538,7 +55680,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55555,7 +55697,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55572,7 +55714,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55589,7 +55731,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55606,7 +55748,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55623,7 +55765,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55640,7 +55782,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55657,7 +55799,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55674,7 +55816,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55691,7 +55833,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55708,7 +55850,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55725,7 +55867,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55742,7 +55884,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55759,7 +55901,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55776,7 +55918,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55793,7 +55935,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55810,7 +55952,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55827,7 +55969,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55844,7 +55986,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55861,7 +56003,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55878,7 +56020,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55895,7 +56037,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55912,7 +56054,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55929,7 +56071,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55946,7 +56088,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55963,7 +56105,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55980,7 +56122,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55997,7 +56139,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56014,7 +56156,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56031,7 +56173,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56048,7 +56190,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56065,7 +56207,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56082,7 +56224,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56099,7 +56241,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56116,7 +56258,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56133,7 +56275,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56150,7 +56292,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56167,7 +56309,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56184,7 +56326,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56201,7 +56343,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56218,7 +56360,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56235,7 +56377,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56252,7 +56394,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56269,7 +56411,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56286,7 +56428,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56303,7 +56445,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56320,7 +56462,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56337,7 +56479,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56354,7 +56496,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56371,7 +56513,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56388,7 +56530,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56405,7 +56547,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56422,7 +56564,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -56439,7 +56581,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="73">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="74">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -56456,7 +56598,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B835AF-3C33-4271-85F4-77BC51AF20CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4A6DC6-EF59-4D7E-A00C-477AE503CFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -676,6 +676,9 @@
                 <c:pt idx="110">
                   <c:v>46287</c:v>
                 </c:pt>
+                <c:pt idx="111">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1019,7 +1022,7 @@
                   <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0</c:v>
+                  <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>0</c:v>
@@ -2335,6 +2338,9 @@
                 <c:pt idx="110">
                   <c:v>46287</c:v>
                 </c:pt>
+                <c:pt idx="111">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2678,7 +2684,7 @@
                   <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0</c:v>
+                  <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>0</c:v>
@@ -3994,6 +4000,9 @@
                 <c:pt idx="110">
                   <c:v>46287</c:v>
                 </c:pt>
+                <c:pt idx="111">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4337,7 +4346,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>0</c:v>
@@ -5653,6 +5662,9 @@
                 <c:pt idx="110">
                   <c:v>46287</c:v>
                 </c:pt>
+                <c:pt idx="111">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5996,7 +6008,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>0</c:v>
@@ -16152,33 +16164,81 @@
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="3"/>
-      <c r="O116" s="3"/>
-      <c r="P116" s="3"/>
-      <c r="Q116" s="3"/>
-      <c r="R116" s="3"/>
-      <c r="S116" s="3"/>
-      <c r="T116" s="3"/>
-      <c r="U116" s="3"/>
-      <c r="V116" s="3"/>
-      <c r="W116" s="3"/>
-      <c r="X116" s="3"/>
-      <c r="Y116" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A116" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B116" s="3">
+        <v>39</v>
+      </c>
+      <c r="C116" s="3">
+        <v>44</v>
+      </c>
+      <c r="D116" s="3">
+        <v>44</v>
+      </c>
+      <c r="E116" s="3">
+        <v>42</v>
+      </c>
+      <c r="F116" s="3">
+        <v>42</v>
+      </c>
+      <c r="G116" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="H116" s="3">
+        <v>44</v>
+      </c>
+      <c r="I116" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J116" s="3">
+        <v>41</v>
+      </c>
+      <c r="K116" s="3">
+        <v>38</v>
+      </c>
+      <c r="L116" s="3">
+        <v>36</v>
+      </c>
+      <c r="M116" s="3">
+        <v>41</v>
+      </c>
+      <c r="N116" s="3">
+        <v>44</v>
+      </c>
+      <c r="O116" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="P116" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q116" s="3">
+        <v>42</v>
+      </c>
+      <c r="R116" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S116" s="3">
+        <v>42</v>
+      </c>
+      <c r="T116" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="U116" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="V116" s="3">
+        <v>38</v>
+      </c>
+      <c r="W116" s="3">
+        <v>44</v>
+      </c>
+      <c r="X116" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y116" s="4">
+        <f t="shared" ref="Y116" si="62">IF(COUNTA(B116:X116)=0,"",AVERAGE(B116:X116))</f>
+        <v>39.678260869565221</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.25">
@@ -16687,7 +16747,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="62">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="63">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="63">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="64">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="64">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="65">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="65">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="66">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24187,7 +24247,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24217,7 +24277,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24247,7 +24307,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24277,7 +24337,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24307,7 +24367,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24337,7 +24397,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -24367,7 +24427,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="66">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="67">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24397,7 +24457,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -31868,29 +31928,69 @@
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="3"/>
-      <c r="O116" s="3"/>
-      <c r="P116" s="3"/>
-      <c r="Q116" s="3"/>
-      <c r="R116" s="3"/>
-      <c r="S116" s="3"/>
-      <c r="T116" s="3"/>
-      <c r="U116" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A116" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B116" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C116" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D116" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E116" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F116" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G116" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H116" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I116" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="J116" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K116" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L116" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M116" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N116" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O116" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P116" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q116" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R116" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S116" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T116" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U116" s="4">
+        <f t="shared" ref="U116" si="70">IF(COUNTA(B116:T116)=0,"",AVERAGE(B116:T116))</f>
+        <v>3.4610526315789478</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -32331,7 +32431,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="70">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="71">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -32357,7 +32457,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32383,7 +32483,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32409,7 +32509,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32435,7 +32535,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32461,7 +32561,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32487,7 +32587,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32513,7 +32613,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32539,7 +32639,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32565,7 +32665,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32591,7 +32691,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32617,7 +32717,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32643,7 +32743,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32669,7 +32769,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32695,7 +32795,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32721,7 +32821,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32747,7 +32847,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32773,7 +32873,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32799,7 +32899,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32825,7 +32925,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32851,7 +32951,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32877,7 +32977,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32903,7 +33003,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32929,7 +33029,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32955,7 +33055,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -32981,7 +33081,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33007,7 +33107,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33033,7 +33133,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33059,7 +33159,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33085,7 +33185,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33111,7 +33211,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33137,7 +33237,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33163,7 +33263,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33189,7 +33289,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33215,7 +33315,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33241,7 +33341,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33267,7 +33367,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33293,7 +33393,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33319,7 +33419,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33345,7 +33445,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33371,7 +33471,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33397,7 +33497,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33423,7 +33523,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33449,7 +33549,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33475,7 +33575,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33501,7 +33601,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33527,7 +33627,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33553,7 +33653,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33579,7 +33679,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33605,7 +33705,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33631,7 +33731,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33657,7 +33757,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33683,7 +33783,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33709,7 +33809,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33735,7 +33835,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33761,7 +33861,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33787,7 +33887,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33813,7 +33913,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33839,7 +33939,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33865,7 +33965,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33891,7 +33991,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33917,7 +34017,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33943,7 +34043,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33969,7 +34069,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -33995,7 +34095,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="71">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="72">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -34021,7 +34121,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34047,7 +34147,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34073,7 +34173,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34099,7 +34199,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34125,7 +34225,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34151,7 +34251,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34177,7 +34277,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34203,7 +34303,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34229,7 +34329,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34255,7 +34355,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34281,7 +34381,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34307,7 +34407,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34333,7 +34433,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34359,7 +34459,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34385,7 +34485,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34411,7 +34511,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34437,7 +34537,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34463,7 +34563,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34489,7 +34589,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34515,7 +34615,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34541,7 +34641,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34567,7 +34667,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34593,7 +34693,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34619,7 +34719,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34645,7 +34745,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34671,7 +34771,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34697,7 +34797,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34723,7 +34823,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34749,7 +34849,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34775,7 +34875,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34801,7 +34901,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34827,7 +34927,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34853,7 +34953,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34879,7 +34979,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34905,7 +35005,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34931,7 +35031,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34957,7 +35057,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34983,7 +35083,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35009,7 +35109,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35035,7 +35135,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35061,7 +35161,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35087,7 +35187,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35113,7 +35213,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35139,7 +35239,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35165,7 +35265,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35191,7 +35291,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35217,7 +35317,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35243,7 +35343,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35269,7 +35369,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35295,7 +35395,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35321,7 +35421,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35347,7 +35447,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35373,7 +35473,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35399,7 +35499,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35425,7 +35525,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35451,7 +35551,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35477,7 +35577,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35503,7 +35603,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35529,7 +35629,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35555,7 +35655,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35581,7 +35681,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35607,7 +35707,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35633,7 +35733,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -35659,7 +35759,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="72">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="73">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35685,7 +35785,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35711,7 +35811,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35737,7 +35837,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35763,7 +35863,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35789,7 +35889,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35815,7 +35915,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35841,7 +35941,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35867,7 +35967,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35893,7 +35993,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35919,7 +36019,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35945,7 +36045,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35971,7 +36071,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35997,7 +36097,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36023,7 +36123,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36049,7 +36149,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36075,7 +36175,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36101,7 +36201,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36127,7 +36227,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36153,7 +36253,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36179,7 +36279,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36205,7 +36305,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36231,7 +36331,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36257,7 +36357,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36283,7 +36383,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36309,7 +36409,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36335,7 +36435,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36361,7 +36461,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36387,7 +36487,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36413,7 +36513,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36439,7 +36539,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36465,7 +36565,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36491,7 +36591,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36517,7 +36617,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36543,7 +36643,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36569,7 +36669,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36595,7 +36695,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36621,7 +36721,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36647,7 +36747,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36673,7 +36773,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36699,7 +36799,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36725,7 +36825,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36751,7 +36851,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36777,7 +36877,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36803,7 +36903,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36829,7 +36929,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36855,7 +36955,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36881,7 +36981,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36907,7 +37007,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36933,7 +37033,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36959,7 +37059,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -36985,7 +37085,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37011,7 +37111,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37037,7 +37137,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37063,7 +37163,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37089,7 +37189,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37115,7 +37215,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37141,7 +37241,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37167,7 +37267,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37193,7 +37293,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37219,7 +37319,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37245,7 +37345,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37271,7 +37371,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37297,7 +37397,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -37323,7 +37423,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="73">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="74">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -37349,7 +37449,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37375,7 +37475,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37401,7 +37501,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37427,7 +37527,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37453,7 +37553,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37479,7 +37579,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37505,7 +37605,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37531,7 +37631,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37557,7 +37657,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37583,7 +37683,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37609,7 +37709,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37635,7 +37735,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37661,7 +37761,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37687,7 +37787,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37713,7 +37813,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37739,7 +37839,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37765,7 +37865,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37791,7 +37891,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37817,7 +37917,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37843,7 +37943,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37869,7 +37969,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37895,7 +37995,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37921,7 +38021,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37947,7 +38047,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37973,7 +38073,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37999,7 +38099,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38025,7 +38125,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38051,7 +38151,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38077,7 +38177,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38103,7 +38203,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38129,7 +38229,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38155,7 +38255,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38181,7 +38281,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38207,7 +38307,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38233,7 +38333,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38259,7 +38359,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38285,7 +38385,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38311,7 +38411,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38337,7 +38437,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38363,7 +38463,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38389,7 +38489,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38415,7 +38515,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38441,7 +38541,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38467,7 +38567,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38493,7 +38593,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38519,7 +38619,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38545,7 +38645,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38571,7 +38671,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38597,7 +38697,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38623,7 +38723,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38649,7 +38749,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38675,7 +38775,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38701,7 +38801,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38727,7 +38827,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38753,7 +38853,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38779,7 +38879,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38805,7 +38905,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38831,7 +38931,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38857,7 +38957,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38883,7 +38983,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38909,7 +39009,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38935,7 +39035,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38961,7 +39061,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -38987,7 +39087,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="74">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="75">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -39013,7 +39113,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -43104,19 +43204,39 @@
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A116" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B116" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C116" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D116" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E116" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F116" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G116" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H116" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I116" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J116" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K116" s="4">
+        <f t="shared" ref="K116" si="70">IF(COUNTA(B116:J116)=0,"",AVERAGE(B116:J116))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -43387,7 +43507,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="70">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="71">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -43403,7 +43523,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43419,7 +43539,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43435,7 +43555,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43451,7 +43571,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43467,7 +43587,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43483,7 +43603,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43499,7 +43619,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43515,7 +43635,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43531,7 +43651,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43547,7 +43667,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43563,7 +43683,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43579,7 +43699,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43595,7 +43715,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43611,7 +43731,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43627,7 +43747,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43643,7 +43763,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43659,7 +43779,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43675,7 +43795,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43691,7 +43811,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43707,7 +43827,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43723,7 +43843,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43739,7 +43859,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43755,7 +43875,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43771,7 +43891,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43787,7 +43907,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43803,7 +43923,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43819,7 +43939,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43835,7 +43955,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43851,7 +43971,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43867,7 +43987,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43883,7 +44003,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43899,7 +44019,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43915,7 +44035,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43931,7 +44051,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43947,7 +44067,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43963,7 +44083,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43979,7 +44099,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -43995,7 +44115,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44011,7 +44131,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44027,7 +44147,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44043,7 +44163,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44059,7 +44179,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44075,7 +44195,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44091,7 +44211,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44107,7 +44227,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44123,7 +44243,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44139,7 +44259,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44155,7 +44275,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44171,7 +44291,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44187,7 +44307,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44203,7 +44323,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44219,7 +44339,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44235,7 +44355,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44251,7 +44371,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44267,7 +44387,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44283,7 +44403,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44299,7 +44419,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44315,7 +44435,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44331,7 +44451,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44347,7 +44467,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44363,7 +44483,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44379,7 +44499,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44395,7 +44515,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -44411,7 +44531,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="71">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="72">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -44427,7 +44547,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44443,7 +44563,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44459,7 +44579,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44475,7 +44595,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44491,7 +44611,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44507,7 +44627,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44523,7 +44643,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44539,7 +44659,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44555,7 +44675,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44571,7 +44691,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44587,7 +44707,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44603,7 +44723,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44619,7 +44739,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44635,7 +44755,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44651,7 +44771,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44667,7 +44787,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44683,7 +44803,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44699,7 +44819,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44715,7 +44835,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44731,7 +44851,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44747,7 +44867,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44763,7 +44883,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44779,7 +44899,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44795,7 +44915,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44811,7 +44931,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44827,7 +44947,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44843,7 +44963,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44859,7 +44979,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44875,7 +44995,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44891,7 +45011,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44907,7 +45027,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44923,7 +45043,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44939,7 +45059,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44955,7 +45075,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44971,7 +45091,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44987,7 +45107,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45003,7 +45123,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45019,7 +45139,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45035,7 +45155,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45051,7 +45171,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45067,7 +45187,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45083,7 +45203,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45099,7 +45219,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45115,7 +45235,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45131,7 +45251,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45147,7 +45267,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45163,7 +45283,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45179,7 +45299,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45195,7 +45315,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45211,7 +45331,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45227,7 +45347,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45243,7 +45363,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45259,7 +45379,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45275,7 +45395,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45291,7 +45411,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45307,7 +45427,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45323,7 +45443,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45339,7 +45459,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45355,7 +45475,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45371,7 +45491,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45387,7 +45507,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45403,7 +45523,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45419,7 +45539,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -45435,7 +45555,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="72">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="73">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -45451,7 +45571,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45467,7 +45587,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45483,7 +45603,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45499,7 +45619,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45515,7 +45635,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45531,7 +45651,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45547,7 +45667,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45563,7 +45683,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45579,7 +45699,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45595,7 +45715,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45611,7 +45731,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45627,7 +45747,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45643,7 +45763,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45659,7 +45779,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45675,7 +45795,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45691,7 +45811,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45707,7 +45827,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45723,7 +45843,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45739,7 +45859,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45755,7 +45875,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45771,7 +45891,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45787,7 +45907,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45803,7 +45923,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45819,7 +45939,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45835,7 +45955,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45851,7 +45971,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45867,7 +45987,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45883,7 +46003,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45899,7 +46019,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45915,7 +46035,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45931,7 +46051,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45947,7 +46067,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45963,7 +46083,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45979,7 +46099,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45995,7 +46115,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46011,7 +46131,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46027,7 +46147,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46043,7 +46163,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46059,7 +46179,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46075,7 +46195,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46091,7 +46211,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46107,7 +46227,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46123,7 +46243,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46139,7 +46259,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46155,7 +46275,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46171,7 +46291,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46187,7 +46307,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46203,7 +46323,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46219,7 +46339,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46235,7 +46355,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46251,7 +46371,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46267,7 +46387,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46283,7 +46403,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46299,7 +46419,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46315,7 +46435,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46331,7 +46451,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46347,7 +46467,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46363,7 +46483,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46379,7 +46499,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46395,7 +46515,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46411,7 +46531,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46427,7 +46547,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46443,7 +46563,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -46459,7 +46579,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="73">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="74">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -46475,7 +46595,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46491,7 +46611,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46507,7 +46627,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46523,7 +46643,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46539,7 +46659,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46555,7 +46675,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46571,7 +46691,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46587,7 +46707,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46603,7 +46723,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46619,7 +46739,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46635,7 +46755,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46651,7 +46771,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46667,7 +46787,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46683,7 +46803,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46699,7 +46819,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46715,7 +46835,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46731,7 +46851,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46747,7 +46867,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46763,7 +46883,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46779,7 +46899,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46795,7 +46915,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46811,7 +46931,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46827,7 +46947,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46843,7 +46963,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46859,7 +46979,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46875,7 +46995,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46891,7 +47011,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46907,7 +47027,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46923,7 +47043,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46939,7 +47059,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46955,7 +47075,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46971,7 +47091,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46987,7 +47107,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47003,7 +47123,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47019,7 +47139,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47035,7 +47155,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47051,7 +47171,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47067,7 +47187,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47083,7 +47203,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47099,7 +47219,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47115,7 +47235,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47131,7 +47251,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47147,7 +47267,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47163,7 +47283,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47179,7 +47299,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47195,7 +47315,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47211,7 +47331,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47227,7 +47347,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47243,7 +47363,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47259,7 +47379,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47275,7 +47395,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47291,7 +47411,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47307,7 +47427,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47323,7 +47443,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47339,7 +47459,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47355,7 +47475,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47371,7 +47491,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47387,7 +47507,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47403,7 +47523,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47419,7 +47539,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47435,7 +47555,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47451,7 +47571,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47467,7 +47587,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -47483,7 +47603,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="74">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="75">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -47499,7 +47619,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -51928,20 +52048,42 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A116" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B116" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C116" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D116" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E116" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F116" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G116" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H116" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I116" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J116" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K116" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L116" s="4">
+        <f t="shared" ref="L116" si="70">IF(COUNTA(B116:K116)=0,"",AVERAGE(B116:K116))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -52229,7 +52371,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="70">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="71">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -52246,7 +52388,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52263,7 +52405,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52280,7 +52422,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52297,7 +52439,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52314,7 +52456,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52331,7 +52473,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52348,7 +52490,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52365,7 +52507,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52382,7 +52524,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52399,7 +52541,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52416,7 +52558,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52433,7 +52575,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52450,7 +52592,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52467,7 +52609,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52484,7 +52626,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52501,7 +52643,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52518,7 +52660,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52535,7 +52677,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52552,7 +52694,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52569,7 +52711,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52586,7 +52728,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52603,7 +52745,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52620,7 +52762,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52637,7 +52779,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52654,7 +52796,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52671,7 +52813,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52688,7 +52830,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52705,7 +52847,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52722,7 +52864,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52739,7 +52881,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52756,7 +52898,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52773,7 +52915,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52790,7 +52932,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52807,7 +52949,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52824,7 +52966,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52841,7 +52983,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52858,7 +53000,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52875,7 +53017,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52892,7 +53034,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52909,7 +53051,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52926,7 +53068,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52943,7 +53085,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52960,7 +53102,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52977,7 +53119,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -52994,7 +53136,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53011,7 +53153,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53028,7 +53170,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53045,7 +53187,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53062,7 +53204,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53079,7 +53221,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53096,7 +53238,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53113,7 +53255,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53130,7 +53272,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53147,7 +53289,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53164,7 +53306,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53181,7 +53323,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53198,7 +53340,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53215,7 +53357,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53232,7 +53374,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53249,7 +53391,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53266,7 +53408,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53283,7 +53425,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53300,7 +53442,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
     </row>
@@ -53317,7 +53459,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="71">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="72">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -53334,7 +53476,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53351,7 +53493,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53368,7 +53510,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53385,7 +53527,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53402,7 +53544,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53419,7 +53561,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53436,7 +53578,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53453,7 +53595,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53470,7 +53612,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53487,7 +53629,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53504,7 +53646,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53521,7 +53663,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53538,7 +53680,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53555,7 +53697,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53572,7 +53714,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53589,7 +53731,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53606,7 +53748,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53623,7 +53765,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53640,7 +53782,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53657,7 +53799,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53674,7 +53816,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53691,7 +53833,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53708,7 +53850,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53725,7 +53867,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53742,7 +53884,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53759,7 +53901,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53776,7 +53918,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53793,7 +53935,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53810,7 +53952,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53827,7 +53969,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53844,7 +53986,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53861,7 +54003,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53878,7 +54020,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53895,7 +54037,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53912,7 +54054,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53929,7 +54071,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53946,7 +54088,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53963,7 +54105,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53980,7 +54122,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53997,7 +54139,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54014,7 +54156,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54031,7 +54173,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54048,7 +54190,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54065,7 +54207,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54082,7 +54224,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54099,7 +54241,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54116,7 +54258,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54133,7 +54275,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54150,7 +54292,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54167,7 +54309,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54184,7 +54326,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54201,7 +54343,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54218,7 +54360,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54235,7 +54377,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54252,7 +54394,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54269,7 +54411,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54286,7 +54428,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54303,7 +54445,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54320,7 +54462,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54337,7 +54479,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54354,7 +54496,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54371,7 +54513,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54388,7 +54530,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -54405,7 +54547,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="72">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="73">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -54422,7 +54564,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54439,7 +54581,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54456,7 +54598,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54473,7 +54615,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54490,7 +54632,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54507,7 +54649,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54524,7 +54666,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54541,7 +54683,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54558,7 +54700,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54575,7 +54717,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54592,7 +54734,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54609,7 +54751,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54626,7 +54768,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54643,7 +54785,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54660,7 +54802,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54677,7 +54819,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54694,7 +54836,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54711,7 +54853,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54728,7 +54870,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54745,7 +54887,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54762,7 +54904,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54779,7 +54921,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54796,7 +54938,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54813,7 +54955,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54830,7 +54972,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54847,7 +54989,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54864,7 +55006,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54881,7 +55023,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54898,7 +55040,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54915,7 +55057,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54932,7 +55074,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54949,7 +55091,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54966,7 +55108,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54983,7 +55125,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55000,7 +55142,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55017,7 +55159,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55034,7 +55176,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55051,7 +55193,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55068,7 +55210,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55085,7 +55227,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55102,7 +55244,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55119,7 +55261,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55136,7 +55278,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55153,7 +55295,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55170,7 +55312,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55187,7 +55329,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55204,7 +55346,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55221,7 +55363,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55238,7 +55380,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55255,7 +55397,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55272,7 +55414,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55289,7 +55431,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55306,7 +55448,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55323,7 +55465,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55340,7 +55482,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55357,7 +55499,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55374,7 +55516,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55391,7 +55533,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55408,7 +55550,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55425,7 +55567,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55442,7 +55584,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55459,7 +55601,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55476,7 +55618,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -55493,7 +55635,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="73">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="74">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -55510,7 +55652,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55527,7 +55669,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55544,7 +55686,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55561,7 +55703,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55578,7 +55720,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55595,7 +55737,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55612,7 +55754,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55629,7 +55771,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55646,7 +55788,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55663,7 +55805,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55680,7 +55822,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55697,7 +55839,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55714,7 +55856,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55731,7 +55873,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55748,7 +55890,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55765,7 +55907,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55782,7 +55924,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55799,7 +55941,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55816,7 +55958,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55833,7 +55975,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55850,7 +55992,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55867,7 +56009,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55884,7 +56026,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55901,7 +56043,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55918,7 +56060,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55935,7 +56077,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55952,7 +56094,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55969,7 +56111,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55986,7 +56128,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56003,7 +56145,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56020,7 +56162,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56037,7 +56179,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56054,7 +56196,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56071,7 +56213,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56088,7 +56230,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56105,7 +56247,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56122,7 +56264,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56139,7 +56281,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56156,7 +56298,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56173,7 +56315,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56190,7 +56332,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56207,7 +56349,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56224,7 +56366,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56241,7 +56383,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56258,7 +56400,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56275,7 +56417,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56292,7 +56434,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56309,7 +56451,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56326,7 +56468,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56343,7 +56485,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56360,7 +56502,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56377,7 +56519,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56394,7 +56536,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56411,7 +56553,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56428,7 +56570,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56445,7 +56587,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56462,7 +56604,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56479,7 +56621,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56496,7 +56638,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56513,7 +56655,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56530,7 +56672,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56547,7 +56689,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56564,7 +56706,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -56581,7 +56723,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="74">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="75">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -56598,7 +56740,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4A6DC6-EF59-4D7E-A00C-477AE503CFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DE9F1D-22FD-40C0-A75E-6708E5ACE52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -679,6 +679,9 @@
                 <c:pt idx="111">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46289</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1025,7 +1028,7 @@
                   <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0</c:v>
+                  <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>0</c:v>
@@ -2341,6 +2344,9 @@
                 <c:pt idx="111">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46289</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2687,7 +2693,7 @@
                   <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0</c:v>
+                  <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>0</c:v>
@@ -4003,6 +4009,9 @@
                 <c:pt idx="111">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46289</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4349,7 +4358,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>0</c:v>
@@ -5665,6 +5674,9 @@
                 <c:pt idx="111">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46289</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6011,7 +6023,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>0</c:v>
@@ -16242,33 +16254,81 @@
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="3"/>
-      <c r="M117" s="3"/>
-      <c r="N117" s="3"/>
-      <c r="O117" s="3"/>
-      <c r="P117" s="3"/>
-      <c r="Q117" s="3"/>
-      <c r="R117" s="3"/>
-      <c r="S117" s="3"/>
-      <c r="T117" s="3"/>
-      <c r="U117" s="3"/>
-      <c r="V117" s="3"/>
-      <c r="W117" s="3"/>
-      <c r="X117" s="3"/>
-      <c r="Y117" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A117" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B117" s="3">
+        <v>39</v>
+      </c>
+      <c r="C117" s="3">
+        <v>44</v>
+      </c>
+      <c r="D117" s="3">
+        <v>44</v>
+      </c>
+      <c r="E117" s="3">
+        <v>42</v>
+      </c>
+      <c r="F117" s="3">
+        <v>42</v>
+      </c>
+      <c r="G117" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="H117" s="3">
+        <v>44</v>
+      </c>
+      <c r="I117" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J117" s="3">
+        <v>41</v>
+      </c>
+      <c r="K117" s="3">
+        <v>38</v>
+      </c>
+      <c r="L117" s="3">
+        <v>36</v>
+      </c>
+      <c r="M117" s="3">
+        <v>41</v>
+      </c>
+      <c r="N117" s="3">
+        <v>44</v>
+      </c>
+      <c r="O117" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="P117" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q117" s="3">
+        <v>42</v>
+      </c>
+      <c r="R117" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S117" s="3">
+        <v>42</v>
+      </c>
+      <c r="T117" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="U117" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="V117" s="3">
+        <v>38</v>
+      </c>
+      <c r="W117" s="3">
+        <v>44</v>
+      </c>
+      <c r="X117" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y117" s="4">
+        <f t="shared" ref="Y117" si="63">IF(COUNTA(B117:X117)=0,"",AVERAGE(B117:X117))</f>
+        <v>39.678260869565221</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.25">
@@ -16747,7 +16807,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="63">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="64">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="64">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="65">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="65">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="66">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="66">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="67">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24187,7 +24247,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24217,7 +24277,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24247,7 +24307,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24277,7 +24337,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24307,7 +24367,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24337,7 +24397,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24367,7 +24427,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24397,7 +24457,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -24427,7 +24487,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="67">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="68">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24457,7 +24517,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -31994,29 +32054,69 @@
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="3"/>
-      <c r="M117" s="3"/>
-      <c r="N117" s="3"/>
-      <c r="O117" s="3"/>
-      <c r="P117" s="3"/>
-      <c r="Q117" s="3"/>
-      <c r="R117" s="3"/>
-      <c r="S117" s="3"/>
-      <c r="T117" s="3"/>
-      <c r="U117" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A117" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B117" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C117" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E117" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F117" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G117" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H117" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I117" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="J117" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K117" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L117" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M117" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N117" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O117" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P117" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q117" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R117" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S117" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T117" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U117" s="4">
+        <f t="shared" ref="U117" si="71">IF(COUNTA(B117:T117)=0,"",AVERAGE(B117:T117))</f>
+        <v>3.4610526315789478</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -32431,7 +32531,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="71">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="72">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -32457,7 +32557,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32483,7 +32583,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32509,7 +32609,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32535,7 +32635,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32561,7 +32661,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32587,7 +32687,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32613,7 +32713,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32639,7 +32739,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32665,7 +32765,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32691,7 +32791,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32717,7 +32817,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32743,7 +32843,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32769,7 +32869,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32795,7 +32895,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32821,7 +32921,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32847,7 +32947,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32873,7 +32973,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32899,7 +32999,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32925,7 +33025,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32951,7 +33051,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -32977,7 +33077,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33003,7 +33103,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33029,7 +33129,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33055,7 +33155,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33081,7 +33181,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33107,7 +33207,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33133,7 +33233,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33159,7 +33259,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33185,7 +33285,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33211,7 +33311,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33237,7 +33337,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33263,7 +33363,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33289,7 +33389,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33315,7 +33415,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33341,7 +33441,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33367,7 +33467,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33393,7 +33493,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33419,7 +33519,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33445,7 +33545,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33471,7 +33571,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33497,7 +33597,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33523,7 +33623,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33549,7 +33649,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33575,7 +33675,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33601,7 +33701,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33627,7 +33727,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33653,7 +33753,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33679,7 +33779,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33705,7 +33805,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33731,7 +33831,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33757,7 +33857,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33783,7 +33883,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33809,7 +33909,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33835,7 +33935,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33861,7 +33961,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33887,7 +33987,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33913,7 +34013,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33939,7 +34039,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33965,7 +34065,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -33991,7 +34091,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34017,7 +34117,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34043,7 +34143,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34069,7 +34169,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -34095,7 +34195,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="72">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="73">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -34121,7 +34221,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34147,7 +34247,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34173,7 +34273,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34199,7 +34299,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34225,7 +34325,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34251,7 +34351,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34277,7 +34377,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34303,7 +34403,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34329,7 +34429,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34355,7 +34455,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34381,7 +34481,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34407,7 +34507,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34433,7 +34533,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34459,7 +34559,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34485,7 +34585,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34511,7 +34611,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34537,7 +34637,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34563,7 +34663,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34589,7 +34689,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34615,7 +34715,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34641,7 +34741,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34667,7 +34767,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34693,7 +34793,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34719,7 +34819,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34745,7 +34845,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34771,7 +34871,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34797,7 +34897,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34823,7 +34923,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34849,7 +34949,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34875,7 +34975,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34901,7 +35001,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34927,7 +35027,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34953,7 +35053,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34979,7 +35079,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35005,7 +35105,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35031,7 +35131,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35057,7 +35157,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35083,7 +35183,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35109,7 +35209,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35135,7 +35235,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35161,7 +35261,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35187,7 +35287,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35213,7 +35313,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35239,7 +35339,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35265,7 +35365,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35291,7 +35391,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35317,7 +35417,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35343,7 +35443,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35369,7 +35469,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35395,7 +35495,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35421,7 +35521,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35447,7 +35547,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35473,7 +35573,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35499,7 +35599,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35525,7 +35625,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35551,7 +35651,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35577,7 +35677,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35603,7 +35703,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35629,7 +35729,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35655,7 +35755,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35681,7 +35781,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35707,7 +35807,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35733,7 +35833,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -35759,7 +35859,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="73">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="74">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35785,7 +35885,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35811,7 +35911,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35837,7 +35937,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35863,7 +35963,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35889,7 +35989,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35915,7 +36015,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35941,7 +36041,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35967,7 +36067,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35993,7 +36093,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36019,7 +36119,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36045,7 +36145,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36071,7 +36171,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36097,7 +36197,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36123,7 +36223,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36149,7 +36249,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36175,7 +36275,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36201,7 +36301,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36227,7 +36327,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36253,7 +36353,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36279,7 +36379,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36305,7 +36405,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36331,7 +36431,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36357,7 +36457,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36383,7 +36483,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36409,7 +36509,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36435,7 +36535,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36461,7 +36561,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36487,7 +36587,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36513,7 +36613,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36539,7 +36639,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36565,7 +36665,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36591,7 +36691,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36617,7 +36717,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36643,7 +36743,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36669,7 +36769,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36695,7 +36795,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36721,7 +36821,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36747,7 +36847,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36773,7 +36873,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36799,7 +36899,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36825,7 +36925,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36851,7 +36951,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36877,7 +36977,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36903,7 +37003,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36929,7 +37029,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36955,7 +37055,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -36981,7 +37081,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37007,7 +37107,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37033,7 +37133,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37059,7 +37159,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37085,7 +37185,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37111,7 +37211,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37137,7 +37237,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37163,7 +37263,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37189,7 +37289,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37215,7 +37315,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37241,7 +37341,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37267,7 +37367,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37293,7 +37393,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37319,7 +37419,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37345,7 +37445,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37371,7 +37471,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37397,7 +37497,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -37423,7 +37523,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="74">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="75">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -37449,7 +37549,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37475,7 +37575,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37501,7 +37601,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37527,7 +37627,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37553,7 +37653,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37579,7 +37679,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37605,7 +37705,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37631,7 +37731,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37657,7 +37757,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37683,7 +37783,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37709,7 +37809,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37735,7 +37835,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37761,7 +37861,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37787,7 +37887,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37813,7 +37913,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37839,7 +37939,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37865,7 +37965,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37891,7 +37991,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37917,7 +38017,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37943,7 +38043,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37969,7 +38069,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37995,7 +38095,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38021,7 +38121,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38047,7 +38147,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38073,7 +38173,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38099,7 +38199,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38125,7 +38225,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38151,7 +38251,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38177,7 +38277,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38203,7 +38303,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38229,7 +38329,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38255,7 +38355,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38281,7 +38381,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38307,7 +38407,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38333,7 +38433,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38359,7 +38459,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38385,7 +38485,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38411,7 +38511,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38437,7 +38537,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38463,7 +38563,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38489,7 +38589,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38515,7 +38615,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38541,7 +38641,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38567,7 +38667,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38593,7 +38693,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38619,7 +38719,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38645,7 +38745,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38671,7 +38771,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38697,7 +38797,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38723,7 +38823,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38749,7 +38849,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38775,7 +38875,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38801,7 +38901,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38827,7 +38927,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38853,7 +38953,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38879,7 +38979,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38905,7 +39005,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38931,7 +39031,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38957,7 +39057,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -38983,7 +39083,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -39009,7 +39109,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -39035,7 +39135,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -39061,7 +39161,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -39087,7 +39187,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="75">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="76">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -39113,7 +39213,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -43240,19 +43340,39 @@
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A117" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B117" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C117" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D117" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E117" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F117" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G117" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H117" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I117" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J117" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K117" s="4">
+        <f t="shared" ref="K117" si="71">IF(COUNTA(B117:J117)=0,"",AVERAGE(B117:J117))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -43507,7 +43627,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="71">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="72">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -43523,7 +43643,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43539,7 +43659,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43555,7 +43675,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43571,7 +43691,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43587,7 +43707,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43603,7 +43723,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43619,7 +43739,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43635,7 +43755,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43651,7 +43771,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43667,7 +43787,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43683,7 +43803,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43699,7 +43819,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43715,7 +43835,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43731,7 +43851,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43747,7 +43867,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43763,7 +43883,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43779,7 +43899,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43795,7 +43915,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43811,7 +43931,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43827,7 +43947,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43843,7 +43963,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43859,7 +43979,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43875,7 +43995,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43891,7 +44011,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43907,7 +44027,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43923,7 +44043,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43939,7 +44059,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43955,7 +44075,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43971,7 +44091,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -43987,7 +44107,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44003,7 +44123,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44019,7 +44139,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44035,7 +44155,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44051,7 +44171,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44067,7 +44187,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44083,7 +44203,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44099,7 +44219,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44115,7 +44235,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44131,7 +44251,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44147,7 +44267,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44163,7 +44283,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44179,7 +44299,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44195,7 +44315,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44211,7 +44331,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44227,7 +44347,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44243,7 +44363,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44259,7 +44379,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44275,7 +44395,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44291,7 +44411,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44307,7 +44427,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44323,7 +44443,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44339,7 +44459,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44355,7 +44475,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44371,7 +44491,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44387,7 +44507,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44403,7 +44523,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44419,7 +44539,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44435,7 +44555,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44451,7 +44571,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44467,7 +44587,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44483,7 +44603,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44499,7 +44619,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44515,7 +44635,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -44531,7 +44651,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="72">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="73">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -44547,7 +44667,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44563,7 +44683,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44579,7 +44699,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44595,7 +44715,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44611,7 +44731,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44627,7 +44747,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44643,7 +44763,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44659,7 +44779,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44675,7 +44795,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44691,7 +44811,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44707,7 +44827,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44723,7 +44843,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44739,7 +44859,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44755,7 +44875,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44771,7 +44891,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44787,7 +44907,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44803,7 +44923,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44819,7 +44939,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44835,7 +44955,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44851,7 +44971,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44867,7 +44987,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44883,7 +45003,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44899,7 +45019,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44915,7 +45035,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44931,7 +45051,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44947,7 +45067,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44963,7 +45083,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44979,7 +45099,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44995,7 +45115,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45011,7 +45131,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45027,7 +45147,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45043,7 +45163,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45059,7 +45179,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45075,7 +45195,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45091,7 +45211,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45107,7 +45227,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45123,7 +45243,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45139,7 +45259,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45155,7 +45275,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45171,7 +45291,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45187,7 +45307,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45203,7 +45323,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45219,7 +45339,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45235,7 +45355,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45251,7 +45371,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45267,7 +45387,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45283,7 +45403,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45299,7 +45419,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45315,7 +45435,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45331,7 +45451,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45347,7 +45467,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45363,7 +45483,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45379,7 +45499,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45395,7 +45515,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45411,7 +45531,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45427,7 +45547,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45443,7 +45563,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45459,7 +45579,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45475,7 +45595,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45491,7 +45611,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45507,7 +45627,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45523,7 +45643,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45539,7 +45659,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -45555,7 +45675,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="73">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="74">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -45571,7 +45691,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45587,7 +45707,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45603,7 +45723,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45619,7 +45739,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45635,7 +45755,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45651,7 +45771,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45667,7 +45787,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45683,7 +45803,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45699,7 +45819,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45715,7 +45835,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45731,7 +45851,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45747,7 +45867,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45763,7 +45883,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45779,7 +45899,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45795,7 +45915,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45811,7 +45931,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45827,7 +45947,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45843,7 +45963,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45859,7 +45979,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45875,7 +45995,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45891,7 +46011,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45907,7 +46027,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45923,7 +46043,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45939,7 +46059,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45955,7 +46075,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45971,7 +46091,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45987,7 +46107,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46003,7 +46123,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46019,7 +46139,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46035,7 +46155,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46051,7 +46171,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46067,7 +46187,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46083,7 +46203,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46099,7 +46219,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46115,7 +46235,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46131,7 +46251,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46147,7 +46267,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46163,7 +46283,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46179,7 +46299,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46195,7 +46315,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46211,7 +46331,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46227,7 +46347,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46243,7 +46363,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46259,7 +46379,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46275,7 +46395,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46291,7 +46411,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46307,7 +46427,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46323,7 +46443,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46339,7 +46459,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46355,7 +46475,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46371,7 +46491,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46387,7 +46507,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46403,7 +46523,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46419,7 +46539,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46435,7 +46555,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46451,7 +46571,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46467,7 +46587,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46483,7 +46603,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46499,7 +46619,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46515,7 +46635,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46531,7 +46651,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46547,7 +46667,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46563,7 +46683,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -46579,7 +46699,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="74">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="75">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -46595,7 +46715,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46611,7 +46731,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46627,7 +46747,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46643,7 +46763,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46659,7 +46779,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46675,7 +46795,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46691,7 +46811,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46707,7 +46827,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46723,7 +46843,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46739,7 +46859,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46755,7 +46875,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46771,7 +46891,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46787,7 +46907,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46803,7 +46923,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46819,7 +46939,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46835,7 +46955,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46851,7 +46971,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46867,7 +46987,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46883,7 +47003,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46899,7 +47019,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46915,7 +47035,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46931,7 +47051,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46947,7 +47067,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46963,7 +47083,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46979,7 +47099,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46995,7 +47115,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47011,7 +47131,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47027,7 +47147,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47043,7 +47163,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47059,7 +47179,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47075,7 +47195,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47091,7 +47211,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47107,7 +47227,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47123,7 +47243,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47139,7 +47259,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47155,7 +47275,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47171,7 +47291,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47187,7 +47307,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47203,7 +47323,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47219,7 +47339,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47235,7 +47355,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47251,7 +47371,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47267,7 +47387,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47283,7 +47403,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47299,7 +47419,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47315,7 +47435,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47331,7 +47451,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47347,7 +47467,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47363,7 +47483,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47379,7 +47499,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47395,7 +47515,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47411,7 +47531,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47427,7 +47547,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47443,7 +47563,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47459,7 +47579,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47475,7 +47595,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47491,7 +47611,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47507,7 +47627,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47523,7 +47643,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47539,7 +47659,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47555,7 +47675,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47571,7 +47691,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47587,7 +47707,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -47603,7 +47723,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="75">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="76">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -47619,7 +47739,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -52087,20 +52207,42 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A117" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B117" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C117" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D117" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E117" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F117" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G117" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H117" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I117" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J117" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K117" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L117" s="4">
+        <f t="shared" ref="L117" si="71">IF(COUNTA(B117:K117)=0,"",AVERAGE(B117:K117))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -52371,7 +52513,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="71">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="72">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -52388,7 +52530,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52405,7 +52547,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52422,7 +52564,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52439,7 +52581,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52456,7 +52598,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52473,7 +52615,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52490,7 +52632,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52507,7 +52649,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52524,7 +52666,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52541,7 +52683,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52558,7 +52700,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52575,7 +52717,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52592,7 +52734,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52609,7 +52751,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52626,7 +52768,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52643,7 +52785,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52660,7 +52802,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52677,7 +52819,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52694,7 +52836,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52711,7 +52853,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52728,7 +52870,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52745,7 +52887,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52762,7 +52904,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52779,7 +52921,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52796,7 +52938,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52813,7 +52955,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52830,7 +52972,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52847,7 +52989,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52864,7 +53006,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52881,7 +53023,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52898,7 +53040,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52915,7 +53057,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52932,7 +53074,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52949,7 +53091,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52966,7 +53108,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -52983,7 +53125,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53000,7 +53142,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53017,7 +53159,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53034,7 +53176,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53051,7 +53193,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53068,7 +53210,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53085,7 +53227,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53102,7 +53244,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53119,7 +53261,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53136,7 +53278,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53153,7 +53295,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53170,7 +53312,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53187,7 +53329,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53204,7 +53346,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53221,7 +53363,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53238,7 +53380,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53255,7 +53397,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53272,7 +53414,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53289,7 +53431,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53306,7 +53448,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53323,7 +53465,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53340,7 +53482,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53357,7 +53499,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53374,7 +53516,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53391,7 +53533,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53408,7 +53550,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53425,7 +53567,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53442,7 +53584,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
     </row>
@@ -53459,7 +53601,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="72">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="73">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -53476,7 +53618,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53493,7 +53635,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53510,7 +53652,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53527,7 +53669,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53544,7 +53686,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53561,7 +53703,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53578,7 +53720,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53595,7 +53737,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53612,7 +53754,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53629,7 +53771,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53646,7 +53788,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53663,7 +53805,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53680,7 +53822,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53697,7 +53839,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53714,7 +53856,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53731,7 +53873,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53748,7 +53890,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53765,7 +53907,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53782,7 +53924,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53799,7 +53941,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53816,7 +53958,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53833,7 +53975,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53850,7 +53992,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53867,7 +54009,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53884,7 +54026,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53901,7 +54043,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53918,7 +54060,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53935,7 +54077,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53952,7 +54094,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53969,7 +54111,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53986,7 +54128,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54003,7 +54145,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54020,7 +54162,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54037,7 +54179,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54054,7 +54196,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54071,7 +54213,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54088,7 +54230,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54105,7 +54247,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54122,7 +54264,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54139,7 +54281,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54156,7 +54298,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54173,7 +54315,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54190,7 +54332,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54207,7 +54349,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54224,7 +54366,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54241,7 +54383,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54258,7 +54400,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54275,7 +54417,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54292,7 +54434,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54309,7 +54451,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54326,7 +54468,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54343,7 +54485,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54360,7 +54502,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54377,7 +54519,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54394,7 +54536,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54411,7 +54553,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54428,7 +54570,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54445,7 +54587,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54462,7 +54604,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54479,7 +54621,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54496,7 +54638,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54513,7 +54655,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54530,7 +54672,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -54547,7 +54689,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="73">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="74">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -54564,7 +54706,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54581,7 +54723,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54598,7 +54740,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54615,7 +54757,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54632,7 +54774,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54649,7 +54791,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54666,7 +54808,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54683,7 +54825,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54700,7 +54842,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54717,7 +54859,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54734,7 +54876,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54751,7 +54893,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54768,7 +54910,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54785,7 +54927,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54802,7 +54944,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54819,7 +54961,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54836,7 +54978,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54853,7 +54995,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54870,7 +55012,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54887,7 +55029,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54904,7 +55046,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54921,7 +55063,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54938,7 +55080,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54955,7 +55097,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54972,7 +55114,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54989,7 +55131,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55006,7 +55148,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55023,7 +55165,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55040,7 +55182,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55057,7 +55199,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55074,7 +55216,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55091,7 +55233,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55108,7 +55250,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55125,7 +55267,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55142,7 +55284,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55159,7 +55301,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55176,7 +55318,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55193,7 +55335,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55210,7 +55352,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55227,7 +55369,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55244,7 +55386,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55261,7 +55403,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55278,7 +55420,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55295,7 +55437,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55312,7 +55454,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55329,7 +55471,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55346,7 +55488,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55363,7 +55505,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55380,7 +55522,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55397,7 +55539,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55414,7 +55556,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55431,7 +55573,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55448,7 +55590,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55465,7 +55607,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55482,7 +55624,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55499,7 +55641,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55516,7 +55658,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55533,7 +55675,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55550,7 +55692,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55567,7 +55709,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55584,7 +55726,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55601,7 +55743,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55618,7 +55760,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -55635,7 +55777,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="74">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="75">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -55652,7 +55794,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55669,7 +55811,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55686,7 +55828,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55703,7 +55845,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55720,7 +55862,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55737,7 +55879,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55754,7 +55896,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55771,7 +55913,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55788,7 +55930,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55805,7 +55947,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55822,7 +55964,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55839,7 +55981,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55856,7 +55998,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55873,7 +56015,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55890,7 +56032,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55907,7 +56049,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55924,7 +56066,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55941,7 +56083,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55958,7 +56100,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55975,7 +56117,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55992,7 +56134,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56009,7 +56151,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56026,7 +56168,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56043,7 +56185,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56060,7 +56202,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56077,7 +56219,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56094,7 +56236,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56111,7 +56253,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56128,7 +56270,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56145,7 +56287,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56162,7 +56304,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56179,7 +56321,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56196,7 +56338,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56213,7 +56355,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56230,7 +56372,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56247,7 +56389,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56264,7 +56406,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56281,7 +56423,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56298,7 +56440,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56315,7 +56457,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56332,7 +56474,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56349,7 +56491,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56366,7 +56508,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56383,7 +56525,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56400,7 +56542,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56417,7 +56559,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56434,7 +56576,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56451,7 +56593,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56468,7 +56610,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56485,7 +56627,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56502,7 +56644,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56519,7 +56661,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56536,7 +56678,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56553,7 +56695,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56570,7 +56712,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56587,7 +56729,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56604,7 +56746,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56621,7 +56763,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56638,7 +56780,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56655,7 +56797,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56672,7 +56814,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56689,7 +56831,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56706,7 +56848,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -56723,7 +56865,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="75">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="76">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -56740,7 +56882,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DE9F1D-22FD-40C0-A75E-6708E5ACE52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98828562-F8D4-4725-A23A-60FE0CF7FA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -682,6 +682,9 @@
                 <c:pt idx="112">
                   <c:v>46289</c:v>
                 </c:pt>
+                <c:pt idx="113">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1031,7 +1034,7 @@
                   <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0</c:v>
+                  <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>0</c:v>
@@ -2347,6 +2350,9 @@
                 <c:pt idx="112">
                   <c:v>46289</c:v>
                 </c:pt>
+                <c:pt idx="113">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2696,7 +2702,7 @@
                   <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0</c:v>
+                  <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>0</c:v>
@@ -4012,6 +4018,9 @@
                 <c:pt idx="112">
                   <c:v>46289</c:v>
                 </c:pt>
+                <c:pt idx="113">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4361,7 +4370,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>0</c:v>
@@ -5677,6 +5686,9 @@
                 <c:pt idx="112">
                   <c:v>46289</c:v>
                 </c:pt>
+                <c:pt idx="113">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6026,7 +6038,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>0</c:v>
@@ -16332,33 +16344,81 @@
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
-      <c r="O118" s="3"/>
-      <c r="P118" s="3"/>
-      <c r="Q118" s="3"/>
-      <c r="R118" s="3"/>
-      <c r="S118" s="3"/>
-      <c r="T118" s="3"/>
-      <c r="U118" s="3"/>
-      <c r="V118" s="3"/>
-      <c r="W118" s="3"/>
-      <c r="X118" s="3"/>
-      <c r="Y118" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A118" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B118" s="3">
+        <v>39</v>
+      </c>
+      <c r="C118" s="3">
+        <v>44</v>
+      </c>
+      <c r="D118" s="3">
+        <v>44</v>
+      </c>
+      <c r="E118" s="3">
+        <v>42</v>
+      </c>
+      <c r="F118" s="3">
+        <v>42</v>
+      </c>
+      <c r="G118" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="H118" s="3">
+        <v>44</v>
+      </c>
+      <c r="I118" s="3">
+        <v>38.5</v>
+      </c>
+      <c r="J118" s="3">
+        <v>41</v>
+      </c>
+      <c r="K118" s="3">
+        <v>38</v>
+      </c>
+      <c r="L118" s="3">
+        <v>36</v>
+      </c>
+      <c r="M118" s="3">
+        <v>41</v>
+      </c>
+      <c r="N118" s="3">
+        <v>44</v>
+      </c>
+      <c r="O118" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="P118" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q118" s="3">
+        <v>42</v>
+      </c>
+      <c r="R118" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="S118" s="3">
+        <v>42</v>
+      </c>
+      <c r="T118" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="U118" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="V118" s="3">
+        <v>38</v>
+      </c>
+      <c r="W118" s="3">
+        <v>44</v>
+      </c>
+      <c r="X118" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y118" s="4">
+        <f t="shared" ref="Y118" si="64">IF(COUNTA(B118:X118)=0,"",AVERAGE(B118:X118))</f>
+        <v>39.678260869565221</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.25">
@@ -16807,7 +16867,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="64">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="65">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="65">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="66">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="66">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="67">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="67">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="68">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24187,7 +24247,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24217,7 +24277,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24247,7 +24307,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24277,7 +24337,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24307,7 +24367,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24337,7 +24397,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24367,7 +24427,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24397,7 +24457,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24427,7 +24487,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24457,7 +24517,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -24487,7 +24547,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="68">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="69">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24517,7 +24577,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -32120,29 +32180,69 @@
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
-      <c r="O118" s="3"/>
-      <c r="P118" s="3"/>
-      <c r="Q118" s="3"/>
-      <c r="R118" s="3"/>
-      <c r="S118" s="3"/>
-      <c r="T118" s="3"/>
-      <c r="U118" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A118" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B118" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C118" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D118" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E118" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F118" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G118" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H118" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I118" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="J118" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K118" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L118" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M118" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N118" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O118" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P118" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q118" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R118" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S118" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T118" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U118" s="4">
+        <f t="shared" ref="U118" si="72">IF(COUNTA(B118:T118)=0,"",AVERAGE(B118:T118))</f>
+        <v>3.4610526315789478</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -32531,7 +32631,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="72">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="73">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -32557,7 +32657,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32583,7 +32683,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32609,7 +32709,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32635,7 +32735,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32661,7 +32761,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32687,7 +32787,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32713,7 +32813,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32739,7 +32839,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32765,7 +32865,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32791,7 +32891,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32817,7 +32917,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32843,7 +32943,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32869,7 +32969,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32895,7 +32995,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32921,7 +33021,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32947,7 +33047,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32973,7 +33073,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -32999,7 +33099,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33025,7 +33125,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33051,7 +33151,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33077,7 +33177,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33103,7 +33203,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33129,7 +33229,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33155,7 +33255,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33181,7 +33281,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33207,7 +33307,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33233,7 +33333,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33259,7 +33359,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33285,7 +33385,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33311,7 +33411,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33337,7 +33437,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33363,7 +33463,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33389,7 +33489,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33415,7 +33515,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33441,7 +33541,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33467,7 +33567,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33493,7 +33593,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33519,7 +33619,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33545,7 +33645,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33571,7 +33671,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33597,7 +33697,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33623,7 +33723,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33649,7 +33749,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33675,7 +33775,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33701,7 +33801,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33727,7 +33827,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33753,7 +33853,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33779,7 +33879,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33805,7 +33905,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33831,7 +33931,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33857,7 +33957,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33883,7 +33983,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33909,7 +34009,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33935,7 +34035,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33961,7 +34061,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -33987,7 +34087,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34013,7 +34113,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34039,7 +34139,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34065,7 +34165,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34091,7 +34191,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34117,7 +34217,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34143,7 +34243,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34169,7 +34269,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -34195,7 +34295,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="73">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="74">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -34221,7 +34321,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34247,7 +34347,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34273,7 +34373,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34299,7 +34399,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34325,7 +34425,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34351,7 +34451,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34377,7 +34477,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34403,7 +34503,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34429,7 +34529,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34455,7 +34555,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34481,7 +34581,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34507,7 +34607,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34533,7 +34633,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34559,7 +34659,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34585,7 +34685,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34611,7 +34711,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34637,7 +34737,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34663,7 +34763,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34689,7 +34789,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34715,7 +34815,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34741,7 +34841,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34767,7 +34867,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34793,7 +34893,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34819,7 +34919,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34845,7 +34945,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34871,7 +34971,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34897,7 +34997,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34923,7 +35023,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34949,7 +35049,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34975,7 +35075,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35001,7 +35101,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35027,7 +35127,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35053,7 +35153,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35079,7 +35179,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35105,7 +35205,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35131,7 +35231,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35157,7 +35257,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35183,7 +35283,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35209,7 +35309,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35235,7 +35335,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35261,7 +35361,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35287,7 +35387,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35313,7 +35413,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35339,7 +35439,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35365,7 +35465,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35391,7 +35491,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35417,7 +35517,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35443,7 +35543,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35469,7 +35569,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35495,7 +35595,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35521,7 +35621,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35547,7 +35647,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35573,7 +35673,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35599,7 +35699,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35625,7 +35725,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35651,7 +35751,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35677,7 +35777,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35703,7 +35803,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35729,7 +35829,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35755,7 +35855,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35781,7 +35881,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35807,7 +35907,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35833,7 +35933,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -35859,7 +35959,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="74">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="75">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -35885,7 +35985,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -35911,7 +36011,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -35937,7 +36037,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -35963,7 +36063,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -35989,7 +36089,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36015,7 +36115,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36041,7 +36141,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36067,7 +36167,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36093,7 +36193,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36119,7 +36219,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36145,7 +36245,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36171,7 +36271,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36197,7 +36297,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36223,7 +36323,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36249,7 +36349,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36275,7 +36375,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36301,7 +36401,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36327,7 +36427,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36353,7 +36453,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36379,7 +36479,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36405,7 +36505,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36431,7 +36531,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36457,7 +36557,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36483,7 +36583,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36509,7 +36609,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36535,7 +36635,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36561,7 +36661,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36587,7 +36687,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36613,7 +36713,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36639,7 +36739,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36665,7 +36765,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36691,7 +36791,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36717,7 +36817,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36743,7 +36843,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36769,7 +36869,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36795,7 +36895,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36821,7 +36921,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36847,7 +36947,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36873,7 +36973,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36899,7 +36999,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36925,7 +37025,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36951,7 +37051,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -36977,7 +37077,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37003,7 +37103,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37029,7 +37129,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37055,7 +37155,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37081,7 +37181,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37107,7 +37207,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37133,7 +37233,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37159,7 +37259,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37185,7 +37285,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37211,7 +37311,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37237,7 +37337,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37263,7 +37363,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37289,7 +37389,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37315,7 +37415,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37341,7 +37441,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37367,7 +37467,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37393,7 +37493,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37419,7 +37519,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37445,7 +37545,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37471,7 +37571,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37497,7 +37597,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -37523,7 +37623,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="75">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="76">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -37549,7 +37649,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37575,7 +37675,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37601,7 +37701,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37627,7 +37727,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37653,7 +37753,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37679,7 +37779,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37705,7 +37805,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37731,7 +37831,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37757,7 +37857,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37783,7 +37883,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37809,7 +37909,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37835,7 +37935,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37861,7 +37961,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37887,7 +37987,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37913,7 +38013,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37939,7 +38039,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37965,7 +38065,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -37991,7 +38091,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38017,7 +38117,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38043,7 +38143,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38069,7 +38169,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38095,7 +38195,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38121,7 +38221,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38147,7 +38247,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38173,7 +38273,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38199,7 +38299,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38225,7 +38325,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38251,7 +38351,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38277,7 +38377,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38303,7 +38403,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38329,7 +38429,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38355,7 +38455,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38381,7 +38481,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38407,7 +38507,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38433,7 +38533,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38459,7 +38559,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38485,7 +38585,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38511,7 +38611,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38537,7 +38637,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38563,7 +38663,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38589,7 +38689,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38615,7 +38715,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38641,7 +38741,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38667,7 +38767,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38693,7 +38793,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38719,7 +38819,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38745,7 +38845,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38771,7 +38871,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38797,7 +38897,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38823,7 +38923,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38849,7 +38949,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38875,7 +38975,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38901,7 +39001,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38927,7 +39027,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38953,7 +39053,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -38979,7 +39079,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39005,7 +39105,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39031,7 +39131,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39057,7 +39157,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39083,7 +39183,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39109,7 +39209,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39135,7 +39235,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39161,7 +39261,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -39187,7 +39287,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="76">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="77">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -39213,7 +39313,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v/>
       </c>
     </row>
@@ -43376,19 +43476,39 @@
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A118" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B118" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C118" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D118" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E118" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F118" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G118" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H118" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I118" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J118" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K118" s="4">
+        <f t="shared" ref="K118" si="72">IF(COUNTA(B118:J118)=0,"",AVERAGE(B118:J118))</f>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -43627,7 +43747,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="72">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="73">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -43643,7 +43763,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43659,7 +43779,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43675,7 +43795,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43691,7 +43811,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43707,7 +43827,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43723,7 +43843,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43739,7 +43859,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43755,7 +43875,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43771,7 +43891,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43787,7 +43907,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43803,7 +43923,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43819,7 +43939,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43835,7 +43955,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43851,7 +43971,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43867,7 +43987,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43883,7 +44003,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43899,7 +44019,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43915,7 +44035,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43931,7 +44051,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43947,7 +44067,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43963,7 +44083,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43979,7 +44099,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -43995,7 +44115,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44011,7 +44131,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44027,7 +44147,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44043,7 +44163,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44059,7 +44179,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44075,7 +44195,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44091,7 +44211,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44107,7 +44227,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44123,7 +44243,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44139,7 +44259,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44155,7 +44275,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44171,7 +44291,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44187,7 +44307,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44203,7 +44323,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44219,7 +44339,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44235,7 +44355,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44251,7 +44371,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44267,7 +44387,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44283,7 +44403,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44299,7 +44419,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44315,7 +44435,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44331,7 +44451,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44347,7 +44467,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44363,7 +44483,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44379,7 +44499,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44395,7 +44515,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44411,7 +44531,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44427,7 +44547,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44443,7 +44563,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44459,7 +44579,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44475,7 +44595,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44491,7 +44611,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44507,7 +44627,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44523,7 +44643,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44539,7 +44659,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44555,7 +44675,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44571,7 +44691,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44587,7 +44707,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44603,7 +44723,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44619,7 +44739,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44635,7 +44755,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -44651,7 +44771,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="73">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="74">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -44667,7 +44787,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44683,7 +44803,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44699,7 +44819,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44715,7 +44835,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44731,7 +44851,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44747,7 +44867,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44763,7 +44883,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44779,7 +44899,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44795,7 +44915,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44811,7 +44931,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44827,7 +44947,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44843,7 +44963,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44859,7 +44979,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44875,7 +44995,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44891,7 +45011,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44907,7 +45027,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44923,7 +45043,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44939,7 +45059,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44955,7 +45075,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44971,7 +45091,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -44987,7 +45107,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45003,7 +45123,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45019,7 +45139,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45035,7 +45155,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45051,7 +45171,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45067,7 +45187,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45083,7 +45203,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45099,7 +45219,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45115,7 +45235,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45131,7 +45251,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45147,7 +45267,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45163,7 +45283,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45179,7 +45299,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45195,7 +45315,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45211,7 +45331,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45227,7 +45347,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45243,7 +45363,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45259,7 +45379,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45275,7 +45395,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45291,7 +45411,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45307,7 +45427,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45323,7 +45443,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45339,7 +45459,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45355,7 +45475,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45371,7 +45491,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45387,7 +45507,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45403,7 +45523,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45419,7 +45539,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45435,7 +45555,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45451,7 +45571,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45467,7 +45587,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45483,7 +45603,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45499,7 +45619,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45515,7 +45635,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45531,7 +45651,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45547,7 +45667,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45563,7 +45683,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45579,7 +45699,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45595,7 +45715,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45611,7 +45731,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45627,7 +45747,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45643,7 +45763,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45659,7 +45779,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -45675,7 +45795,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="74">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="75">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -45691,7 +45811,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45707,7 +45827,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45723,7 +45843,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45739,7 +45859,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45755,7 +45875,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45771,7 +45891,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45787,7 +45907,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45803,7 +45923,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45819,7 +45939,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45835,7 +45955,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45851,7 +45971,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45867,7 +45987,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45883,7 +46003,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45899,7 +46019,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45915,7 +46035,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45931,7 +46051,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45947,7 +46067,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45963,7 +46083,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45979,7 +46099,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -45995,7 +46115,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46011,7 +46131,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46027,7 +46147,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46043,7 +46163,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46059,7 +46179,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46075,7 +46195,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46091,7 +46211,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46107,7 +46227,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46123,7 +46243,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46139,7 +46259,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46155,7 +46275,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46171,7 +46291,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46187,7 +46307,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46203,7 +46323,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46219,7 +46339,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46235,7 +46355,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46251,7 +46371,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46267,7 +46387,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46283,7 +46403,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46299,7 +46419,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46315,7 +46435,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46331,7 +46451,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46347,7 +46467,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46363,7 +46483,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46379,7 +46499,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46395,7 +46515,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46411,7 +46531,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46427,7 +46547,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46443,7 +46563,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46459,7 +46579,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46475,7 +46595,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46491,7 +46611,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46507,7 +46627,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46523,7 +46643,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46539,7 +46659,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46555,7 +46675,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46571,7 +46691,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46587,7 +46707,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46603,7 +46723,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46619,7 +46739,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46635,7 +46755,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46651,7 +46771,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46667,7 +46787,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46683,7 +46803,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -46699,7 +46819,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="75">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="76">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -46715,7 +46835,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46731,7 +46851,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46747,7 +46867,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46763,7 +46883,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46779,7 +46899,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46795,7 +46915,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46811,7 +46931,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46827,7 +46947,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46843,7 +46963,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46859,7 +46979,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46875,7 +46995,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46891,7 +47011,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46907,7 +47027,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46923,7 +47043,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46939,7 +47059,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46955,7 +47075,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46971,7 +47091,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -46987,7 +47107,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47003,7 +47123,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47019,7 +47139,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47035,7 +47155,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47051,7 +47171,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47067,7 +47187,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47083,7 +47203,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47099,7 +47219,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47115,7 +47235,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47131,7 +47251,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47147,7 +47267,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47163,7 +47283,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47179,7 +47299,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47195,7 +47315,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47211,7 +47331,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47227,7 +47347,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47243,7 +47363,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47259,7 +47379,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47275,7 +47395,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47291,7 +47411,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47307,7 +47427,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47323,7 +47443,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47339,7 +47459,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47355,7 +47475,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47371,7 +47491,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47387,7 +47507,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47403,7 +47523,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47419,7 +47539,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47435,7 +47555,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47451,7 +47571,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47467,7 +47587,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47483,7 +47603,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47499,7 +47619,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47515,7 +47635,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47531,7 +47651,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47547,7 +47667,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47563,7 +47683,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47579,7 +47699,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47595,7 +47715,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47611,7 +47731,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47627,7 +47747,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47643,7 +47763,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47659,7 +47779,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47675,7 +47795,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47691,7 +47811,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47707,7 +47827,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -47723,7 +47843,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="76">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="77">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -47739,7 +47859,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v/>
       </c>
     </row>
@@ -52246,20 +52366,42 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A118" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B118" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C118" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D118" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E118" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F118" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G118" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H118" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I118" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J118" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K118" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L118" s="4">
+        <f t="shared" ref="L118" si="72">IF(COUNTA(B118:K118)=0,"",AVERAGE(B118:K118))</f>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -52513,7 +52655,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="72">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="73">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -52530,7 +52672,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52547,7 +52689,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52564,7 +52706,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52581,7 +52723,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52598,7 +52740,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52615,7 +52757,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52632,7 +52774,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52649,7 +52791,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52666,7 +52808,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52683,7 +52825,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52700,7 +52842,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52717,7 +52859,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52734,7 +52876,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52751,7 +52893,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52768,7 +52910,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52785,7 +52927,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52802,7 +52944,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52819,7 +52961,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52836,7 +52978,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52853,7 +52995,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52870,7 +53012,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52887,7 +53029,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52904,7 +53046,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52921,7 +53063,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52938,7 +53080,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52955,7 +53097,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52972,7 +53114,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -52989,7 +53131,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53006,7 +53148,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53023,7 +53165,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53040,7 +53182,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53057,7 +53199,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53074,7 +53216,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53091,7 +53233,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53108,7 +53250,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53125,7 +53267,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53142,7 +53284,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53159,7 +53301,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53176,7 +53318,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53193,7 +53335,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53210,7 +53352,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53227,7 +53369,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53244,7 +53386,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53261,7 +53403,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53278,7 +53420,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53295,7 +53437,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53312,7 +53454,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53329,7 +53471,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53346,7 +53488,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53363,7 +53505,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53380,7 +53522,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53397,7 +53539,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53414,7 +53556,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53431,7 +53573,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53448,7 +53590,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53465,7 +53607,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53482,7 +53624,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53499,7 +53641,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53516,7 +53658,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53533,7 +53675,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53550,7 +53692,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53567,7 +53709,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53584,7 +53726,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
     </row>
@@ -53601,7 +53743,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="73">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="74">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -53618,7 +53760,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53635,7 +53777,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53652,7 +53794,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53669,7 +53811,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53686,7 +53828,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53703,7 +53845,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53720,7 +53862,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53737,7 +53879,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53754,7 +53896,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53771,7 +53913,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53788,7 +53930,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53805,7 +53947,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53822,7 +53964,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53839,7 +53981,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53856,7 +53998,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53873,7 +54015,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53890,7 +54032,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53907,7 +54049,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53924,7 +54066,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53941,7 +54083,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53958,7 +54100,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53975,7 +54117,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -53992,7 +54134,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54009,7 +54151,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54026,7 +54168,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54043,7 +54185,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54060,7 +54202,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54077,7 +54219,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54094,7 +54236,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54111,7 +54253,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54128,7 +54270,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54145,7 +54287,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54162,7 +54304,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54179,7 +54321,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54196,7 +54338,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54213,7 +54355,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54230,7 +54372,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54247,7 +54389,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54264,7 +54406,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54281,7 +54423,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54298,7 +54440,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54315,7 +54457,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54332,7 +54474,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54349,7 +54491,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54366,7 +54508,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54383,7 +54525,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54400,7 +54542,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54417,7 +54559,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54434,7 +54576,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54451,7 +54593,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54468,7 +54610,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54485,7 +54627,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54502,7 +54644,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54519,7 +54661,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54536,7 +54678,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54553,7 +54695,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54570,7 +54712,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54587,7 +54729,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54604,7 +54746,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54621,7 +54763,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54638,7 +54780,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54655,7 +54797,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54672,7 +54814,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -54689,7 +54831,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="74">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="75">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -54706,7 +54848,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54723,7 +54865,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54740,7 +54882,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54757,7 +54899,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54774,7 +54916,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54791,7 +54933,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54808,7 +54950,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54825,7 +54967,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54842,7 +54984,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54859,7 +55001,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54876,7 +55018,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54893,7 +55035,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54910,7 +55052,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54927,7 +55069,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54944,7 +55086,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54961,7 +55103,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54978,7 +55120,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -54995,7 +55137,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55012,7 +55154,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55029,7 +55171,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55046,7 +55188,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55063,7 +55205,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55080,7 +55222,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55097,7 +55239,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55114,7 +55256,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55131,7 +55273,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55148,7 +55290,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55165,7 +55307,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55182,7 +55324,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55199,7 +55341,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55216,7 +55358,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55233,7 +55375,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55250,7 +55392,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55267,7 +55409,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55284,7 +55426,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55301,7 +55443,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55318,7 +55460,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55335,7 +55477,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55352,7 +55494,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55369,7 +55511,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55386,7 +55528,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55403,7 +55545,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55420,7 +55562,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55437,7 +55579,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55454,7 +55596,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55471,7 +55613,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55488,7 +55630,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55505,7 +55647,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55522,7 +55664,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55539,7 +55681,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55556,7 +55698,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55573,7 +55715,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55590,7 +55732,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55607,7 +55749,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55624,7 +55766,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55641,7 +55783,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55658,7 +55800,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55675,7 +55817,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55692,7 +55834,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55709,7 +55851,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55726,7 +55868,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55743,7 +55885,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55760,7 +55902,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -55777,7 +55919,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="75">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="76">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -55794,7 +55936,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55811,7 +55953,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55828,7 +55970,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55845,7 +55987,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55862,7 +56004,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55879,7 +56021,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55896,7 +56038,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55913,7 +56055,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55930,7 +56072,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55947,7 +56089,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55964,7 +56106,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55981,7 +56123,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -55998,7 +56140,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56015,7 +56157,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56032,7 +56174,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56049,7 +56191,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56066,7 +56208,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56083,7 +56225,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56100,7 +56242,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56117,7 +56259,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56134,7 +56276,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56151,7 +56293,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56168,7 +56310,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56185,7 +56327,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56202,7 +56344,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56219,7 +56361,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56236,7 +56378,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56253,7 +56395,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56270,7 +56412,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56287,7 +56429,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56304,7 +56446,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56321,7 +56463,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56338,7 +56480,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56355,7 +56497,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56372,7 +56514,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56389,7 +56531,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56406,7 +56548,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56423,7 +56565,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56440,7 +56582,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56457,7 +56599,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56474,7 +56616,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56491,7 +56633,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56508,7 +56650,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56525,7 +56667,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56542,7 +56684,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56559,7 +56701,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56576,7 +56718,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56593,7 +56735,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56610,7 +56752,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56627,7 +56769,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56644,7 +56786,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56661,7 +56803,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56678,7 +56820,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56695,7 +56837,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56712,7 +56854,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56729,7 +56871,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56746,7 +56888,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56763,7 +56905,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56780,7 +56922,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56797,7 +56939,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56814,7 +56956,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56831,7 +56973,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56848,7 +56990,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
     </row>
@@ -56865,7 +57007,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="76">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="77">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -56882,7 +57024,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98828562-F8D4-4725-A23A-60FE0CF7FA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C4FF2F-19A5-43C6-85F0-C49A1D02B40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -685,6 +685,9 @@
                 <c:pt idx="113">
                   <c:v>46290</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>46293</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1037,7 +1040,7 @@
                   <c:v>39.678260869565221</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0</c:v>
+                  <c:v>41.098260869565216</c:v>
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>0</c:v>
@@ -2353,6 +2356,9 @@
                 <c:pt idx="113">
                   <c:v>46290</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>46293</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2705,7 +2711,7 @@
                   <c:v>3.4610526315789478</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0</c:v>
+                  <c:v>3.453157894736842</c:v>
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>0</c:v>
@@ -4021,6 +4027,9 @@
                 <c:pt idx="113">
                   <c:v>46290</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>46293</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4373,7 +4382,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>0</c:v>
@@ -5689,6 +5698,9 @@
                 <c:pt idx="113">
                   <c:v>46290</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>46293</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6041,7 +6053,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>0</c:v>
@@ -16422,33 +16434,81 @@
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
-      <c r="O119" s="3"/>
-      <c r="P119" s="3"/>
-      <c r="Q119" s="3"/>
-      <c r="R119" s="3"/>
-      <c r="S119" s="3"/>
-      <c r="T119" s="3"/>
-      <c r="U119" s="3"/>
-      <c r="V119" s="3"/>
-      <c r="W119" s="3"/>
-      <c r="X119" s="3"/>
-      <c r="Y119" s="4" t="str">
+      <c r="A119" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B119" s="3">
+        <v>39</v>
+      </c>
+      <c r="C119" s="3">
+        <v>44</v>
+      </c>
+      <c r="D119" s="3">
+        <v>44</v>
+      </c>
+      <c r="E119" s="3">
+        <v>42</v>
+      </c>
+      <c r="F119" s="3">
+        <v>42</v>
+      </c>
+      <c r="G119" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H119" s="3">
+        <v>44</v>
+      </c>
+      <c r="I119" s="3">
+        <v>38</v>
+      </c>
+      <c r="J119" s="3">
+        <v>41</v>
+      </c>
+      <c r="K119" s="3">
+        <v>38</v>
+      </c>
+      <c r="L119" s="3">
+        <v>36</v>
+      </c>
+      <c r="M119" s="3">
+        <v>41</v>
+      </c>
+      <c r="N119" s="3">
+        <v>44</v>
+      </c>
+      <c r="O119" s="3">
+        <v>41.26</v>
+      </c>
+      <c r="P119" s="3">
+        <v>38</v>
+      </c>
+      <c r="Q119" s="3">
+        <v>42</v>
+      </c>
+      <c r="R119" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="S119" s="3">
+        <v>42</v>
+      </c>
+      <c r="T119" s="3">
+        <v>40.25</v>
+      </c>
+      <c r="U119" s="3">
+        <v>42</v>
+      </c>
+      <c r="V119" s="3">
+        <v>38</v>
+      </c>
+      <c r="W119" s="3">
+        <v>44</v>
+      </c>
+      <c r="X119" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="Y119" s="4">
         <f t="shared" si="26"/>
-        <v/>
+        <v>41.098260869565216</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.25">
@@ -32246,29 +32306,69 @@
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
-      <c r="O119" s="3"/>
-      <c r="P119" s="3"/>
-      <c r="Q119" s="3"/>
-      <c r="R119" s="3"/>
-      <c r="S119" s="3"/>
-      <c r="T119" s="3"/>
-      <c r="U119" s="4" t="str">
+      <c r="A119" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B119" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C119" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D119" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E119" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F119" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G119" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H119" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I119" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="J119" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K119" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="L119" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M119" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N119" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O119" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P119" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q119" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R119" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S119" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T119" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U119" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.453157894736842</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -43512,19 +43612,39 @@
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="4" t="str">
+      <c r="A119" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B119" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="C119" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="D119" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="E119" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="F119" s="3">
+        <v>2.87</v>
+      </c>
+      <c r="G119" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="H119" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I119" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="J119" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K119" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.0022222222222221</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -52405,20 +52525,42 @@
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="4" t="str">
+      <c r="A119" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B119" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C119" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D119" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E119" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F119" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="G119" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="H119" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="I119" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J119" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="K119" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L119" s="4">
         <f t="shared" si="34"/>
-        <v/>
+        <v>3.3109999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C4FF2F-19A5-43C6-85F0-C49A1D02B40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5398F557-1D2C-4BEA-B5D4-DE3093E36A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -688,6 +688,9 @@
                 <c:pt idx="114">
                   <c:v>46293</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46294</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1043,7 +1046,7 @@
                   <c:v>41.098260869565216</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0</c:v>
+                  <c:v>41.098260869565216</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>0</c:v>
@@ -2359,6 +2362,9 @@
                 <c:pt idx="114">
                   <c:v>46293</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46294</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2714,7 +2720,7 @@
                   <c:v>3.453157894736842</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0</c:v>
+                  <c:v>3.453157894736842</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>0</c:v>
@@ -4030,6 +4036,9 @@
                 <c:pt idx="114">
                   <c:v>46293</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46294</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4385,7 +4394,7 @@
                   <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0</c:v>
+                  <c:v>3.0022222222222221</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>0</c:v>
@@ -5701,6 +5710,9 @@
                 <c:pt idx="114">
                   <c:v>46293</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46294</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6056,7 +6068,7 @@
                   <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0</c:v>
+                  <c:v>3.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>0</c:v>
@@ -16512,33 +16524,81 @@
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3"/>
-      <c r="O120" s="3"/>
-      <c r="P120" s="3"/>
-      <c r="Q120" s="3"/>
-      <c r="R120" s="3"/>
-      <c r="S120" s="3"/>
-      <c r="T120" s="3"/>
-      <c r="U120" s="3"/>
-      <c r="V120" s="3"/>
-      <c r="W120" s="3"/>
-      <c r="X120" s="3"/>
-      <c r="Y120" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A120" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B120" s="3">
+        <v>39</v>
+      </c>
+      <c r="C120" s="3">
+        <v>44</v>
+      </c>
+      <c r="D120" s="3">
+        <v>44</v>
+      </c>
+      <c r="E120" s="3">
+        <v>42</v>
+      </c>
+      <c r="F120" s="3">
+        <v>42</v>
+      </c>
+      <c r="G120" s="3">
+        <v>37.75</v>
+      </c>
+      <c r="H120" s="3">
+        <v>44</v>
+      </c>
+      <c r="I120" s="3">
+        <v>38</v>
+      </c>
+      <c r="J120" s="3">
+        <v>41</v>
+      </c>
+      <c r="K120" s="3">
+        <v>38</v>
+      </c>
+      <c r="L120" s="3">
+        <v>36</v>
+      </c>
+      <c r="M120" s="3">
+        <v>41</v>
+      </c>
+      <c r="N120" s="3">
+        <v>44</v>
+      </c>
+      <c r="O120" s="3">
+        <v>41.26</v>
+      </c>
+      <c r="P120" s="3">
+        <v>38</v>
+      </c>
+      <c r="Q120" s="3">
+        <v>42</v>
+      </c>
+      <c r="R120" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="S120" s="3">
+        <v>42</v>
+      </c>
+      <c r="T120" s="3">
+        <v>40.25</v>
+      </c>
+      <c r="U120" s="3">
+        <v>42</v>
+      </c>
+      <c r="V120" s="3">
+        <v>38</v>
+      </c>
+      <c r="W120" s="3">
+        <v>44</v>
+      </c>
+      <c r="X120" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="Y120" s="4">
+        <f t="shared" ref="Y120" si="65">IF(COUNTA(B120:X120)=0,"",AVERAGE(B120:X120))</f>
+        <v>41.098260869565216</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.25">
@@ -16927,7 +16987,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="65">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="66">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="66">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="67">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="67">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="68">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21967,7 +22027,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -21997,7 +22057,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22027,7 +22087,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22057,7 +22117,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22087,7 +22147,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22117,7 +22177,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22147,7 +22207,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22177,7 +22237,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22207,7 +22267,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22237,7 +22297,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22267,7 +22327,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22297,7 +22357,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22327,7 +22387,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22357,7 +22417,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22387,7 +22447,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22417,7 +22477,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22447,7 +22507,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22477,7 +22537,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22507,7 +22567,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22537,7 +22597,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22567,7 +22627,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22597,7 +22657,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22627,7 +22687,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22657,7 +22717,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
     </row>
@@ -22687,7 +22747,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="68">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="69">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -22717,7 +22777,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22747,7 +22807,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22777,7 +22837,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22807,7 +22867,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22837,7 +22897,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22867,7 +22927,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22897,7 +22957,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22927,7 +22987,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22957,7 +23017,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -22987,7 +23047,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23017,7 +23077,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23047,7 +23107,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23077,7 +23137,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23107,7 +23167,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23137,7 +23197,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23167,7 +23227,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23197,7 +23257,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23227,7 +23287,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23257,7 +23317,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23287,7 +23347,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23317,7 +23377,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23347,7 +23407,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23377,7 +23437,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23407,7 +23467,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23437,7 +23497,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23467,7 +23527,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23497,7 +23557,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23527,7 +23587,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23557,7 +23617,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23587,7 +23647,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23617,7 +23677,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23647,7 +23707,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23677,7 +23737,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23707,7 +23767,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23737,7 +23797,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23767,7 +23827,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23797,7 +23857,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23827,7 +23887,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23857,7 +23917,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23887,7 +23947,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23917,7 +23977,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23947,7 +24007,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -23977,7 +24037,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24007,7 +24067,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24037,7 +24097,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24067,7 +24127,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24097,7 +24157,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24127,7 +24187,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24157,7 +24217,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24187,7 +24247,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24217,7 +24277,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24247,7 +24307,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24277,7 +24337,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24307,7 +24367,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24337,7 +24397,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24367,7 +24427,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24397,7 +24457,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24427,7 +24487,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24457,7 +24517,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24487,7 +24547,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24517,7 +24577,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24547,7 +24607,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24577,7 +24637,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
     </row>
@@ -24607,7 +24667,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="69">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="70">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -24637,7 +24697,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
     </row>
@@ -32372,29 +32432,69 @@
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3"/>
-      <c r="O120" s="3"/>
-      <c r="P120" s="3"/>
-      <c r="Q120" s="3"/>
-      <c r="R120" s="3"/>
-      <c r="S120" s="3"/>
-      <c r="T120" s="3"/>
-      <c r="U120" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A120" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B120" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C120" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="E120" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="F120" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G120" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="H120" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I120" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="J120" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="K120" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="L120" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M120" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N120" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O120" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="P120" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="Q120" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="R120" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="S120" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T120" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U120" s="4">
+        <f t="shared" ref="U120" si="73">IF(COUNTA(B120:T120)=0,"",AVERAGE(B120:T120))</f>
+        <v>3.453157894736842</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -32731,7 +32831,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="73">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="74">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -32757,7 +32857,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32783,7 +32883,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32809,7 +32909,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32835,7 +32935,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32861,7 +32961,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32887,7 +32987,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32913,7 +33013,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32939,7 +33039,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32965,7 +33065,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -32991,7 +33091,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33017,7 +33117,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33043,7 +33143,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33069,7 +33169,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33095,7 +33195,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33121,7 +33221,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33147,7 +33247,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33173,7 +33273,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33199,7 +33299,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33225,7 +33325,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33251,7 +33351,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33277,7 +33377,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33303,7 +33403,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33329,7 +33429,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33355,7 +33455,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33381,7 +33481,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33407,7 +33507,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33433,7 +33533,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33459,7 +33559,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33485,7 +33585,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33511,7 +33611,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33537,7 +33637,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33563,7 +33663,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33589,7 +33689,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33615,7 +33715,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33641,7 +33741,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33667,7 +33767,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33693,7 +33793,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33719,7 +33819,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33745,7 +33845,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33771,7 +33871,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33797,7 +33897,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33823,7 +33923,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33849,7 +33949,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33875,7 +33975,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33901,7 +34001,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33927,7 +34027,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33953,7 +34053,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -33979,7 +34079,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34005,7 +34105,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34031,7 +34131,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34057,7 +34157,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34083,7 +34183,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34109,7 +34209,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34135,7 +34235,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34161,7 +34261,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34187,7 +34287,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34213,7 +34313,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34239,7 +34339,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34265,7 +34365,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34291,7 +34391,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34317,7 +34417,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34343,7 +34443,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34369,7 +34469,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
     </row>
@@ -34395,7 +34495,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="74">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="75">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -34421,7 +34521,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -34447,7 +34547,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -34473,7 +34573,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -34499,7 +34599,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -34525,7 +34625,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
     </row>
@@ -34551,7 +34651,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="s